--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1380,7 +1380,7 @@
         <v>127016698</v>
       </c>
       <c r="B8" t="n">
-        <v>106200</v>
+        <v>106275</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127016863</v>
       </c>
       <c r="B10" t="n">
-        <v>106654</v>
+        <v>106729</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,6 +1688,4385 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127295526</v>
+      </c>
+      <c r="B11" t="n">
+        <v>107318</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>705394</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6396670</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127295536</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106275</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>705357</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6396670</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127295472</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>671</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>705521</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6396665</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Röse 10 m V.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127295515</v>
+      </c>
+      <c r="B14" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>671</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>705366</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6396780</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minsta antal. Mot ny myrstack.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127295474</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>671</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>705499</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6396683</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127295490</v>
+      </c>
+      <c r="B16" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>705332</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6396980</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127295507</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>705371</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6396780</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127295476</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>671</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>705490</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6396722</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127295477</v>
+      </c>
+      <c r="B19" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>671</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>705490</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6396728</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, vid myrstig nära granar.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127295488</v>
+      </c>
+      <c r="B20" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>671</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>705308</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6396955</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127295527</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>671</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>705395</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6396678</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Just N sten.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127295514</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>705366</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6396780</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127295501</v>
+      </c>
+      <c r="B23" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>671</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>705351</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6396798</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127295516</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>705383</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6396779</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127295505</v>
+      </c>
+      <c r="B25" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>671</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>705352</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6396785</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127295481</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>671</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>705478</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6396749</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127295504</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106031</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>705352</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6396785</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127295475</v>
+      </c>
+      <c r="B28" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>671</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>705501</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6396721</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127295616</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>705528</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6396664</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127295511</v>
+      </c>
+      <c r="B30" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>671</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>705371</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6396787</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127296628</v>
+      </c>
+      <c r="B31" t="n">
+        <v>43059</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101260</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svartfläckig blåvinge</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>705369</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6396695</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127295486</v>
+      </c>
+      <c r="B32" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>671</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>705414</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6396806</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127295482</v>
+      </c>
+      <c r="B33" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>671</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>705483</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6396749</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127295551</v>
+      </c>
+      <c r="B34" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>671</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>705400</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6396606</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ungefärligt antal; småex.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127295537</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>705357</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6396670</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127295550</v>
+      </c>
+      <c r="B36" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>671</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>705402</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6396607</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ungefärligt antal; småex.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127295520</v>
+      </c>
+      <c r="B37" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>671</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>705389</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6396765</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127295553</v>
+      </c>
+      <c r="B38" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>671</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>705399</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6396595</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127295510</v>
+      </c>
+      <c r="B39" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>671</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>705381</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6396796</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127295499</v>
+      </c>
+      <c r="B40" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>671</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>705323</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6396800</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minsta antal. Nära stor dubbelgran.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127295485</v>
+      </c>
+      <c r="B41" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>671</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>705434</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6396784</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127295478</v>
+      </c>
+      <c r="B42" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>671</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>705482</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6396738</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127295517</v>
+      </c>
+      <c r="B43" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>671</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>705383</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6396779</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid svag myrstig.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127295509</v>
+      </c>
+      <c r="B44" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>671</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>705371</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6396780</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127295483</v>
+      </c>
+      <c r="B45" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>671</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>705466</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6396767</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127295512</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98414</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>705380</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6396786</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127295531</v>
+      </c>
+      <c r="B47" t="n">
+        <v>106275</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>705369</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6396695</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127295479</v>
+      </c>
+      <c r="B48" t="n">
+        <v>105565</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>671</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>705482</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6396736</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, nära granar.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127295532</v>
+      </c>
+      <c r="B49" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>705369</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6396695</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127016376</v>
+        <v>127016698</v>
       </c>
       <c r="B7" t="n">
-        <v>57578</v>
+        <v>106281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,27 +1287,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>221903</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1315,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>705342</v>
+        <v>705426</v>
       </c>
       <c r="R7" t="n">
-        <v>6396842</v>
+        <v>6396735</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,12 +1349,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1363,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1377,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127016698</v>
+        <v>127016376</v>
       </c>
       <c r="B8" t="n">
-        <v>106275</v>
+        <v>57578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,31 +1393,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221903</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1420,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705426</v>
+        <v>705342</v>
       </c>
       <c r="R8" t="n">
-        <v>6396735</v>
+        <v>6396842</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,12 +1451,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1465,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>127016863</v>
       </c>
       <c r="B10" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>127295536</v>
       </c>
       <c r="B12" t="n">
-        <v>106275</v>
+        <v>106281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>127295472</v>
       </c>
       <c r="B13" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>127295515</v>
       </c>
       <c r="B14" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>127295474</v>
       </c>
       <c r="B15" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,37 +2246,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295490</v>
+        <v>127295507</v>
       </c>
       <c r="B16" t="n">
-        <v>109260</v>
+        <v>98420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705332</v>
+        <v>705371</v>
       </c>
       <c r="R16" t="n">
-        <v>6396980</v>
+        <v>6396780</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,11 +2326,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,37 +2357,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295507</v>
+        <v>127295490</v>
       </c>
       <c r="B17" t="n">
-        <v>98414</v>
+        <v>109266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2406,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705371</v>
+        <v>705332</v>
       </c>
       <c r="R17" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,6 +2437,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,7 +2476,7 @@
         <v>127295476</v>
       </c>
       <c r="B18" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127295477</v>
       </c>
       <c r="B19" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,37 +2806,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295527</v>
+        <v>127295514</v>
       </c>
       <c r="B21" t="n">
-        <v>105565</v>
+        <v>98420</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705395</v>
+        <v>705366</v>
       </c>
       <c r="R21" t="n">
-        <v>6396678</v>
+        <v>6396780</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2888,11 +2888,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Just N sten.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2904,7 +2899,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2922,37 +2917,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295514</v>
+        <v>127295527</v>
       </c>
       <c r="B22" t="n">
-        <v>98414</v>
+        <v>105571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2966,10 +2961,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705366</v>
+        <v>705395</v>
       </c>
       <c r="R22" t="n">
-        <v>6396780</v>
+        <v>6396678</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3004,6 +2999,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Just N sten.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
         <v>127295501</v>
       </c>
       <c r="B23" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>98414</v>
+        <v>105571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R24" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,6 +3231,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3242,7 +3247,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,37 +3265,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>105565</v>
+        <v>98420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3304,13 +3309,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R25" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,11 +3347,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B26" t="n">
-        <v>105565</v>
+        <v>106037</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,29 +3404,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R26" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3469,7 +3460,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3487,27 +3478,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B27" t="n">
-        <v>106031</v>
+        <v>105571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3515,20 +3506,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R27" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,37 +3700,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295616</v>
+        <v>127295511</v>
       </c>
       <c r="B29" t="n">
-        <v>98414</v>
+        <v>105571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705528</v>
+        <v>705371</v>
       </c>
       <c r="R29" t="n">
-        <v>6396664</v>
+        <v>6396787</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,6 +3782,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3793,7 +3798,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3811,37 +3816,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295511</v>
+        <v>127295616</v>
       </c>
       <c r="B30" t="n">
-        <v>105565</v>
+        <v>98420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3855,13 +3860,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705371</v>
+        <v>705528</v>
       </c>
       <c r="R30" t="n">
-        <v>6396787</v>
+        <v>6396664</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,11 +3898,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minsta antal. Vid granrot.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3927,57 +3927,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127296628</v>
+        <v>127295486</v>
       </c>
       <c r="B31" t="n">
-        <v>43059</v>
+        <v>105571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101260</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3986,13 +3971,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705369</v>
+        <v>705414</v>
       </c>
       <c r="R31" t="n">
-        <v>6396695</v>
+        <v>6396806</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4035,7 +4020,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4053,10 +4038,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295486</v>
+        <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4083,7 +4068,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4097,13 +4082,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>705414</v>
+        <v>705483</v>
       </c>
       <c r="R32" t="n">
-        <v>6396806</v>
+        <v>6396749</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4164,42 +4149,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295482</v>
+        <v>127296628</v>
       </c>
       <c r="B33" t="n">
-        <v>105565</v>
+        <v>43059</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>671</v>
+        <v>101260</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705483</v>
+        <v>705369</v>
       </c>
       <c r="R33" t="n">
-        <v>6396749</v>
+        <v>6396695</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>127295550</v>
       </c>
       <c r="B36" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>127295520</v>
       </c>
       <c r="B37" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>127295553</v>
       </c>
       <c r="B38" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>127295510</v>
       </c>
       <c r="B39" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>127295499</v>
       </c>
       <c r="B40" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>127295485</v>
       </c>
       <c r="B41" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>127295478</v>
       </c>
       <c r="B42" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105565</v>
+        <v>105571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5643,37 +5643,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295512</v>
+        <v>127295479</v>
       </c>
       <c r="B46" t="n">
-        <v>98414</v>
+        <v>105571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705380</v>
+        <v>705482</v>
       </c>
       <c r="R46" t="n">
-        <v>6396786</v>
+        <v>6396736</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5757,7 +5757,7 @@
         <v>127295531</v>
       </c>
       <c r="B47" t="n">
-        <v>106275</v>
+        <v>106281</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295479</v>
+        <v>127295512</v>
       </c>
       <c r="B48" t="n">
-        <v>105565</v>
+        <v>98420</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5900,13 +5900,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705482</v>
+        <v>705380</v>
       </c>
       <c r="R48" t="n">
-        <v>6396736</v>
+        <v>6396786</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127016698</v>
+        <v>127016376</v>
       </c>
       <c r="B7" t="n">
-        <v>106281</v>
+        <v>57578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,31 +1287,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221903</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1315,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>705426</v>
+        <v>705342</v>
       </c>
       <c r="R7" t="n">
-        <v>6396735</v>
+        <v>6396842</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,12 +1345,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,7 +1359,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1382,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127016376</v>
+        <v>127016698</v>
       </c>
       <c r="B8" t="n">
-        <v>57578</v>
+        <v>106281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,27 +1388,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>221903</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1421,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705342</v>
+        <v>705426</v>
       </c>
       <c r="R8" t="n">
-        <v>6396842</v>
+        <v>6396735</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,12 +1450,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,6 +1464,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1801,27 +1801,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295536</v>
+        <v>127295472</v>
       </c>
       <c r="B12" t="n">
-        <v>106281</v>
+        <v>105571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,20 +1829,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705357</v>
+        <v>705521</v>
       </c>
       <c r="R12" t="n">
-        <v>6396670</v>
+        <v>6396665</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,6 +1883,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Röse 10 m V.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1885,7 +1899,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1903,7 +1917,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295472</v>
+        <v>127295515</v>
       </c>
       <c r="B13" t="n">
         <v>105571</v>
@@ -1933,12 +1947,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1947,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705521</v>
+        <v>705366</v>
       </c>
       <c r="R13" t="n">
-        <v>6396665</v>
+        <v>6396780</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Röse 10 m V.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +2015,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2019,7 +2033,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295515</v>
+        <v>127295474</v>
       </c>
       <c r="B14" t="n">
         <v>105571</v>
@@ -2049,12 +2063,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2063,13 +2077,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705366</v>
+        <v>705499</v>
       </c>
       <c r="R14" t="n">
-        <v>6396780</v>
+        <v>6396683</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,11 +2115,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2117,7 +2126,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2135,27 +2144,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295474</v>
+        <v>127295536</v>
       </c>
       <c r="B15" t="n">
-        <v>105571</v>
+        <v>106281</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2163,29 +2172,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705499</v>
+        <v>705357</v>
       </c>
       <c r="R15" t="n">
-        <v>6396683</v>
+        <v>6396670</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2806,37 +2806,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295514</v>
+        <v>127295527</v>
       </c>
       <c r="B21" t="n">
-        <v>98420</v>
+        <v>105571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705366</v>
+        <v>705395</v>
       </c>
       <c r="R21" t="n">
-        <v>6396780</v>
+        <v>6396678</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2888,6 +2888,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Just N sten.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2904,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2917,7 +2922,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295527</v>
+        <v>127295501</v>
       </c>
       <c r="B22" t="n">
         <v>105571</v>
@@ -2947,12 +2952,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2961,13 +2966,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705395</v>
+        <v>705351</v>
       </c>
       <c r="R22" t="n">
-        <v>6396678</v>
+        <v>6396798</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3001,7 +3006,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Just N sten.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,7 +3020,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3033,42 +3038,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295501</v>
+        <v>127295514</v>
       </c>
       <c r="B23" t="n">
-        <v>105571</v>
+        <v>98420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3077,13 +3082,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>705351</v>
+        <v>705366</v>
       </c>
       <c r="R23" t="n">
-        <v>6396798</v>
+        <v>6396780</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,11 +3118,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>106037</v>
+        <v>105571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,20 +3404,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R26" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,7 +3469,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3478,27 +3487,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>105571</v>
+        <v>106037</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3506,29 +3515,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R27" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127016376</v>
+        <v>127016698</v>
       </c>
       <c r="B7" t="n">
-        <v>57578</v>
+        <v>106282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,27 +1287,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>221903</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1315,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>705342</v>
+        <v>705426</v>
       </c>
       <c r="R7" t="n">
-        <v>6396842</v>
+        <v>6396735</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,12 +1349,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1363,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1377,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127016698</v>
+        <v>127016376</v>
       </c>
       <c r="B8" t="n">
-        <v>106281</v>
+        <v>57578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,31 +1393,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221903</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1420,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705426</v>
+        <v>705342</v>
       </c>
       <c r="R8" t="n">
-        <v>6396735</v>
+        <v>6396842</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,12 +1451,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1465,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>127016863</v>
       </c>
       <c r="B10" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,27 +1801,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295472</v>
+        <v>127295490</v>
       </c>
       <c r="B12" t="n">
-        <v>105571</v>
+        <v>109267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705521</v>
+        <v>705332</v>
       </c>
       <c r="R12" t="n">
-        <v>6396665</v>
+        <v>6396980</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Röse 10 m V.</t>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1917,27 +1917,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295515</v>
+        <v>127295536</v>
       </c>
       <c r="B13" t="n">
-        <v>105571</v>
+        <v>106282</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1945,29 +1945,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705366</v>
+        <v>705357</v>
       </c>
       <c r="R13" t="n">
-        <v>6396780</v>
+        <v>6396670</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,11 +1990,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2015,7 +2001,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2033,37 +2019,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295474</v>
+        <v>127295507</v>
       </c>
       <c r="B14" t="n">
-        <v>105571</v>
+        <v>98421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2077,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705499</v>
+        <v>705371</v>
       </c>
       <c r="R14" t="n">
-        <v>6396683</v>
+        <v>6396780</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2112,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2144,27 +2130,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295536</v>
+        <v>127295472</v>
       </c>
       <c r="B15" t="n">
-        <v>106281</v>
+        <v>105572</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2172,20 +2158,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705357</v>
+        <v>705521</v>
       </c>
       <c r="R15" t="n">
-        <v>6396670</v>
+        <v>6396665</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2217,6 +2212,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Röse 10 m V.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2246,42 +2246,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295507</v>
+        <v>127295515</v>
       </c>
       <c r="B16" t="n">
-        <v>98420</v>
+        <v>105572</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705371</v>
+        <v>705366</v>
       </c>
       <c r="R16" t="n">
         <v>6396780</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,6 +2328,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minsta antal. Mot ny myrstack.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2339,7 +2344,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2357,27 +2362,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295490</v>
+        <v>127295474</v>
       </c>
       <c r="B17" t="n">
-        <v>109266</v>
+        <v>105572</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2387,7 +2392,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2401,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705332</v>
+        <v>705499</v>
       </c>
       <c r="R17" t="n">
-        <v>6396980</v>
+        <v>6396683</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,11 +2444,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2476,7 +2476,7 @@
         <v>127295476</v>
       </c>
       <c r="B18" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127295477</v>
       </c>
       <c r="B19" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,37 +2806,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295527</v>
+        <v>127295514</v>
       </c>
       <c r="B21" t="n">
-        <v>105571</v>
+        <v>98421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705395</v>
+        <v>705366</v>
       </c>
       <c r="R21" t="n">
-        <v>6396678</v>
+        <v>6396780</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2888,11 +2888,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Just N sten.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2904,7 +2899,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2922,10 +2917,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295501</v>
+        <v>127295527</v>
       </c>
       <c r="B22" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,12 +2947,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2966,13 +2961,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705351</v>
+        <v>705395</v>
       </c>
       <c r="R22" t="n">
-        <v>6396798</v>
+        <v>6396678</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,7 +3001,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Just N sten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3038,42 +3033,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295514</v>
+        <v>127295501</v>
       </c>
       <c r="B23" t="n">
-        <v>98420</v>
+        <v>105572</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3082,13 +3077,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>705366</v>
+        <v>705351</v>
       </c>
       <c r="R23" t="n">
-        <v>6396780</v>
+        <v>6396798</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3118,6 +3113,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,7 +3152,7 @@
         <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B26" t="n">
-        <v>105571</v>
+        <v>106038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,29 +3404,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R26" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3469,7 +3460,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3487,27 +3478,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B27" t="n">
-        <v>106037</v>
+        <v>105572</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3515,20 +3506,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R27" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127295511</v>
       </c>
       <c r="B29" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>127295616</v>
       </c>
       <c r="B30" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>127295486</v>
       </c>
       <c r="B31" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>127295550</v>
       </c>
       <c r="B36" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>127295520</v>
       </c>
       <c r="B37" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>127295553</v>
       </c>
       <c r="B38" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>127295510</v>
       </c>
       <c r="B39" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>127295499</v>
       </c>
       <c r="B40" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>127295485</v>
       </c>
       <c r="B41" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>127295478</v>
       </c>
       <c r="B42" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105571</v>
+        <v>105572</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5643,27 +5643,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295479</v>
+        <v>127295531</v>
       </c>
       <c r="B46" t="n">
-        <v>105571</v>
+        <v>106282</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5671,26 +5671,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705482</v>
+        <v>705369</v>
       </c>
       <c r="R46" t="n">
-        <v>6396736</v>
+        <v>6396695</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5736,7 +5727,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5754,48 +5745,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295531</v>
+        <v>127295512</v>
       </c>
       <c r="B47" t="n">
-        <v>106281</v>
+        <v>98421</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705369</v>
+        <v>705380</v>
       </c>
       <c r="R47" t="n">
-        <v>6396695</v>
+        <v>6396786</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295512</v>
+        <v>127295479</v>
       </c>
       <c r="B48" t="n">
-        <v>98420</v>
+        <v>105572</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5900,13 +5900,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705380</v>
+        <v>705482</v>
       </c>
       <c r="R48" t="n">
-        <v>6396786</v>
+        <v>6396736</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>106038</v>
+        <v>105572</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,20 +3404,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R26" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,7 +3469,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3478,27 +3487,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>105572</v>
+        <v>106038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3506,29 +3515,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R27" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3700,37 +3700,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295511</v>
+        <v>127295616</v>
       </c>
       <c r="B29" t="n">
-        <v>105572</v>
+        <v>98421</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705371</v>
+        <v>705528</v>
       </c>
       <c r="R29" t="n">
-        <v>6396787</v>
+        <v>6396664</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,11 +3782,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minsta antal. Vid granrot.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3798,7 +3793,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3816,37 +3811,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295616</v>
+        <v>127295511</v>
       </c>
       <c r="B30" t="n">
-        <v>98421</v>
+        <v>105572</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3860,13 +3855,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705528</v>
+        <v>705371</v>
       </c>
       <c r="R30" t="n">
-        <v>6396664</v>
+        <v>6396787</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,6 +3893,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295490</v>
+        <v>127295536</v>
       </c>
       <c r="B12" t="n">
-        <v>109267</v>
+        <v>106282</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1812,16 +1812,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,29 +1829,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705332</v>
+        <v>705357</v>
       </c>
       <c r="R12" t="n">
-        <v>6396980</v>
+        <v>6396670</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,11 +1874,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1899,7 +1885,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1917,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295536</v>
+        <v>127295490</v>
       </c>
       <c r="B13" t="n">
-        <v>106282</v>
+        <v>109267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,16 +1914,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1945,20 +1931,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705357</v>
+        <v>705332</v>
       </c>
       <c r="R13" t="n">
-        <v>6396670</v>
+        <v>6396980</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,6 +1985,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2019,37 +2019,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295507</v>
+        <v>127295472</v>
       </c>
       <c r="B14" t="n">
-        <v>98421</v>
+        <v>105572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705371</v>
+        <v>705521</v>
       </c>
       <c r="R14" t="n">
-        <v>6396780</v>
+        <v>6396665</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,6 +2101,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Röse 10 m V.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2112,7 +2117,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2130,7 +2135,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295472</v>
+        <v>127295515</v>
       </c>
       <c r="B15" t="n">
         <v>105572</v>
@@ -2160,12 +2165,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2174,13 +2179,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705521</v>
+        <v>705366</v>
       </c>
       <c r="R15" t="n">
-        <v>6396665</v>
+        <v>6396780</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2219,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Röse 10 m V.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,7 +2233,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2246,7 +2251,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295515</v>
+        <v>127295474</v>
       </c>
       <c r="B16" t="n">
         <v>105572</v>
@@ -2276,12 +2281,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2290,13 +2295,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705366</v>
+        <v>705499</v>
       </c>
       <c r="R16" t="n">
-        <v>6396780</v>
+        <v>6396683</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,11 +2333,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2362,37 +2362,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295474</v>
+        <v>127295507</v>
       </c>
       <c r="B17" t="n">
-        <v>105572</v>
+        <v>98421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705499</v>
+        <v>705371</v>
       </c>
       <c r="R17" t="n">
-        <v>6396683</v>
+        <v>6396780</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B26" t="n">
-        <v>105572</v>
+        <v>106038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,29 +3404,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R26" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3469,7 +3460,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3487,27 +3478,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B27" t="n">
-        <v>106038</v>
+        <v>105572</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3515,20 +3506,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R27" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3700,37 +3700,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295616</v>
+        <v>127295511</v>
       </c>
       <c r="B29" t="n">
-        <v>98421</v>
+        <v>105572</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705528</v>
+        <v>705371</v>
       </c>
       <c r="R29" t="n">
-        <v>6396664</v>
+        <v>6396787</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,6 +3782,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3793,7 +3798,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3811,37 +3816,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295511</v>
+        <v>127295616</v>
       </c>
       <c r="B30" t="n">
-        <v>105572</v>
+        <v>98421</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3855,13 +3860,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705371</v>
+        <v>705528</v>
       </c>
       <c r="R30" t="n">
-        <v>6396787</v>
+        <v>6396664</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,11 +3898,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minsta antal. Vid granrot.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5643,27 +5643,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295531</v>
+        <v>127295479</v>
       </c>
       <c r="B46" t="n">
-        <v>106282</v>
+        <v>105572</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5671,17 +5671,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705369</v>
+        <v>705482</v>
       </c>
       <c r="R46" t="n">
-        <v>6396695</v>
+        <v>6396736</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5727,7 +5736,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5745,57 +5754,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295512</v>
+        <v>127295531</v>
       </c>
       <c r="B47" t="n">
-        <v>98421</v>
+        <v>106282</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705380</v>
+        <v>705369</v>
       </c>
       <c r="R47" t="n">
-        <v>6396786</v>
+        <v>6396695</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295479</v>
+        <v>127295512</v>
       </c>
       <c r="B48" t="n">
-        <v>105572</v>
+        <v>98421</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5900,13 +5900,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705482</v>
+        <v>705380</v>
       </c>
       <c r="R48" t="n">
-        <v>6396736</v>
+        <v>6396786</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1903,37 +1903,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295490</v>
+        <v>127295507</v>
       </c>
       <c r="B13" t="n">
-        <v>109267</v>
+        <v>98421</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705332</v>
+        <v>705371</v>
       </c>
       <c r="R13" t="n">
-        <v>6396980</v>
+        <v>6396780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,11 +1983,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,27 +2014,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295472</v>
+        <v>127295490</v>
       </c>
       <c r="B14" t="n">
-        <v>105572</v>
+        <v>109267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>671</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2049,7 +2044,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2063,13 +2058,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705521</v>
+        <v>705332</v>
       </c>
       <c r="R14" t="n">
-        <v>6396665</v>
+        <v>6396980</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,7 +2098,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Röse 10 m V.</t>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2112,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2135,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295515</v>
+        <v>127295472</v>
       </c>
       <c r="B15" t="n">
         <v>105572</v>
@@ -2165,12 +2160,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2179,13 +2174,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705366</v>
+        <v>705521</v>
       </c>
       <c r="R15" t="n">
-        <v>6396780</v>
+        <v>6396665</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,7 +2214,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
+          <t>Röse 10 m V.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,7 +2228,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2251,7 +2246,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295474</v>
+        <v>127295515</v>
       </c>
       <c r="B16" t="n">
         <v>105572</v>
@@ -2281,12 +2276,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2295,13 +2290,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705499</v>
+        <v>705366</v>
       </c>
       <c r="R16" t="n">
-        <v>6396683</v>
+        <v>6396780</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2333,6 +2328,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minsta antal. Mot ny myrstack.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2362,37 +2362,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295507</v>
+        <v>127295474</v>
       </c>
       <c r="B17" t="n">
-        <v>98421</v>
+        <v>105572</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705371</v>
+        <v>705499</v>
       </c>
       <c r="R17" t="n">
-        <v>6396780</v>
+        <v>6396683</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B24" t="n">
-        <v>105572</v>
+        <v>98421</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R24" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,11 +3231,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3247,7 +3242,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3265,37 +3260,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B25" t="n">
-        <v>98421</v>
+        <v>105572</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3309,13 +3304,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R25" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3347,6 +3342,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>106038</v>
+        <v>105572</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,20 +3404,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R26" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,7 +3469,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3478,27 +3487,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>105572</v>
+        <v>106038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3506,29 +3515,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R27" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1903,37 +1903,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295507</v>
+        <v>127295490</v>
       </c>
       <c r="B13" t="n">
-        <v>98421</v>
+        <v>109267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705371</v>
+        <v>705332</v>
       </c>
       <c r="R13" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,6 +1983,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,27 +2019,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295490</v>
+        <v>127295472</v>
       </c>
       <c r="B14" t="n">
-        <v>109267</v>
+        <v>105572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2044,7 +2049,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2058,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705332</v>
+        <v>705521</v>
       </c>
       <c r="R14" t="n">
-        <v>6396980</v>
+        <v>6396665</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Röse 10 m V.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,7 +2117,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2130,7 +2135,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295472</v>
+        <v>127295515</v>
       </c>
       <c r="B15" t="n">
         <v>105572</v>
@@ -2160,12 +2165,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2174,13 +2179,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705521</v>
+        <v>705366</v>
       </c>
       <c r="R15" t="n">
-        <v>6396665</v>
+        <v>6396780</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2219,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Röse 10 m V.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,7 +2233,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2246,7 +2251,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295515</v>
+        <v>127295474</v>
       </c>
       <c r="B16" t="n">
         <v>105572</v>
@@ -2276,12 +2281,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2290,13 +2295,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705366</v>
+        <v>705499</v>
       </c>
       <c r="R16" t="n">
-        <v>6396780</v>
+        <v>6396683</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,11 +2333,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2362,37 +2362,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295474</v>
+        <v>127295507</v>
       </c>
       <c r="B17" t="n">
-        <v>105572</v>
+        <v>98421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705499</v>
+        <v>705371</v>
       </c>
       <c r="R17" t="n">
-        <v>6396683</v>
+        <v>6396780</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>98421</v>
+        <v>105572</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R24" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,6 +3231,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3242,7 +3247,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,37 +3265,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>105572</v>
+        <v>98421</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3304,13 +3309,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R25" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,11 +3347,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3700,37 +3700,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295511</v>
+        <v>127295616</v>
       </c>
       <c r="B29" t="n">
-        <v>105572</v>
+        <v>98421</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705371</v>
+        <v>705528</v>
       </c>
       <c r="R29" t="n">
-        <v>6396787</v>
+        <v>6396664</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,11 +3782,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minsta antal. Vid granrot.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3798,7 +3793,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3816,37 +3811,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295616</v>
+        <v>127295511</v>
       </c>
       <c r="B30" t="n">
-        <v>98421</v>
+        <v>105572</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3860,13 +3855,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705528</v>
+        <v>705371</v>
       </c>
       <c r="R30" t="n">
-        <v>6396664</v>
+        <v>6396787</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,6 +3893,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -6067,6 +6067,228 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127534911</v>
+      </c>
+      <c r="B50" t="n">
+        <v>105578</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>671</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>705412</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6396771</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Svårt att bestämma exakt antal individer, stort bestånd utspridda på hela området runikring. Antalet är en uppskattning och siffran är troligen ännu högre. Somliga unga individer, somliga överblommade eller med knopp</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Hanna Wallin</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Hanna Wallin</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127544907</v>
+      </c>
+      <c r="B51" t="n">
+        <v>105578</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>671</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Ytlings norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>705297</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6396906</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Unga exemplar i upptorkat dike</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Hanna Wallin</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Hanna Wallin</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127016698</v>
+        <v>127016376</v>
       </c>
       <c r="B7" t="n">
-        <v>106282</v>
+        <v>57582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,31 +1287,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221903</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1315,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>705426</v>
+        <v>705342</v>
       </c>
       <c r="R7" t="n">
-        <v>6396735</v>
+        <v>6396842</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,12 +1345,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,7 +1359,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1382,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127016376</v>
+        <v>127016698</v>
       </c>
       <c r="B8" t="n">
-        <v>57578</v>
+        <v>106288</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,27 +1388,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>221903</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1421,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705342</v>
+        <v>705426</v>
       </c>
       <c r="R8" t="n">
-        <v>6396842</v>
+        <v>6396735</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,12 +1450,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,6 +1464,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>127016538</v>
       </c>
       <c r="B9" t="n">
-        <v>57578</v>
+        <v>57582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127016863</v>
       </c>
       <c r="B10" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,27 +1801,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295536</v>
+        <v>127295472</v>
       </c>
       <c r="B12" t="n">
-        <v>106282</v>
+        <v>105578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,20 +1829,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705357</v>
+        <v>705521</v>
       </c>
       <c r="R12" t="n">
-        <v>6396670</v>
+        <v>6396665</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,6 +1883,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Röse 10 m V.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1885,7 +1899,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1903,27 +1917,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295490</v>
+        <v>127295515</v>
       </c>
       <c r="B13" t="n">
-        <v>109267</v>
+        <v>105578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1933,12 +1947,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1947,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705332</v>
+        <v>705366</v>
       </c>
       <c r="R13" t="n">
-        <v>6396980</v>
+        <v>6396780</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +2015,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2019,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295472</v>
+        <v>127295474</v>
       </c>
       <c r="B14" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,13 +2077,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705521</v>
+        <v>705499</v>
       </c>
       <c r="R14" t="n">
-        <v>6396665</v>
+        <v>6396683</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,11 +2113,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Röse 10 m V.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,27 +2144,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295515</v>
+        <v>127295536</v>
       </c>
       <c r="B15" t="n">
-        <v>105572</v>
+        <v>106288</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2163,29 +2172,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705366</v>
+        <v>705357</v>
       </c>
       <c r="R15" t="n">
-        <v>6396780</v>
+        <v>6396670</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2217,11 +2217,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2233,7 +2228,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2251,37 +2246,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295474</v>
+        <v>127295507</v>
       </c>
       <c r="B16" t="n">
-        <v>105572</v>
+        <v>98425</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2295,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705499</v>
+        <v>705371</v>
       </c>
       <c r="R16" t="n">
-        <v>6396683</v>
+        <v>6396780</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2339,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2362,37 +2357,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295507</v>
+        <v>127295490</v>
       </c>
       <c r="B17" t="n">
-        <v>98421</v>
+        <v>109273</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2406,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705371</v>
+        <v>705332</v>
       </c>
       <c r="R17" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,6 +2437,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,7 +2476,7 @@
         <v>127295476</v>
       </c>
       <c r="B18" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127295477</v>
       </c>
       <c r="B19" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,37 +2806,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295514</v>
+        <v>127295527</v>
       </c>
       <c r="B21" t="n">
-        <v>98421</v>
+        <v>105578</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705366</v>
+        <v>705395</v>
       </c>
       <c r="R21" t="n">
-        <v>6396780</v>
+        <v>6396678</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2888,6 +2888,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Just N sten.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2904,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2917,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295527</v>
+        <v>127295501</v>
       </c>
       <c r="B22" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2947,12 +2952,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2961,13 +2966,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705395</v>
+        <v>705351</v>
       </c>
       <c r="R22" t="n">
-        <v>6396678</v>
+        <v>6396798</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3001,7 +3006,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Just N sten.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,7 +3020,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3033,42 +3038,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295501</v>
+        <v>127295514</v>
       </c>
       <c r="B23" t="n">
-        <v>105572</v>
+        <v>98425</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3077,13 +3082,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>705351</v>
+        <v>705366</v>
       </c>
       <c r="R23" t="n">
-        <v>6396798</v>
+        <v>6396780</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,11 +3118,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,7 +3152,7 @@
         <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B26" t="n">
-        <v>105572</v>
+        <v>106044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,29 +3404,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R26" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3469,7 +3460,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3487,27 +3478,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B27" t="n">
-        <v>106038</v>
+        <v>105578</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3515,20 +3506,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R27" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,37 +3700,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295616</v>
+        <v>127295511</v>
       </c>
       <c r="B29" t="n">
-        <v>98421</v>
+        <v>105578</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705528</v>
+        <v>705371</v>
       </c>
       <c r="R29" t="n">
-        <v>6396664</v>
+        <v>6396787</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,6 +3782,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3793,7 +3798,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3811,37 +3816,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295511</v>
+        <v>127295616</v>
       </c>
       <c r="B30" t="n">
-        <v>105572</v>
+        <v>98425</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3855,13 +3860,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705371</v>
+        <v>705528</v>
       </c>
       <c r="R30" t="n">
-        <v>6396787</v>
+        <v>6396664</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,11 +3898,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minsta antal. Vid granrot.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3930,7 +3930,7 @@
         <v>127295486</v>
       </c>
       <c r="B31" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>127296628</v>
       </c>
       <c r="B33" t="n">
-        <v>43059</v>
+        <v>43063</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>127295550</v>
       </c>
       <c r="B36" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>127295520</v>
       </c>
       <c r="B37" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>127295553</v>
       </c>
       <c r="B38" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>127295510</v>
       </c>
       <c r="B39" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>127295499</v>
       </c>
       <c r="B40" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>127295485</v>
       </c>
       <c r="B41" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>127295478</v>
       </c>
       <c r="B42" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105572</v>
+        <v>105578</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5643,37 +5643,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295479</v>
+        <v>127295512</v>
       </c>
       <c r="B46" t="n">
-        <v>105572</v>
+        <v>98425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705482</v>
+        <v>705380</v>
       </c>
       <c r="R46" t="n">
-        <v>6396736</v>
+        <v>6396786</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5757,7 +5757,7 @@
         <v>127295531</v>
       </c>
       <c r="B47" t="n">
-        <v>106282</v>
+        <v>106288</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295512</v>
+        <v>127295479</v>
       </c>
       <c r="B48" t="n">
-        <v>98421</v>
+        <v>105578</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5900,13 +5900,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705380</v>
+        <v>705482</v>
       </c>
       <c r="R48" t="n">
-        <v>6396786</v>
+        <v>6396736</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127016376</v>
+        <v>127016698</v>
       </c>
       <c r="B7" t="n">
-        <v>57582</v>
+        <v>106288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,27 +1287,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>221903</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1315,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>705342</v>
+        <v>705426</v>
       </c>
       <c r="R7" t="n">
-        <v>6396842</v>
+        <v>6396735</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,12 +1349,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1363,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1377,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127016698</v>
+        <v>127016376</v>
       </c>
       <c r="B8" t="n">
-        <v>106288</v>
+        <v>57582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,31 +1393,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221903</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1420,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705426</v>
+        <v>705342</v>
       </c>
       <c r="R8" t="n">
-        <v>6396735</v>
+        <v>6396842</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,12 +1451,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1465,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2144,48 +2144,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295536</v>
+        <v>127295507</v>
       </c>
       <c r="B15" t="n">
-        <v>106288</v>
+        <v>98425</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705357</v>
+        <v>705371</v>
       </c>
       <c r="R15" t="n">
-        <v>6396670</v>
+        <v>6396780</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2237,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2246,57 +2255,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295507</v>
+        <v>127295536</v>
       </c>
       <c r="B16" t="n">
-        <v>98425</v>
+        <v>106288</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705371</v>
+        <v>705357</v>
       </c>
       <c r="R16" t="n">
-        <v>6396780</v>
+        <v>6396670</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>106044</v>
+        <v>105578</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,20 +3404,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R26" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,7 +3469,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3478,27 +3487,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>105578</v>
+        <v>106044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3506,29 +3515,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R27" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3927,42 +3927,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295486</v>
+        <v>127296628</v>
       </c>
       <c r="B31" t="n">
-        <v>105578</v>
+        <v>43063</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>101260</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3971,13 +3986,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705414</v>
+        <v>705369</v>
       </c>
       <c r="R31" t="n">
-        <v>6396806</v>
+        <v>6396695</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4020,7 +4035,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4038,7 +4053,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295482</v>
+        <v>127295486</v>
       </c>
       <c r="B32" t="n">
         <v>105578</v>
@@ -4068,7 +4083,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4082,13 +4097,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>705483</v>
+        <v>705414</v>
       </c>
       <c r="R32" t="n">
-        <v>6396749</v>
+        <v>6396806</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4149,57 +4164,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127296628</v>
+        <v>127295482</v>
       </c>
       <c r="B33" t="n">
-        <v>43063</v>
+        <v>105578</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101260</v>
+        <v>671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705369</v>
+        <v>705483</v>
       </c>
       <c r="R33" t="n">
-        <v>6396695</v>
+        <v>6396749</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5643,37 +5643,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295512</v>
+        <v>127295479</v>
       </c>
       <c r="B46" t="n">
-        <v>98425</v>
+        <v>105578</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705380</v>
+        <v>705482</v>
       </c>
       <c r="R46" t="n">
-        <v>6396786</v>
+        <v>6396736</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5754,48 +5754,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295531</v>
+        <v>127295512</v>
       </c>
       <c r="B47" t="n">
-        <v>106288</v>
+        <v>98425</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705369</v>
+        <v>705380</v>
       </c>
       <c r="R47" t="n">
-        <v>6396695</v>
+        <v>6396786</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5838,7 +5847,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5856,27 +5865,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295479</v>
+        <v>127295531</v>
       </c>
       <c r="B48" t="n">
-        <v>105578</v>
+        <v>106288</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5884,26 +5893,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705482</v>
+        <v>705369</v>
       </c>
       <c r="R48" t="n">
-        <v>6396736</v>
+        <v>6396695</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1801,27 +1801,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295472</v>
+        <v>127295536</v>
       </c>
       <c r="B12" t="n">
-        <v>105578</v>
+        <v>106288</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,29 +1829,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705521</v>
+        <v>705357</v>
       </c>
       <c r="R12" t="n">
-        <v>6396665</v>
+        <v>6396670</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,11 +1874,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Röse 10 m V.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1899,7 +1885,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1917,27 +1903,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295515</v>
+        <v>127295490</v>
       </c>
       <c r="B13" t="n">
-        <v>105578</v>
+        <v>109273</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>671</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1947,12 +1933,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1961,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705366</v>
+        <v>705332</v>
       </c>
       <c r="R13" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,7 +1987,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,7 +2001,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2033,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295474</v>
+        <v>127295472</v>
       </c>
       <c r="B14" t="n">
         <v>105578</v>
@@ -2077,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705499</v>
+        <v>705521</v>
       </c>
       <c r="R14" t="n">
-        <v>6396683</v>
+        <v>6396665</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2113,6 +2099,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Röse 10 m V.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,42 +2135,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295507</v>
+        <v>127295515</v>
       </c>
       <c r="B15" t="n">
-        <v>98425</v>
+        <v>105578</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2188,13 +2179,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705371</v>
+        <v>705366</v>
       </c>
       <c r="R15" t="n">
         <v>6396780</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,6 +2217,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minsta antal. Mot ny myrstack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2237,7 +2233,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2255,27 +2251,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295536</v>
+        <v>127295474</v>
       </c>
       <c r="B16" t="n">
-        <v>106288</v>
+        <v>105578</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2283,20 +2279,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705357</v>
+        <v>705499</v>
       </c>
       <c r="R16" t="n">
-        <v>6396670</v>
+        <v>6396683</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2339,7 +2344,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2357,37 +2362,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295490</v>
+        <v>127295507</v>
       </c>
       <c r="B17" t="n">
-        <v>109273</v>
+        <v>98425</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2401,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705332</v>
+        <v>705371</v>
       </c>
       <c r="R17" t="n">
-        <v>6396980</v>
+        <v>6396780</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,11 +2442,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B24" t="n">
-        <v>105578</v>
+        <v>98425</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R24" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,11 +3231,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3247,7 +3242,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3265,37 +3260,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B25" t="n">
-        <v>98425</v>
+        <v>105578</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3309,13 +3304,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R25" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3347,6 +3342,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4730,7 +4730,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295553</v>
+        <v>127295510</v>
       </c>
       <c r="B38" t="n">
         <v>105578</v>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>705399</v>
+        <v>705381</v>
       </c>
       <c r="R38" t="n">
-        <v>6396595</v>
+        <v>6396796</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295510</v>
+        <v>127295553</v>
       </c>
       <c r="B39" t="n">
         <v>105578</v>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>705381</v>
+        <v>705399</v>
       </c>
       <c r="R39" t="n">
-        <v>6396796</v>
+        <v>6396595</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B26" t="n">
-        <v>105578</v>
+        <v>106044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,29 +3404,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R26" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3469,7 +3460,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3487,27 +3478,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B27" t="n">
-        <v>106044</v>
+        <v>105578</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3515,20 +3506,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R27" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127016698</v>
+        <v>127016376</v>
       </c>
       <c r="B7" t="n">
-        <v>106288</v>
+        <v>57582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,31 +1287,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221903</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1315,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>705426</v>
+        <v>705342</v>
       </c>
       <c r="R7" t="n">
-        <v>6396735</v>
+        <v>6396842</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,12 +1345,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,7 +1359,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1382,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127016376</v>
+        <v>127016698</v>
       </c>
       <c r="B8" t="n">
-        <v>57582</v>
+        <v>106290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,27 +1388,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>221903</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1421,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705342</v>
+        <v>705426</v>
       </c>
       <c r="R8" t="n">
-        <v>6396842</v>
+        <v>6396735</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,12 +1450,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,6 +1464,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>127016863</v>
       </c>
       <c r="B10" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,27 +1801,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295536</v>
+        <v>127295474</v>
       </c>
       <c r="B12" t="n">
-        <v>106288</v>
+        <v>105580</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,20 +1829,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705357</v>
+        <v>705499</v>
       </c>
       <c r="R12" t="n">
-        <v>6396670</v>
+        <v>6396683</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,7 +1894,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1903,27 +1912,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295490</v>
+        <v>127295515</v>
       </c>
       <c r="B13" t="n">
-        <v>109273</v>
+        <v>105580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1933,12 +1942,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1947,13 +1956,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705332</v>
+        <v>705366</v>
       </c>
       <c r="R13" t="n">
-        <v>6396980</v>
+        <v>6396780</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +2010,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2022,7 +2031,7 @@
         <v>127295472</v>
       </c>
       <c r="B14" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,42 +2144,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295515</v>
+        <v>127295507</v>
       </c>
       <c r="B15" t="n">
-        <v>105578</v>
+        <v>98426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2179,13 +2188,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705366</v>
+        <v>705371</v>
       </c>
       <c r="R15" t="n">
         <v>6396780</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2217,11 +2226,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2233,7 +2237,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2251,27 +2255,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295474</v>
+        <v>127295490</v>
       </c>
       <c r="B16" t="n">
-        <v>105578</v>
+        <v>109275</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>671</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2281,7 +2285,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2295,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705499</v>
+        <v>705332</v>
       </c>
       <c r="R16" t="n">
-        <v>6396683</v>
+        <v>6396980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,6 +2337,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2344,7 +2353,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2362,57 +2371,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295507</v>
+        <v>127295536</v>
       </c>
       <c r="B17" t="n">
-        <v>98425</v>
+        <v>106290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705371</v>
+        <v>705357</v>
       </c>
       <c r="R17" t="n">
-        <v>6396780</v>
+        <v>6396670</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295476</v>
+        <v>127295477</v>
       </c>
       <c r="B18" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>705490</v>
       </c>
       <c r="R18" t="n">
-        <v>6396722</v>
+        <v>6396728</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, vid myrstig nära granar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127295477</v>
+        <v>127295476</v>
       </c>
       <c r="B19" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,7 +2631,7 @@
         <v>705490</v>
       </c>
       <c r="R19" t="n">
-        <v>6396728</v>
+        <v>6396722</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, vid myrstig nära granar.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295527</v>
+        <v>127295501</v>
       </c>
       <c r="B21" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705395</v>
+        <v>705351</v>
       </c>
       <c r="R21" t="n">
-        <v>6396678</v>
+        <v>6396798</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Just N sten.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295501</v>
+        <v>127295527</v>
       </c>
       <c r="B22" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,12 +2952,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705351</v>
+        <v>705395</v>
       </c>
       <c r="R22" t="n">
-        <v>6396798</v>
+        <v>6396678</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Just N sten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>127295514</v>
       </c>
       <c r="B23" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>98425</v>
+        <v>105580</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R24" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,6 +3231,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3242,7 +3247,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,37 +3265,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>105578</v>
+        <v>98426</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3304,13 +3309,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R25" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,11 +3347,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>106044</v>
+        <v>105580</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,20 +3404,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R26" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,7 +3469,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3478,27 +3487,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>105578</v>
+        <v>106046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3506,29 +3515,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R27" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,37 +3700,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295511</v>
+        <v>127295616</v>
       </c>
       <c r="B29" t="n">
-        <v>105578</v>
+        <v>98426</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705371</v>
+        <v>705528</v>
       </c>
       <c r="R29" t="n">
-        <v>6396787</v>
+        <v>6396664</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,11 +3782,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minsta antal. Vid granrot.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3798,7 +3793,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3816,37 +3811,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295616</v>
+        <v>127295511</v>
       </c>
       <c r="B30" t="n">
-        <v>98425</v>
+        <v>105580</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3860,13 +3855,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705528</v>
+        <v>705371</v>
       </c>
       <c r="R30" t="n">
-        <v>6396664</v>
+        <v>6396787</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,6 +3893,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295486</v>
+        <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4097,13 +4097,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>705414</v>
+        <v>705483</v>
       </c>
       <c r="R32" t="n">
-        <v>6396806</v>
+        <v>6396749</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295482</v>
+        <v>127295486</v>
       </c>
       <c r="B33" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705483</v>
+        <v>705414</v>
       </c>
       <c r="R33" t="n">
-        <v>6396749</v>
+        <v>6396806</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295550</v>
+        <v>127295520</v>
       </c>
       <c r="B36" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>705402</v>
+        <v>705389</v>
       </c>
       <c r="R36" t="n">
-        <v>6396607</v>
+        <v>6396765</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex.</t>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295520</v>
+        <v>127295550</v>
       </c>
       <c r="B37" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>705389</v>
+        <v>705402</v>
       </c>
       <c r="R37" t="n">
-        <v>6396765</v>
+        <v>6396607</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minsta antal.</t>
+          <t>Ungefärligt antal; småex.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4733,7 +4733,7 @@
         <v>127295510</v>
       </c>
       <c r="B38" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295553</v>
+        <v>127295499</v>
       </c>
       <c r="B39" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4890,13 +4890,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>705399</v>
+        <v>705323</v>
       </c>
       <c r="R39" t="n">
-        <v>6396595</v>
+        <v>6396800</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
+          <t>Minsta antal. Nära stor dubbelgran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4962,10 +4962,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295499</v>
+        <v>127295553</v>
       </c>
       <c r="B40" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>705323</v>
+        <v>705399</v>
       </c>
       <c r="R40" t="n">
-        <v>6396800</v>
+        <v>6396595</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minsta antal. Nära stor dubbelgran.</t>
+          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295485</v>
+        <v>127295478</v>
       </c>
       <c r="B41" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>705434</v>
+        <v>705482</v>
       </c>
       <c r="R41" t="n">
-        <v>6396784</v>
+        <v>6396738</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295478</v>
+        <v>127295485</v>
       </c>
       <c r="B42" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>705482</v>
+        <v>705434</v>
       </c>
       <c r="R42" t="n">
-        <v>6396738</v>
+        <v>6396784</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5643,37 +5643,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295479</v>
+        <v>127295512</v>
       </c>
       <c r="B46" t="n">
-        <v>105578</v>
+        <v>98426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705482</v>
+        <v>705380</v>
       </c>
       <c r="R46" t="n">
-        <v>6396736</v>
+        <v>6396786</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5754,57 +5754,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295512</v>
+        <v>127295531</v>
       </c>
       <c r="B47" t="n">
-        <v>98425</v>
+        <v>106290</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705380</v>
+        <v>705369</v>
       </c>
       <c r="R47" t="n">
-        <v>6396786</v>
+        <v>6396695</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5847,7 +5838,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5865,27 +5856,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295531</v>
+        <v>127295479</v>
       </c>
       <c r="B48" t="n">
-        <v>106288</v>
+        <v>105580</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5893,17 +5884,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705369</v>
+        <v>705482</v>
       </c>
       <c r="R48" t="n">
-        <v>6396695</v>
+        <v>6396736</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>127534911</v>
       </c>
       <c r="B50" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>127544907</v>
       </c>
       <c r="B51" t="n">
-        <v>105578</v>
+        <v>105580</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -2806,42 +2806,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295501</v>
+        <v>127295514</v>
       </c>
       <c r="B21" t="n">
-        <v>105580</v>
+        <v>98426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705351</v>
+        <v>705366</v>
       </c>
       <c r="R21" t="n">
-        <v>6396798</v>
+        <v>6396780</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2886,11 +2886,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,7 +2917,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295527</v>
+        <v>127295501</v>
       </c>
       <c r="B22" t="n">
         <v>105580</v>
@@ -2952,12 +2947,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2966,13 +2961,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705395</v>
+        <v>705351</v>
       </c>
       <c r="R22" t="n">
-        <v>6396678</v>
+        <v>6396798</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,7 +3001,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Just N sten.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3038,37 +3033,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295514</v>
+        <v>127295527</v>
       </c>
       <c r="B23" t="n">
-        <v>98426</v>
+        <v>105580</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>705366</v>
+        <v>705395</v>
       </c>
       <c r="R23" t="n">
-        <v>6396780</v>
+        <v>6396678</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,6 +3115,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Just N sten.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -5643,57 +5643,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295512</v>
+        <v>127295531</v>
       </c>
       <c r="B46" t="n">
-        <v>98426</v>
+        <v>106290</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705380</v>
+        <v>705369</v>
       </c>
       <c r="R46" t="n">
-        <v>6396786</v>
+        <v>6396695</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5736,7 +5727,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5754,27 +5745,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295531</v>
+        <v>127295479</v>
       </c>
       <c r="B47" t="n">
-        <v>106290</v>
+        <v>105580</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5782,17 +5773,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705369</v>
+        <v>705482</v>
       </c>
       <c r="R47" t="n">
-        <v>6396695</v>
+        <v>6396736</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295479</v>
+        <v>127295512</v>
       </c>
       <c r="B48" t="n">
-        <v>105580</v>
+        <v>98426</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5900,13 +5900,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705482</v>
+        <v>705380</v>
       </c>
       <c r="R48" t="n">
-        <v>6396736</v>
+        <v>6396786</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1279,7 +1279,7 @@
         <v>127016376</v>
       </c>
       <c r="B7" t="n">
-        <v>57582</v>
+        <v>57584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127016698</v>
       </c>
       <c r="B8" t="n">
-        <v>106290</v>
+        <v>106292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127016538</v>
       </c>
       <c r="B9" t="n">
-        <v>57582</v>
+        <v>57584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127016863</v>
       </c>
       <c r="B10" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,37 +1801,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295474</v>
+        <v>127295507</v>
       </c>
       <c r="B12" t="n">
-        <v>105580</v>
+        <v>98428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705499</v>
+        <v>705371</v>
       </c>
       <c r="R12" t="n">
-        <v>6396683</v>
+        <v>6396780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1912,27 +1912,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295515</v>
+        <v>127295490</v>
       </c>
       <c r="B13" t="n">
-        <v>105580</v>
+        <v>109277</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>671</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1956,13 +1956,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705366</v>
+        <v>705332</v>
       </c>
       <c r="R13" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
         <v>127295472</v>
       </c>
       <c r="B14" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,42 +2144,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295507</v>
+        <v>127295515</v>
       </c>
       <c r="B15" t="n">
-        <v>98426</v>
+        <v>105582</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705371</v>
+        <v>705366</v>
       </c>
       <c r="R15" t="n">
         <v>6396780</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,6 +2226,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minsta antal. Mot ny myrstack.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2237,7 +2242,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2255,27 +2260,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295490</v>
+        <v>127295474</v>
       </c>
       <c r="B16" t="n">
-        <v>109275</v>
+        <v>105582</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2285,7 +2290,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2299,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705332</v>
+        <v>705499</v>
       </c>
       <c r="R16" t="n">
-        <v>6396980</v>
+        <v>6396683</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,11 +2342,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2374,7 +2374,7 @@
         <v>127295536</v>
       </c>
       <c r="B17" t="n">
-        <v>106290</v>
+        <v>106292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295477</v>
+        <v>127295476</v>
       </c>
       <c r="B18" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>705490</v>
       </c>
       <c r="R18" t="n">
-        <v>6396728</v>
+        <v>6396722</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, vid myrstig nära granar.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127295476</v>
+        <v>127295477</v>
       </c>
       <c r="B19" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,7 +2631,7 @@
         <v>705490</v>
       </c>
       <c r="R19" t="n">
-        <v>6396722</v>
+        <v>6396728</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, vid myrstig nära granar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,37 +2806,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295514</v>
+        <v>127295527</v>
       </c>
       <c r="B21" t="n">
-        <v>98426</v>
+        <v>105582</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705366</v>
+        <v>705395</v>
       </c>
       <c r="R21" t="n">
-        <v>6396780</v>
+        <v>6396678</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2888,6 +2888,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Just N sten.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2904,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2920,7 +2925,7 @@
         <v>127295501</v>
       </c>
       <c r="B22" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,37 +3038,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295527</v>
+        <v>127295514</v>
       </c>
       <c r="B23" t="n">
-        <v>105580</v>
+        <v>98428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>705395</v>
+        <v>705366</v>
       </c>
       <c r="R23" t="n">
-        <v>6396678</v>
+        <v>6396780</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3115,11 +3120,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Just N sten.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B24" t="n">
-        <v>105580</v>
+        <v>98428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R24" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,11 +3231,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3247,7 +3242,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3265,37 +3260,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B25" t="n">
-        <v>98426</v>
+        <v>105582</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3309,13 +3304,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R25" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3347,6 +3342,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B26" t="n">
-        <v>105580</v>
+        <v>106048</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,29 +3404,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R26" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3469,7 +3460,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3487,27 +3478,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B27" t="n">
-        <v>106046</v>
+        <v>105582</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3515,20 +3506,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R27" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,37 +3700,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295616</v>
+        <v>127295511</v>
       </c>
       <c r="B29" t="n">
-        <v>98426</v>
+        <v>105582</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705528</v>
+        <v>705371</v>
       </c>
       <c r="R29" t="n">
-        <v>6396664</v>
+        <v>6396787</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,6 +3782,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3793,7 +3798,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3811,37 +3816,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295511</v>
+        <v>127295616</v>
       </c>
       <c r="B30" t="n">
-        <v>105580</v>
+        <v>98428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3855,13 +3860,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705371</v>
+        <v>705528</v>
       </c>
       <c r="R30" t="n">
-        <v>6396787</v>
+        <v>6396664</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,11 +3898,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minsta antal. Vid granrot.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3927,57 +3927,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127296628</v>
+        <v>127295486</v>
       </c>
       <c r="B31" t="n">
-        <v>43063</v>
+        <v>105582</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101260</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3986,13 +3971,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705369</v>
+        <v>705414</v>
       </c>
       <c r="R31" t="n">
-        <v>6396695</v>
+        <v>6396806</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4035,7 +4020,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4056,7 +4041,7 @@
         <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4164,42 +4149,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295486</v>
+        <v>127296628</v>
       </c>
       <c r="B33" t="n">
-        <v>105580</v>
+        <v>43065</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>671</v>
+        <v>101260</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705414</v>
+        <v>705369</v>
       </c>
       <c r="R33" t="n">
-        <v>6396806</v>
+        <v>6396695</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295520</v>
+        <v>127295550</v>
       </c>
       <c r="B36" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>705389</v>
+        <v>705402</v>
       </c>
       <c r="R36" t="n">
-        <v>6396765</v>
+        <v>6396607</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minsta antal.</t>
+          <t>Ungefärligt antal; småex.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295550</v>
+        <v>127295520</v>
       </c>
       <c r="B37" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>705402</v>
+        <v>705389</v>
       </c>
       <c r="R37" t="n">
-        <v>6396607</v>
+        <v>6396765</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex.</t>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295510</v>
+        <v>127295553</v>
       </c>
       <c r="B38" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>705381</v>
+        <v>705399</v>
       </c>
       <c r="R38" t="n">
-        <v>6396796</v>
+        <v>6396595</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295499</v>
+        <v>127295510</v>
       </c>
       <c r="B39" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4890,13 +4890,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>705323</v>
+        <v>705381</v>
       </c>
       <c r="R39" t="n">
-        <v>6396800</v>
+        <v>6396796</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minsta antal. Nära stor dubbelgran.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4962,10 +4962,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295553</v>
+        <v>127295499</v>
       </c>
       <c r="B40" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>705399</v>
+        <v>705323</v>
       </c>
       <c r="R40" t="n">
-        <v>6396595</v>
+        <v>6396800</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
+          <t>Minsta antal. Nära stor dubbelgran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295478</v>
+        <v>127295485</v>
       </c>
       <c r="B41" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>705482</v>
+        <v>705434</v>
       </c>
       <c r="R41" t="n">
-        <v>6396738</v>
+        <v>6396784</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295485</v>
+        <v>127295478</v>
       </c>
       <c r="B42" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>705434</v>
+        <v>705482</v>
       </c>
       <c r="R42" t="n">
-        <v>6396784</v>
+        <v>6396738</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5643,27 +5643,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295531</v>
+        <v>127295479</v>
       </c>
       <c r="B46" t="n">
-        <v>106290</v>
+        <v>105582</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5671,17 +5671,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705369</v>
+        <v>705482</v>
       </c>
       <c r="R46" t="n">
-        <v>6396695</v>
+        <v>6396736</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5727,7 +5736,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5745,27 +5754,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295479</v>
+        <v>127295531</v>
       </c>
       <c r="B47" t="n">
-        <v>105580</v>
+        <v>106292</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5773,26 +5782,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705482</v>
+        <v>705369</v>
       </c>
       <c r="R47" t="n">
-        <v>6396736</v>
+        <v>6396695</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5859,7 +5859,7 @@
         <v>127295512</v>
       </c>
       <c r="B48" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>127534911</v>
       </c>
       <c r="B50" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>127544907</v>
       </c>
       <c r="B51" t="n">
-        <v>105580</v>
+        <v>105582</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -2028,27 +2028,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295472</v>
+        <v>127295536</v>
       </c>
       <c r="B14" t="n">
-        <v>105582</v>
+        <v>106292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2056,29 +2056,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705521</v>
+        <v>705357</v>
       </c>
       <c r="R14" t="n">
-        <v>6396665</v>
+        <v>6396670</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,11 +2101,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Röse 10 m V.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2126,7 +2112,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2144,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295515</v>
+        <v>127295472</v>
       </c>
       <c r="B15" t="n">
         <v>105582</v>
@@ -2174,12 +2160,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2188,13 +2174,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705366</v>
+        <v>705521</v>
       </c>
       <c r="R15" t="n">
-        <v>6396780</v>
+        <v>6396665</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2214,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
+          <t>Röse 10 m V.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,7 +2228,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2260,7 +2246,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295474</v>
+        <v>127295515</v>
       </c>
       <c r="B16" t="n">
         <v>105582</v>
@@ -2290,12 +2276,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2304,13 +2290,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705499</v>
+        <v>705366</v>
       </c>
       <c r="R16" t="n">
-        <v>6396683</v>
+        <v>6396780</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,6 +2328,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minsta antal. Mot ny myrstack.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2353,7 +2344,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2371,27 +2362,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295536</v>
+        <v>127295474</v>
       </c>
       <c r="B17" t="n">
-        <v>106292</v>
+        <v>105582</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2399,20 +2390,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705357</v>
+        <v>705499</v>
       </c>
       <c r="R17" t="n">
-        <v>6396670</v>
+        <v>6396683</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>98428</v>
+        <v>105582</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R24" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,6 +3231,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3242,7 +3247,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,37 +3265,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>105582</v>
+        <v>98428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3304,13 +3309,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R25" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,11 +3347,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3927,42 +3927,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295486</v>
+        <v>127296628</v>
       </c>
       <c r="B31" t="n">
-        <v>105582</v>
+        <v>43065</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>101260</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3971,13 +3986,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705414</v>
+        <v>705369</v>
       </c>
       <c r="R31" t="n">
-        <v>6396806</v>
+        <v>6396695</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4020,7 +4035,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4038,7 +4053,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295482</v>
+        <v>127295486</v>
       </c>
       <c r="B32" t="n">
         <v>105582</v>
@@ -4068,7 +4083,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4082,13 +4097,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>705483</v>
+        <v>705414</v>
       </c>
       <c r="R32" t="n">
-        <v>6396749</v>
+        <v>6396806</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4149,57 +4164,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127296628</v>
+        <v>127295482</v>
       </c>
       <c r="B33" t="n">
-        <v>43065</v>
+        <v>105582</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101260</v>
+        <v>671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705369</v>
+        <v>705483</v>
       </c>
       <c r="R33" t="n">
-        <v>6396695</v>
+        <v>6396749</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5643,37 +5643,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295479</v>
+        <v>127295512</v>
       </c>
       <c r="B46" t="n">
-        <v>105582</v>
+        <v>98428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705482</v>
+        <v>705380</v>
       </c>
       <c r="R46" t="n">
-        <v>6396736</v>
+        <v>6396786</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295512</v>
+        <v>127295479</v>
       </c>
       <c r="B48" t="n">
-        <v>98428</v>
+        <v>105582</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5900,13 +5900,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705380</v>
+        <v>705482</v>
       </c>
       <c r="R48" t="n">
-        <v>6396786</v>
+        <v>6396736</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127016376</v>
+        <v>127016698</v>
       </c>
       <c r="B7" t="n">
-        <v>57584</v>
+        <v>106292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,27 +1287,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>221903</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1315,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>705342</v>
+        <v>705426</v>
       </c>
       <c r="R7" t="n">
-        <v>6396842</v>
+        <v>6396735</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,12 +1349,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,6 +1363,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1377,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127016698</v>
+        <v>127016376</v>
       </c>
       <c r="B8" t="n">
-        <v>106292</v>
+        <v>57584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,31 +1393,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221903</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1420,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705426</v>
+        <v>705342</v>
       </c>
       <c r="R8" t="n">
-        <v>6396735</v>
+        <v>6396842</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,12 +1451,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1465,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1801,37 +1801,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295507</v>
+        <v>127295490</v>
       </c>
       <c r="B12" t="n">
-        <v>98428</v>
+        <v>109277</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705371</v>
+        <v>705332</v>
       </c>
       <c r="R12" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,6 +1881,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,27 +1917,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295490</v>
+        <v>127295472</v>
       </c>
       <c r="B13" t="n">
-        <v>109277</v>
+        <v>105582</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1956,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705332</v>
+        <v>705521</v>
       </c>
       <c r="R13" t="n">
-        <v>6396980</v>
+        <v>6396665</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1996,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Röse 10 m V.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,7 +2015,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2028,27 +2033,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295536</v>
+        <v>127295515</v>
       </c>
       <c r="B14" t="n">
-        <v>106292</v>
+        <v>105582</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2056,20 +2061,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705357</v>
+        <v>705366</v>
       </c>
       <c r="R14" t="n">
-        <v>6396670</v>
+        <v>6396780</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,6 +2115,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minsta antal. Mot ny myrstack.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2112,7 +2131,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2130,7 +2149,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295472</v>
+        <v>127295474</v>
       </c>
       <c r="B15" t="n">
         <v>105582</v>
@@ -2174,13 +2193,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705521</v>
+        <v>705499</v>
       </c>
       <c r="R15" t="n">
-        <v>6396665</v>
+        <v>6396683</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,11 +2229,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Röse 10 m V.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,42 +2260,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295515</v>
+        <v>127295507</v>
       </c>
       <c r="B16" t="n">
-        <v>105582</v>
+        <v>98428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2290,13 +2304,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705366</v>
+        <v>705371</v>
       </c>
       <c r="R16" t="n">
         <v>6396780</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,11 +2342,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2344,7 +2353,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2362,27 +2371,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295474</v>
+        <v>127295536</v>
       </c>
       <c r="B17" t="n">
-        <v>105582</v>
+        <v>106292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2390,29 +2399,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705499</v>
+        <v>705357</v>
       </c>
       <c r="R17" t="n">
-        <v>6396683</v>
+        <v>6396670</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2806,37 +2806,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295527</v>
+        <v>127295514</v>
       </c>
       <c r="B21" t="n">
-        <v>105582</v>
+        <v>98428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705395</v>
+        <v>705366</v>
       </c>
       <c r="R21" t="n">
-        <v>6396678</v>
+        <v>6396780</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2888,11 +2888,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Just N sten.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2904,7 +2899,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2922,7 +2917,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295501</v>
+        <v>127295527</v>
       </c>
       <c r="B22" t="n">
         <v>105582</v>
@@ -2952,12 +2947,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2966,13 +2961,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705351</v>
+        <v>705395</v>
       </c>
       <c r="R22" t="n">
-        <v>6396798</v>
+        <v>6396678</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,7 +3001,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Just N sten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3038,42 +3033,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295514</v>
+        <v>127295501</v>
       </c>
       <c r="B23" t="n">
-        <v>98428</v>
+        <v>105582</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3082,13 +3077,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>705366</v>
+        <v>705351</v>
       </c>
       <c r="R23" t="n">
-        <v>6396780</v>
+        <v>6396798</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3118,6 +3113,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3927,57 +3927,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127296628</v>
+        <v>127295486</v>
       </c>
       <c r="B31" t="n">
-        <v>43065</v>
+        <v>105582</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101260</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3986,13 +3971,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705369</v>
+        <v>705414</v>
       </c>
       <c r="R31" t="n">
-        <v>6396695</v>
+        <v>6396806</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4035,7 +4020,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4053,7 +4038,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295486</v>
+        <v>127295482</v>
       </c>
       <c r="B32" t="n">
         <v>105582</v>
@@ -4083,7 +4068,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4097,13 +4082,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>705414</v>
+        <v>705483</v>
       </c>
       <c r="R32" t="n">
-        <v>6396806</v>
+        <v>6396749</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4164,42 +4149,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295482</v>
+        <v>127296628</v>
       </c>
       <c r="B33" t="n">
-        <v>105582</v>
+        <v>43065</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>671</v>
+        <v>101260</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705483</v>
+        <v>705369</v>
       </c>
       <c r="R33" t="n">
-        <v>6396749</v>
+        <v>6396695</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,27 +1801,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295490</v>
+        <v>127295472</v>
       </c>
       <c r="B12" t="n">
-        <v>109277</v>
+        <v>105588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705332</v>
+        <v>705521</v>
       </c>
       <c r="R12" t="n">
-        <v>6396980</v>
+        <v>6396665</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Röse 10 m V.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295472</v>
+        <v>127295515</v>
       </c>
       <c r="B13" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1961,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705521</v>
+        <v>705366</v>
       </c>
       <c r="R13" t="n">
-        <v>6396665</v>
+        <v>6396780</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Röse 10 m V.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295515</v>
+        <v>127295474</v>
       </c>
       <c r="B14" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705366</v>
+        <v>705499</v>
       </c>
       <c r="R14" t="n">
-        <v>6396780</v>
+        <v>6396683</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,11 +2115,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2131,7 +2126,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2149,27 +2144,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295474</v>
+        <v>127295490</v>
       </c>
       <c r="B15" t="n">
-        <v>105582</v>
+        <v>109283</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>671</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2179,7 +2174,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705499</v>
+        <v>705332</v>
       </c>
       <c r="R15" t="n">
-        <v>6396683</v>
+        <v>6396980</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,6 +2226,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2263,7 +2263,7 @@
         <v>127295507</v>
       </c>
       <c r="B16" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>127295536</v>
       </c>
       <c r="B17" t="n">
-        <v>106292</v>
+        <v>106298</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>127295476</v>
       </c>
       <c r="B18" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127295477</v>
       </c>
       <c r="B19" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,37 +2806,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295514</v>
+        <v>127295527</v>
       </c>
       <c r="B21" t="n">
-        <v>98428</v>
+        <v>105588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705366</v>
+        <v>705395</v>
       </c>
       <c r="R21" t="n">
-        <v>6396780</v>
+        <v>6396678</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2888,6 +2888,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Just N sten.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2904,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2917,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295527</v>
+        <v>127295501</v>
       </c>
       <c r="B22" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2947,12 +2952,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2961,13 +2966,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705395</v>
+        <v>705351</v>
       </c>
       <c r="R22" t="n">
-        <v>6396678</v>
+        <v>6396798</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3001,7 +3006,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Just N sten.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,7 +3020,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3033,42 +3038,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295501</v>
+        <v>127295514</v>
       </c>
       <c r="B23" t="n">
-        <v>105582</v>
+        <v>98434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3077,13 +3082,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>705351</v>
+        <v>705366</v>
       </c>
       <c r="R23" t="n">
-        <v>6396798</v>
+        <v>6396780</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,11 +3118,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,7 +3152,7 @@
         <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>106048</v>
+        <v>105588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,20 +3404,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R26" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,7 +3469,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3478,27 +3487,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>105582</v>
+        <v>106054</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3506,29 +3515,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R27" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127295511</v>
       </c>
       <c r="B29" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>127295616</v>
       </c>
       <c r="B30" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>127295486</v>
       </c>
       <c r="B31" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>127295550</v>
       </c>
       <c r="B36" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>127295520</v>
       </c>
       <c r="B37" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>127295553</v>
       </c>
       <c r="B38" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>127295510</v>
       </c>
       <c r="B39" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>127295499</v>
       </c>
       <c r="B40" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>127295485</v>
       </c>
       <c r="B41" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>127295478</v>
       </c>
       <c r="B42" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5643,37 +5643,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295512</v>
+        <v>127295479</v>
       </c>
       <c r="B46" t="n">
-        <v>98428</v>
+        <v>105588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705380</v>
+        <v>705482</v>
       </c>
       <c r="R46" t="n">
-        <v>6396786</v>
+        <v>6396736</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5754,48 +5754,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295531</v>
+        <v>127295512</v>
       </c>
       <c r="B47" t="n">
-        <v>106292</v>
+        <v>98434</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705369</v>
+        <v>705380</v>
       </c>
       <c r="R47" t="n">
-        <v>6396695</v>
+        <v>6396786</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5838,7 +5847,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5856,27 +5865,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295479</v>
+        <v>127295531</v>
       </c>
       <c r="B48" t="n">
-        <v>105582</v>
+        <v>106298</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5884,26 +5893,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705482</v>
+        <v>705369</v>
       </c>
       <c r="R48" t="n">
-        <v>6396736</v>
+        <v>6396695</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>127534911</v>
       </c>
       <c r="B50" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>127544907</v>
       </c>
       <c r="B51" t="n">
-        <v>105582</v>
+        <v>105588</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,37 +1801,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295472</v>
+        <v>127295507</v>
       </c>
       <c r="B12" t="n">
-        <v>105588</v>
+        <v>98437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705521</v>
+        <v>705371</v>
       </c>
       <c r="R12" t="n">
-        <v>6396665</v>
+        <v>6396780</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,11 +1883,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Röse 10 m V.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1899,7 +1894,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1917,27 +1912,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295515</v>
+        <v>127295490</v>
       </c>
       <c r="B13" t="n">
-        <v>105588</v>
+        <v>109286</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>671</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1947,12 +1942,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1961,13 +1956,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705366</v>
+        <v>705332</v>
       </c>
       <c r="R13" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,7 +2010,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2036,7 +2031,7 @@
         <v>127295474</v>
       </c>
       <c r="B14" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,27 +2139,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295490</v>
+        <v>127295515</v>
       </c>
       <c r="B15" t="n">
-        <v>109283</v>
+        <v>105591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2174,12 +2169,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2188,13 +2183,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705332</v>
+        <v>705366</v>
       </c>
       <c r="R15" t="n">
-        <v>6396980</v>
+        <v>6396780</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2223,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,7 +2237,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2260,37 +2255,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295507</v>
+        <v>127295472</v>
       </c>
       <c r="B16" t="n">
-        <v>98434</v>
+        <v>105591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2304,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705371</v>
+        <v>705521</v>
       </c>
       <c r="R16" t="n">
-        <v>6396780</v>
+        <v>6396665</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,6 +2337,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Röse 10 m V.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2374,7 +2374,7 @@
         <v>127295536</v>
       </c>
       <c r="B17" t="n">
-        <v>106298</v>
+        <v>106301</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295476</v>
+        <v>127295477</v>
       </c>
       <c r="B18" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>705490</v>
       </c>
       <c r="R18" t="n">
-        <v>6396722</v>
+        <v>6396728</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, vid myrstig nära granar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127295477</v>
+        <v>127295476</v>
       </c>
       <c r="B19" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,7 +2631,7 @@
         <v>705490</v>
       </c>
       <c r="R19" t="n">
-        <v>6396728</v>
+        <v>6396722</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, vid myrstig nära granar.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295527</v>
+        <v>127295501</v>
       </c>
       <c r="B21" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705395</v>
+        <v>705351</v>
       </c>
       <c r="R21" t="n">
-        <v>6396678</v>
+        <v>6396798</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Just N sten.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295501</v>
+        <v>127295527</v>
       </c>
       <c r="B22" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,12 +2952,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705351</v>
+        <v>705395</v>
       </c>
       <c r="R22" t="n">
-        <v>6396798</v>
+        <v>6396678</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Just N sten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>127295514</v>
       </c>
       <c r="B23" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B24" t="n">
-        <v>105588</v>
+        <v>98437</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R24" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,11 +3231,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3247,7 +3242,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3265,37 +3260,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B25" t="n">
-        <v>98434</v>
+        <v>105591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3309,13 +3304,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R25" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3347,6 +3342,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
         <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127295511</v>
       </c>
       <c r="B29" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>127295616</v>
       </c>
       <c r="B30" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,42 +3927,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295486</v>
+        <v>127296628</v>
       </c>
       <c r="B31" t="n">
-        <v>105588</v>
+        <v>43066</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>101260</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3971,13 +3986,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705414</v>
+        <v>705369</v>
       </c>
       <c r="R31" t="n">
-        <v>6396806</v>
+        <v>6396695</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4020,7 +4035,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4041,7 +4056,7 @@
         <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4149,57 +4164,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127296628</v>
+        <v>127295486</v>
       </c>
       <c r="B33" t="n">
-        <v>43065</v>
+        <v>105591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101260</v>
+        <v>671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705369</v>
+        <v>705414</v>
       </c>
       <c r="R33" t="n">
-        <v>6396695</v>
+        <v>6396806</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295550</v>
+        <v>127295520</v>
       </c>
       <c r="B36" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>705402</v>
+        <v>705389</v>
       </c>
       <c r="R36" t="n">
-        <v>6396607</v>
+        <v>6396765</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex.</t>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295520</v>
+        <v>127295550</v>
       </c>
       <c r="B37" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>705389</v>
+        <v>705402</v>
       </c>
       <c r="R37" t="n">
-        <v>6396765</v>
+        <v>6396607</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minsta antal.</t>
+          <t>Ungefärligt antal; småex.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295553</v>
+        <v>127295510</v>
       </c>
       <c r="B38" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>705399</v>
+        <v>705381</v>
       </c>
       <c r="R38" t="n">
-        <v>6396595</v>
+        <v>6396796</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295510</v>
+        <v>127295499</v>
       </c>
       <c r="B39" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4890,13 +4890,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>705381</v>
+        <v>705323</v>
       </c>
       <c r="R39" t="n">
-        <v>6396796</v>
+        <v>6396800</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Minsta antal. Nära stor dubbelgran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4962,10 +4962,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295499</v>
+        <v>127295553</v>
       </c>
       <c r="B40" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>705323</v>
+        <v>705399</v>
       </c>
       <c r="R40" t="n">
-        <v>6396800</v>
+        <v>6396595</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minsta antal. Nära stor dubbelgran.</t>
+          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295485</v>
+        <v>127295478</v>
       </c>
       <c r="B41" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>705434</v>
+        <v>705482</v>
       </c>
       <c r="R41" t="n">
-        <v>6396784</v>
+        <v>6396738</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295478</v>
+        <v>127295485</v>
       </c>
       <c r="B42" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>705482</v>
+        <v>705434</v>
       </c>
       <c r="R42" t="n">
-        <v>6396738</v>
+        <v>6396784</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>127295479</v>
       </c>
       <c r="B46" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5754,57 +5754,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295512</v>
+        <v>127295531</v>
       </c>
       <c r="B47" t="n">
-        <v>98434</v>
+        <v>106301</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705380</v>
+        <v>705369</v>
       </c>
       <c r="R47" t="n">
-        <v>6396786</v>
+        <v>6396695</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5847,7 +5838,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5865,48 +5856,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295531</v>
+        <v>127295512</v>
       </c>
       <c r="B48" t="n">
-        <v>106298</v>
+        <v>98437</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705369</v>
+        <v>705380</v>
       </c>
       <c r="R48" t="n">
-        <v>6396695</v>
+        <v>6396786</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>127534911</v>
       </c>
       <c r="B50" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>127544907</v>
       </c>
       <c r="B51" t="n">
-        <v>105588</v>
+        <v>105591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,37 +1801,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295507</v>
+        <v>127295472</v>
       </c>
       <c r="B12" t="n">
-        <v>98437</v>
+        <v>105599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705371</v>
+        <v>705521</v>
       </c>
       <c r="R12" t="n">
-        <v>6396780</v>
+        <v>6396665</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,6 +1883,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Röse 10 m V.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1894,7 +1899,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1912,27 +1917,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295490</v>
+        <v>127295515</v>
       </c>
       <c r="B13" t="n">
-        <v>109286</v>
+        <v>105599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1942,12 +1947,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1956,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705332</v>
+        <v>705366</v>
       </c>
       <c r="R13" t="n">
-        <v>6396980</v>
+        <v>6396780</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1996,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,7 +2015,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2031,7 +2036,7 @@
         <v>127295474</v>
       </c>
       <c r="B14" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,27 +2144,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295515</v>
+        <v>127295490</v>
       </c>
       <c r="B15" t="n">
-        <v>105591</v>
+        <v>109294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>671</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2169,12 +2174,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2183,13 +2188,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705366</v>
+        <v>705332</v>
       </c>
       <c r="R15" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2223,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2242,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2255,37 +2260,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295472</v>
+        <v>127295507</v>
       </c>
       <c r="B16" t="n">
-        <v>105591</v>
+        <v>98445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2299,13 +2304,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705521</v>
+        <v>705371</v>
       </c>
       <c r="R16" t="n">
-        <v>6396665</v>
+        <v>6396780</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2337,11 +2342,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Röse 10 m V.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2374,7 +2374,7 @@
         <v>127295536</v>
       </c>
       <c r="B17" t="n">
-        <v>106301</v>
+        <v>106309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295477</v>
+        <v>127295476</v>
       </c>
       <c r="B18" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>705490</v>
       </c>
       <c r="R18" t="n">
-        <v>6396728</v>
+        <v>6396722</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, vid myrstig nära granar.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127295476</v>
+        <v>127295477</v>
       </c>
       <c r="B19" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,7 +2631,7 @@
         <v>705490</v>
       </c>
       <c r="R19" t="n">
-        <v>6396722</v>
+        <v>6396728</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, vid myrstig nära granar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295501</v>
+        <v>127295527</v>
       </c>
       <c r="B21" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705351</v>
+        <v>705395</v>
       </c>
       <c r="R21" t="n">
-        <v>6396798</v>
+        <v>6396678</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Just N sten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295527</v>
+        <v>127295501</v>
       </c>
       <c r="B22" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,12 +2952,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705395</v>
+        <v>705351</v>
       </c>
       <c r="R22" t="n">
-        <v>6396678</v>
+        <v>6396798</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Just N sten.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>127295514</v>
       </c>
       <c r="B23" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>98437</v>
+        <v>105599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R24" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,6 +3231,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3242,7 +3247,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,37 +3265,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>105591</v>
+        <v>98445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3304,13 +3309,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R25" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,11 +3347,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
         <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>106057</v>
+        <v>106065</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127295511</v>
       </c>
       <c r="B29" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>127295616</v>
       </c>
       <c r="B30" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,57 +3927,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127296628</v>
+        <v>127295486</v>
       </c>
       <c r="B31" t="n">
-        <v>43066</v>
+        <v>105599</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101260</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3986,13 +3971,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705369</v>
+        <v>705414</v>
       </c>
       <c r="R31" t="n">
-        <v>6396695</v>
+        <v>6396806</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4035,7 +4020,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4056,7 +4041,7 @@
         <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4164,42 +4149,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295486</v>
+        <v>127296628</v>
       </c>
       <c r="B33" t="n">
-        <v>105591</v>
+        <v>43066</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>671</v>
+        <v>101260</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705414</v>
+        <v>705369</v>
       </c>
       <c r="R33" t="n">
-        <v>6396806</v>
+        <v>6396695</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295520</v>
+        <v>127295550</v>
       </c>
       <c r="B36" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>705389</v>
+        <v>705402</v>
       </c>
       <c r="R36" t="n">
-        <v>6396765</v>
+        <v>6396607</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minsta antal.</t>
+          <t>Ungefärligt antal; småex.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295550</v>
+        <v>127295520</v>
       </c>
       <c r="B37" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>705402</v>
+        <v>705389</v>
       </c>
       <c r="R37" t="n">
-        <v>6396607</v>
+        <v>6396765</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex.</t>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295510</v>
+        <v>127295553</v>
       </c>
       <c r="B38" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>705381</v>
+        <v>705399</v>
       </c>
       <c r="R38" t="n">
-        <v>6396796</v>
+        <v>6396595</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295499</v>
+        <v>127295510</v>
       </c>
       <c r="B39" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4890,13 +4890,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>705323</v>
+        <v>705381</v>
       </c>
       <c r="R39" t="n">
-        <v>6396800</v>
+        <v>6396796</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minsta antal. Nära stor dubbelgran.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4962,10 +4962,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295553</v>
+        <v>127295499</v>
       </c>
       <c r="B40" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>705399</v>
+        <v>705323</v>
       </c>
       <c r="R40" t="n">
-        <v>6396595</v>
+        <v>6396800</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
+          <t>Minsta antal. Nära stor dubbelgran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295478</v>
+        <v>127295485</v>
       </c>
       <c r="B41" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>705482</v>
+        <v>705434</v>
       </c>
       <c r="R41" t="n">
-        <v>6396738</v>
+        <v>6396784</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295485</v>
+        <v>127295478</v>
       </c>
       <c r="B42" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>705434</v>
+        <v>705482</v>
       </c>
       <c r="R42" t="n">
-        <v>6396784</v>
+        <v>6396738</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>127295479</v>
       </c>
       <c r="B46" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5754,48 +5754,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295531</v>
+        <v>127295512</v>
       </c>
       <c r="B47" t="n">
-        <v>106301</v>
+        <v>98445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705369</v>
+        <v>705380</v>
       </c>
       <c r="R47" t="n">
-        <v>6396695</v>
+        <v>6396786</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5838,7 +5847,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5856,57 +5865,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295512</v>
+        <v>127295531</v>
       </c>
       <c r="B48" t="n">
-        <v>98437</v>
+        <v>106309</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705380</v>
+        <v>705369</v>
       </c>
       <c r="R48" t="n">
-        <v>6396786</v>
+        <v>6396695</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>127534911</v>
       </c>
       <c r="B50" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>127544907</v>
       </c>
       <c r="B51" t="n">
-        <v>105591</v>
+        <v>105599</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295472</v>
+        <v>127295515</v>
       </c>
       <c r="B12" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705521</v>
+        <v>705366</v>
       </c>
       <c r="R12" t="n">
-        <v>6396665</v>
+        <v>6396780</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Röse 10 m V.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295515</v>
+        <v>127295474</v>
       </c>
       <c r="B13" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1961,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705366</v>
+        <v>705499</v>
       </c>
       <c r="R13" t="n">
-        <v>6396780</v>
+        <v>6396683</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,11 +1999,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2015,7 +2010,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2033,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295474</v>
+        <v>127295472</v>
       </c>
       <c r="B14" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,13 +2072,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705499</v>
+        <v>705521</v>
       </c>
       <c r="R14" t="n">
-        <v>6396683</v>
+        <v>6396665</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2113,6 +2108,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Röse 10 m V.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,37 +2144,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295490</v>
+        <v>127295507</v>
       </c>
       <c r="B15" t="n">
-        <v>109294</v>
+        <v>98446</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705332</v>
+        <v>705371</v>
       </c>
       <c r="R15" t="n">
-        <v>6396980</v>
+        <v>6396780</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,11 +2224,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,37 +2255,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295507</v>
+        <v>127295490</v>
       </c>
       <c r="B16" t="n">
-        <v>98445</v>
+        <v>109295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2304,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705371</v>
+        <v>705332</v>
       </c>
       <c r="R16" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,6 +2335,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,7 +2374,7 @@
         <v>127295536</v>
       </c>
       <c r="B17" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295476</v>
+        <v>127295477</v>
       </c>
       <c r="B18" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>705490</v>
       </c>
       <c r="R18" t="n">
-        <v>6396722</v>
+        <v>6396728</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, vid myrstig nära granar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127295477</v>
+        <v>127295476</v>
       </c>
       <c r="B19" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,7 +2631,7 @@
         <v>705490</v>
       </c>
       <c r="R19" t="n">
-        <v>6396728</v>
+        <v>6396722</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, vid myrstig nära granar.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295527</v>
+        <v>127295501</v>
       </c>
       <c r="B21" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705395</v>
+        <v>705351</v>
       </c>
       <c r="R21" t="n">
-        <v>6396678</v>
+        <v>6396798</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Just N sten.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295501</v>
+        <v>127295527</v>
       </c>
       <c r="B22" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,12 +2952,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705351</v>
+        <v>705395</v>
       </c>
       <c r="R22" t="n">
-        <v>6396798</v>
+        <v>6396678</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Just N sten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>127295514</v>
       </c>
       <c r="B23" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>106065</v>
+        <v>106066</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,37 +3700,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295511</v>
+        <v>127295616</v>
       </c>
       <c r="B29" t="n">
-        <v>105599</v>
+        <v>98446</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705371</v>
+        <v>705528</v>
       </c>
       <c r="R29" t="n">
-        <v>6396787</v>
+        <v>6396664</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,11 +3782,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minsta antal. Vid granrot.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3798,7 +3793,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3816,37 +3811,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295616</v>
+        <v>127295511</v>
       </c>
       <c r="B30" t="n">
-        <v>98445</v>
+        <v>105600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3860,13 +3855,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705528</v>
+        <v>705371</v>
       </c>
       <c r="R30" t="n">
-        <v>6396664</v>
+        <v>6396787</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,6 +3893,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3927,42 +3927,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295486</v>
+        <v>127296628</v>
       </c>
       <c r="B31" t="n">
-        <v>105599</v>
+        <v>43066</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>671</v>
+        <v>101260</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3971,13 +3986,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705414</v>
+        <v>705369</v>
       </c>
       <c r="R31" t="n">
-        <v>6396806</v>
+        <v>6396695</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4020,7 +4035,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4041,7 +4056,7 @@
         <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4149,57 +4164,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127296628</v>
+        <v>127295486</v>
       </c>
       <c r="B33" t="n">
-        <v>43066</v>
+        <v>105600</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101260</v>
+        <v>671</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705369</v>
+        <v>705414</v>
       </c>
       <c r="R33" t="n">
-        <v>6396695</v>
+        <v>6396806</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295550</v>
+        <v>127295520</v>
       </c>
       <c r="B36" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>705402</v>
+        <v>705389</v>
       </c>
       <c r="R36" t="n">
-        <v>6396607</v>
+        <v>6396765</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex.</t>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295520</v>
+        <v>127295550</v>
       </c>
       <c r="B37" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>705389</v>
+        <v>705402</v>
       </c>
       <c r="R37" t="n">
-        <v>6396765</v>
+        <v>6396607</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minsta antal.</t>
+          <t>Ungefärligt antal; småex.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295553</v>
+        <v>127295510</v>
       </c>
       <c r="B38" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>705399</v>
+        <v>705381</v>
       </c>
       <c r="R38" t="n">
-        <v>6396595</v>
+        <v>6396796</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295510</v>
+        <v>127295499</v>
       </c>
       <c r="B39" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4890,13 +4890,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>705381</v>
+        <v>705323</v>
       </c>
       <c r="R39" t="n">
-        <v>6396796</v>
+        <v>6396800</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Minsta antal. Nära stor dubbelgran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4962,10 +4962,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295499</v>
+        <v>127295553</v>
       </c>
       <c r="B40" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>705323</v>
+        <v>705399</v>
       </c>
       <c r="R40" t="n">
-        <v>6396800</v>
+        <v>6396595</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minsta antal. Nära stor dubbelgran.</t>
+          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295485</v>
+        <v>127295478</v>
       </c>
       <c r="B41" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>705434</v>
+        <v>705482</v>
       </c>
       <c r="R41" t="n">
-        <v>6396784</v>
+        <v>6396738</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295478</v>
+        <v>127295485</v>
       </c>
       <c r="B42" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>705482</v>
+        <v>705434</v>
       </c>
       <c r="R42" t="n">
-        <v>6396738</v>
+        <v>6396784</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5643,37 +5643,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295479</v>
+        <v>127295512</v>
       </c>
       <c r="B46" t="n">
-        <v>105599</v>
+        <v>98446</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>705482</v>
+        <v>705380</v>
       </c>
       <c r="R46" t="n">
-        <v>6396736</v>
+        <v>6396786</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5754,57 +5754,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295512</v>
+        <v>127295531</v>
       </c>
       <c r="B47" t="n">
-        <v>98445</v>
+        <v>106310</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705380</v>
+        <v>705369</v>
       </c>
       <c r="R47" t="n">
-        <v>6396786</v>
+        <v>6396695</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5847,7 +5838,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5865,27 +5856,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295531</v>
+        <v>127295479</v>
       </c>
       <c r="B48" t="n">
-        <v>106309</v>
+        <v>105600</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5893,17 +5884,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705369</v>
+        <v>705482</v>
       </c>
       <c r="R48" t="n">
-        <v>6396695</v>
+        <v>6396736</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>127534911</v>
       </c>
       <c r="B50" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>127544907</v>
       </c>
       <c r="B51" t="n">
-        <v>105599</v>
+        <v>105600</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1801,7 +1801,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295515</v>
+        <v>127295474</v>
       </c>
       <c r="B12" t="n">
         <v>105600</v>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705366</v>
+        <v>705499</v>
       </c>
       <c r="R12" t="n">
-        <v>6396780</v>
+        <v>6396683</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,11 +1883,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1899,7 +1894,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1917,7 +1912,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295474</v>
+        <v>127295515</v>
       </c>
       <c r="B13" t="n">
         <v>105600</v>
@@ -1947,12 +1942,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1961,13 +1956,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705499</v>
+        <v>705366</v>
       </c>
       <c r="R13" t="n">
-        <v>6396683</v>
+        <v>6396780</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,6 +1994,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minsta antal. Mot ny myrstack.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2144,37 +2144,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295507</v>
+        <v>127295490</v>
       </c>
       <c r="B15" t="n">
-        <v>98446</v>
+        <v>109295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705371</v>
+        <v>705332</v>
       </c>
       <c r="R15" t="n">
-        <v>6396780</v>
+        <v>6396980</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,6 +2224,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295490</v>
+        <v>127295536</v>
       </c>
       <c r="B16" t="n">
-        <v>109295</v>
+        <v>106310</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,16 +2271,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2283,29 +2288,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705332</v>
+        <v>705357</v>
       </c>
       <c r="R16" t="n">
-        <v>6396980</v>
+        <v>6396670</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2337,11 +2333,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2353,7 +2344,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2371,48 +2362,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295536</v>
+        <v>127295507</v>
       </c>
       <c r="B17" t="n">
-        <v>106310</v>
+        <v>98446</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705357</v>
+        <v>705371</v>
       </c>
       <c r="R17" t="n">
-        <v>6396670</v>
+        <v>6396780</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2806,42 +2806,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295501</v>
+        <v>127295514</v>
       </c>
       <c r="B21" t="n">
-        <v>105600</v>
+        <v>98446</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705351</v>
+        <v>705366</v>
       </c>
       <c r="R21" t="n">
-        <v>6396798</v>
+        <v>6396780</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2886,11 +2886,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,7 +2917,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295527</v>
+        <v>127295501</v>
       </c>
       <c r="B22" t="n">
         <v>105600</v>
@@ -2952,12 +2947,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2966,13 +2961,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>705395</v>
+        <v>705351</v>
       </c>
       <c r="R22" t="n">
-        <v>6396678</v>
+        <v>6396798</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,7 +3001,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Just N sten.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3038,37 +3033,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295514</v>
+        <v>127295527</v>
       </c>
       <c r="B23" t="n">
-        <v>98446</v>
+        <v>105600</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>705366</v>
+        <v>705395</v>
       </c>
       <c r="R23" t="n">
-        <v>6396780</v>
+        <v>6396678</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,6 +3115,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Just N sten.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B24" t="n">
-        <v>105600</v>
+        <v>98446</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R24" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,11 +3231,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3247,7 +3242,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3265,37 +3260,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B25" t="n">
-        <v>98446</v>
+        <v>105600</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3309,13 +3304,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R25" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3347,6 +3342,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B26" t="n">
-        <v>105600</v>
+        <v>106066</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,29 +3404,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R26" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3469,7 +3460,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3487,27 +3478,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B27" t="n">
-        <v>106066</v>
+        <v>105600</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3515,20 +3506,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R27" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3927,57 +3927,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127296628</v>
+        <v>127295482</v>
       </c>
       <c r="B31" t="n">
-        <v>43066</v>
+        <v>105600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101260</v>
+        <v>671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3986,13 +3971,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705369</v>
+        <v>705483</v>
       </c>
       <c r="R31" t="n">
-        <v>6396695</v>
+        <v>6396749</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4035,7 +4020,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4053,7 +4038,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295482</v>
+        <v>127295486</v>
       </c>
       <c r="B32" t="n">
         <v>105600</v>
@@ -4083,7 +4068,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4097,13 +4082,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>705483</v>
+        <v>705414</v>
       </c>
       <c r="R32" t="n">
-        <v>6396749</v>
+        <v>6396806</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4164,42 +4149,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295486</v>
+        <v>127296628</v>
       </c>
       <c r="B33" t="n">
-        <v>105600</v>
+        <v>43066</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>671</v>
+        <v>101260</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>705414</v>
+        <v>705369</v>
       </c>
       <c r="R33" t="n">
-        <v>6396806</v>
+        <v>6396695</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5754,27 +5754,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295531</v>
+        <v>127295479</v>
       </c>
       <c r="B47" t="n">
-        <v>106310</v>
+        <v>105600</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5782,17 +5782,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705369</v>
+        <v>705482</v>
       </c>
       <c r="R47" t="n">
-        <v>6396695</v>
+        <v>6396736</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5838,7 +5847,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5856,27 +5865,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295479</v>
+        <v>127295531</v>
       </c>
       <c r="B48" t="n">
-        <v>105600</v>
+        <v>106310</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5884,26 +5893,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705482</v>
+        <v>705369</v>
       </c>
       <c r="R48" t="n">
-        <v>6396736</v>
+        <v>6396695</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -1693,7 +1693,7 @@
         <v>127295526</v>
       </c>
       <c r="B11" t="n">
-        <v>107353</v>
+        <v>107354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,27 +1801,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295474</v>
+        <v>127295490</v>
       </c>
       <c r="B12" t="n">
-        <v>105600</v>
+        <v>109296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>671</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705499</v>
+        <v>705332</v>
       </c>
       <c r="R12" t="n">
-        <v>6396683</v>
+        <v>6396980</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,6 +1883,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1894,7 +1899,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1912,42 +1917,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295515</v>
+        <v>127295507</v>
       </c>
       <c r="B13" t="n">
-        <v>105600</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1956,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705366</v>
+        <v>705371</v>
       </c>
       <c r="R13" t="n">
         <v>6396780</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,11 +1999,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minsta antal. Mot ny myrstack.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
         <v>127295472</v>
       </c>
       <c r="B14" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,27 +2144,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295490</v>
+        <v>127295515</v>
       </c>
       <c r="B15" t="n">
-        <v>109295</v>
+        <v>105601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705332</v>
+        <v>705366</v>
       </c>
       <c r="R15" t="n">
-        <v>6396980</v>
+        <v>6396780</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Minsta antal. Mot ny myrstack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2260,27 +2260,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295536</v>
+        <v>127295474</v>
       </c>
       <c r="B16" t="n">
-        <v>106310</v>
+        <v>105601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2288,20 +2288,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705357</v>
+        <v>705499</v>
       </c>
       <c r="R16" t="n">
-        <v>6396670</v>
+        <v>6396683</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2344,7 +2353,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2362,57 +2371,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295507</v>
+        <v>127295536</v>
       </c>
       <c r="B17" t="n">
-        <v>98446</v>
+        <v>106311</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>221903</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705371</v>
+        <v>705357</v>
       </c>
       <c r="R17" t="n">
-        <v>6396780</v>
+        <v>6396670</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295477</v>
+        <v>127295476</v>
       </c>
       <c r="B18" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>705490</v>
       </c>
       <c r="R18" t="n">
-        <v>6396728</v>
+        <v>6396722</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, vid myrstig nära granar.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127295476</v>
+        <v>127295477</v>
       </c>
       <c r="B19" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,7 +2631,7 @@
         <v>705490</v>
       </c>
       <c r="R19" t="n">
-        <v>6396722</v>
+        <v>6396728</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, vid myrstig nära granar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
         <v>127295488</v>
       </c>
       <c r="B20" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,37 +2806,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295514</v>
+        <v>127295527</v>
       </c>
       <c r="B21" t="n">
-        <v>98446</v>
+        <v>105601</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>705366</v>
+        <v>705395</v>
       </c>
       <c r="R21" t="n">
-        <v>6396780</v>
+        <v>6396678</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2888,6 +2888,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Just N sten.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2899,7 +2904,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2920,7 +2925,7 @@
         <v>127295501</v>
       </c>
       <c r="B22" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,37 +3038,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295527</v>
+        <v>127295514</v>
       </c>
       <c r="B23" t="n">
-        <v>105600</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>705395</v>
+        <v>705366</v>
       </c>
       <c r="R23" t="n">
-        <v>6396678</v>
+        <v>6396780</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3115,11 +3120,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Just N sten.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3149,37 +3149,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295516</v>
+        <v>127295505</v>
       </c>
       <c r="B24" t="n">
-        <v>98446</v>
+        <v>105601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>705383</v>
+        <v>705352</v>
       </c>
       <c r="R24" t="n">
-        <v>6396779</v>
+        <v>6396785</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,6 +3231,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal. Flera myrstackar i området..</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3242,7 +3247,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,37 +3265,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295505</v>
+        <v>127295516</v>
       </c>
       <c r="B25" t="n">
-        <v>105600</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3304,13 +3309,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>705352</v>
+        <v>705383</v>
       </c>
       <c r="R25" t="n">
-        <v>6396785</v>
+        <v>6396779</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,11 +3347,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3376,27 +3376,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295504</v>
+        <v>127295481</v>
       </c>
       <c r="B26" t="n">
-        <v>106066</v>
+        <v>105601</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3404,20 +3404,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>705352</v>
+        <v>705478</v>
       </c>
       <c r="R26" t="n">
-        <v>6396785</v>
+        <v>6396749</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,7 +3469,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3478,27 +3487,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295481</v>
+        <v>127295504</v>
       </c>
       <c r="B27" t="n">
-        <v>105600</v>
+        <v>106067</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>671</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3506,29 +3515,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>705478</v>
+        <v>705352</v>
       </c>
       <c r="R27" t="n">
-        <v>6396749</v>
+        <v>6396785</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>127295475</v>
       </c>
       <c r="B28" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,37 +3700,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295616</v>
+        <v>127295511</v>
       </c>
       <c r="B29" t="n">
-        <v>98446</v>
+        <v>105601</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>705528</v>
+        <v>705371</v>
       </c>
       <c r="R29" t="n">
-        <v>6396664</v>
+        <v>6396787</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,6 +3782,11 @@
           <t>2025-07-17</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minsta antal. Vid granrot.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3793,7 +3798,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3811,37 +3816,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295511</v>
+        <v>127295616</v>
       </c>
       <c r="B30" t="n">
-        <v>105600</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3855,13 +3860,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>705371</v>
+        <v>705528</v>
       </c>
       <c r="R30" t="n">
-        <v>6396787</v>
+        <v>6396664</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,11 +3898,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minsta antal. Vid granrot.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295482</v>
+        <v>127295486</v>
       </c>
       <c r="B31" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3971,13 +3971,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>705483</v>
+        <v>705414</v>
       </c>
       <c r="R31" t="n">
-        <v>6396749</v>
+        <v>6396806</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295486</v>
+        <v>127295482</v>
       </c>
       <c r="B32" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4082,13 +4082,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>705414</v>
+        <v>705483</v>
       </c>
       <c r="R32" t="n">
-        <v>6396806</v>
+        <v>6396749</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>127295551</v>
       </c>
       <c r="B34" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>127295537</v>
       </c>
       <c r="B35" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295520</v>
+        <v>127295550</v>
       </c>
       <c r="B36" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>705389</v>
+        <v>705402</v>
       </c>
       <c r="R36" t="n">
-        <v>6396765</v>
+        <v>6396607</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minsta antal.</t>
+          <t>Ungefärligt antal; småex.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295550</v>
+        <v>127295520</v>
       </c>
       <c r="B37" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>705402</v>
+        <v>705389</v>
       </c>
       <c r="R37" t="n">
-        <v>6396607</v>
+        <v>6396765</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex.</t>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295510</v>
+        <v>127295553</v>
       </c>
       <c r="B38" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>705381</v>
+        <v>705399</v>
       </c>
       <c r="R38" t="n">
-        <v>6396796</v>
+        <v>6396595</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minsta antal. Flera myrstackar i området..</t>
+          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
+          <t>Tallskog, grov, sand över kalkberggrund.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295499</v>
+        <v>127295510</v>
       </c>
       <c r="B39" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4890,13 +4890,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>705323</v>
+        <v>705381</v>
       </c>
       <c r="R39" t="n">
-        <v>6396800</v>
+        <v>6396796</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minsta antal. Nära stor dubbelgran.</t>
+          <t>Minsta antal. Flera myrstackar i området..</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4962,10 +4962,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295553</v>
+        <v>127295499</v>
       </c>
       <c r="B40" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>705399</v>
+        <v>705323</v>
       </c>
       <c r="R40" t="n">
-        <v>6396595</v>
+        <v>6396800</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ungefärligt antal; småex. Även spridd öste om bete i V.</t>
+          <t>Minsta antal. Nära stor dubbelgran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Tallskog, grov, sand över kalkberggrund.</t>
+          <t>Kalkbarrskog, längs myrstig till stor myrstack.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295478</v>
+        <v>127295485</v>
       </c>
       <c r="B41" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>705482</v>
+        <v>705434</v>
       </c>
       <c r="R41" t="n">
-        <v>6396738</v>
+        <v>6396784</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295485</v>
+        <v>127295478</v>
       </c>
       <c r="B42" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>705434</v>
+        <v>705482</v>
       </c>
       <c r="R42" t="n">
-        <v>6396784</v>
+        <v>6396738</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5303,7 +5303,7 @@
         <v>127295517</v>
       </c>
       <c r="B43" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>127295509</v>
       </c>
       <c r="B44" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127295483</v>
       </c>
       <c r="B45" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>127295512</v>
       </c>
       <c r="B46" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5754,27 +5754,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295479</v>
+        <v>127295531</v>
       </c>
       <c r="B47" t="n">
-        <v>105600</v>
+        <v>106311</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>671</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5782,26 +5782,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>705482</v>
+        <v>705369</v>
       </c>
       <c r="R47" t="n">
-        <v>6396736</v>
+        <v>6396695</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5847,7 +5838,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, nära granar.</t>
+          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5865,27 +5856,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295531</v>
+        <v>127295479</v>
       </c>
       <c r="B48" t="n">
-        <v>106310</v>
+        <v>105601</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221903</v>
+        <v>671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5893,17 +5884,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bro Ytlings 1:8 A 33728-2025., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>705369</v>
+        <v>705482</v>
       </c>
       <c r="R48" t="n">
-        <v>6396695</v>
+        <v>6396736</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkglänta, 40 m x 40m, igenväxande.</t>
+          <t>Kalkbarrskog, nära granar.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>127295532</v>
       </c>
       <c r="B49" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>127534911</v>
       </c>
       <c r="B50" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>127544907</v>
       </c>
       <c r="B51" t="n">
-        <v>105600</v>
+        <v>105601</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6072,7 +6072,7 @@
         <v>127534911</v>
       </c>
       <c r="B50" t="n">
-        <v>105601</v>
+        <v>105602</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>127544907</v>
       </c>
       <c r="B51" t="n">
-        <v>105601</v>
+        <v>105602</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6289,6 +6289,5641 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128884883</v>
+      </c>
+      <c r="B52" t="n">
+        <v>86758</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörkfjällig olivspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius melanotus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>705450</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6396748</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128884885</v>
+      </c>
+      <c r="B53" t="n">
+        <v>86859</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>705360</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6396790</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128884302</v>
+      </c>
+      <c r="B54" t="n">
+        <v>86758</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörkfjällig olivspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius melanotus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>705513</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6396594</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128889600</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91034</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>705477</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6396583</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128884872</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92801</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>705338</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6396936</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128884887</v>
+      </c>
+      <c r="B57" t="n">
+        <v>86934</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>705305</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6396830</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128884894</v>
+      </c>
+      <c r="B58" t="n">
+        <v>90960</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>705317</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6396863</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128884906</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92131</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>705291</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6396952</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128884863</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92196</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>705446</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6396726</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128884884</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91008</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>705475</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6396574</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128884301</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91034</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>705546</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6396613</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128890120</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>705487</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6396675</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128884912</v>
+      </c>
+      <c r="B64" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>705461</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6396579</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128884879</v>
+      </c>
+      <c r="B65" t="n">
+        <v>86958</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>705537</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6396616</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128884875</v>
+      </c>
+      <c r="B66" t="n">
+        <v>90297</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>705428</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6396833</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128884294</v>
+      </c>
+      <c r="B67" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>705415</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6396763</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128884861</v>
+      </c>
+      <c r="B68" t="n">
+        <v>87003</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>705483</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6396620</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128884914</v>
+      </c>
+      <c r="B69" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>705401</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6396625</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128884865</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91008</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>705416</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6396601</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128884898</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>705425</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6396809</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128884871</v>
+      </c>
+      <c r="B72" t="n">
+        <v>87024</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>705290</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6396809</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128884886</v>
+      </c>
+      <c r="B73" t="n">
+        <v>86859</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>705473</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6396572</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128884868</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91008</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>705418</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6396750</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128884869</v>
+      </c>
+      <c r="B75" t="n">
+        <v>86806</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>424</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>705297</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6396817</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128884867</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91008</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>705431</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6396688</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128884890</v>
+      </c>
+      <c r="B77" t="n">
+        <v>105675</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>705281</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6396886</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128884873</v>
+      </c>
+      <c r="B78" t="n">
+        <v>90297</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>705314</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6396809</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128884296</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91008</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>705419</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6396769</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128884299</v>
+      </c>
+      <c r="B80" t="n">
+        <v>86859</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>705536</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6396651</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128884305</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91008</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>705468</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6396595</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128884881</v>
+      </c>
+      <c r="B82" t="n">
+        <v>86945</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Narrspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius pseudoarcuatorum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>705474</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6396574</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128884866</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91008</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>705433</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6396684</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128884882</v>
+      </c>
+      <c r="B84" t="n">
+        <v>86758</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörkfjällig olivspindling</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cortinarius melanotus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>705380</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6396917</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128884862</v>
+      </c>
+      <c r="B85" t="n">
+        <v>87003</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>705398</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6396569</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128884909</v>
+      </c>
+      <c r="B86" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>705257</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6396921</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128889624</v>
+      </c>
+      <c r="B87" t="n">
+        <v>90297</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>705513</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6396594</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128884878</v>
+      </c>
+      <c r="B88" t="n">
+        <v>86958</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>705291</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6396809</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128884870</v>
+      </c>
+      <c r="B89" t="n">
+        <v>86806</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>424</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>705479</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6396566</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128884300</v>
+      </c>
+      <c r="B90" t="n">
+        <v>86806</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>424</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>705540</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6396625</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128884298</v>
+      </c>
+      <c r="B91" t="n">
+        <v>90297</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>705518</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6396658</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128884907</v>
+      </c>
+      <c r="B92" t="n">
+        <v>90240</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>970</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Bittermusseron</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Leucopaxillus gentianeus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Quél.) Kotl.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>705399</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6396889</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128884896</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>705227</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6396932</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128884864</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91008</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>705252</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6396894</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128884304</v>
+      </c>
+      <c r="B95" t="n">
+        <v>86945</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Narrspindling</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Cortinarius pseudoarcuatorum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>705475</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6396577</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128884876</v>
+      </c>
+      <c r="B96" t="n">
+        <v>90297</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>705430</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6396834</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128884915</v>
+      </c>
+      <c r="B97" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>705291</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6396949</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128884900</v>
+      </c>
+      <c r="B98" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>705445</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6396819</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128884306</v>
+      </c>
+      <c r="B99" t="n">
+        <v>86859</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>705439</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6396582</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128884303</v>
+      </c>
+      <c r="B100" t="n">
+        <v>86859</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>705477</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6396583</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128884913</v>
+      </c>
+      <c r="B101" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>705414</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6396611</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128884897</v>
+      </c>
+      <c r="B102" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>705297</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6396949</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128884899</v>
+      </c>
+      <c r="B103" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>705436</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6396834</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128884910</v>
+      </c>
+      <c r="B104" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>705273</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6396934</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128884911</v>
+      </c>
+      <c r="B105" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>705527</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6396694</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128884874</v>
+      </c>
+      <c r="B106" t="n">
+        <v>90297</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>705425</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6396850</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128884908</v>
+      </c>
+      <c r="B107" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>705320</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6396829</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6291,45 +6291,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884883</v>
+        <v>128884885</v>
       </c>
       <c r="B52" t="n">
-        <v>86758</v>
+        <v>86860</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1985</v>
+        <v>3611</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705450</v>
+        <v>705360</v>
       </c>
       <c r="R52" t="n">
-        <v>6396748</v>
+        <v>6396790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6389,48 +6392,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884885</v>
+        <v>128884883</v>
       </c>
       <c r="B53" t="n">
-        <v>86859</v>
+        <v>86758</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3611</v>
+        <v>1985</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705360</v>
+        <v>705450</v>
       </c>
       <c r="R53" t="n">
-        <v>6396790</v>
+        <v>6396748</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6600,7 +6600,7 @@
         <v>128889600</v>
       </c>
       <c r="B55" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884872</v>
+        <v>128884863</v>
       </c>
       <c r="B56" t="n">
-        <v>92801</v>
+        <v>92201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6715,21 +6715,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705338</v>
+        <v>705446</v>
       </c>
       <c r="R56" t="n">
-        <v>6396936</v>
+        <v>6396726</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,32 +6801,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884887</v>
+        <v>128884894</v>
       </c>
       <c r="B57" t="n">
-        <v>86934</v>
+        <v>90965</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1988</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705305</v>
+        <v>705317</v>
       </c>
       <c r="R57" t="n">
-        <v>6396830</v>
+        <v>6396863</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6898,32 +6898,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884894</v>
+        <v>128884887</v>
       </c>
       <c r="B58" t="n">
-        <v>90960</v>
+        <v>86935</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3286</v>
+        <v>1988</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705317</v>
+        <v>705305</v>
       </c>
       <c r="R58" t="n">
-        <v>6396863</v>
+        <v>6396830</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6998,7 +6998,7 @@
         <v>128884906</v>
       </c>
       <c r="B59" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7092,45 +7092,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884863</v>
+        <v>128884301</v>
       </c>
       <c r="B60" t="n">
-        <v>92196</v>
+        <v>91039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705446</v>
+        <v>705546</v>
       </c>
       <c r="R60" t="n">
-        <v>6396726</v>
+        <v>6396613</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7160,9 +7160,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7177,22 +7187,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884884</v>
+        <v>128884872</v>
       </c>
       <c r="B61" t="n">
-        <v>91008</v>
+        <v>92806</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7200,21 +7210,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7224,10 +7234,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705475</v>
+        <v>705338</v>
       </c>
       <c r="R61" t="n">
-        <v>6396574</v>
+        <v>6396936</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7268,7 +7278,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7287,45 +7296,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884301</v>
+        <v>128884884</v>
       </c>
       <c r="B62" t="n">
-        <v>91034</v>
+        <v>91013</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5747</v>
+        <v>5741</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705546</v>
+        <v>705475</v>
       </c>
       <c r="R62" t="n">
-        <v>6396613</v>
+        <v>6396574</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7355,39 +7364,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7397,7 +7397,7 @@
         <v>128890120</v>
       </c>
       <c r="B63" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884912</v>
+        <v>128884294</v>
       </c>
       <c r="B64" t="n">
         <v>86713</v>
@@ -7532,14 +7532,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705461</v>
+        <v>705415</v>
       </c>
       <c r="R64" t="n">
-        <v>6396579</v>
+        <v>6396763</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,9 +7569,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7587,22 +7597,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884879</v>
+        <v>128884912</v>
       </c>
       <c r="B65" t="n">
-        <v>86958</v>
+        <v>86713</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7610,21 +7620,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7634,10 +7644,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705537</v>
+        <v>705461</v>
       </c>
       <c r="R65" t="n">
-        <v>6396616</v>
+        <v>6396579</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7700,7 +7710,7 @@
         <v>128884875</v>
       </c>
       <c r="B66" t="n">
-        <v>90297</v>
+        <v>90302</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7794,10 +7804,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884294</v>
+        <v>128884879</v>
       </c>
       <c r="B67" t="n">
-        <v>86713</v>
+        <v>86959</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7805,34 +7815,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705415</v>
+        <v>705537</v>
       </c>
       <c r="R67" t="n">
-        <v>6396763</v>
+        <v>6396616</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7862,19 +7872,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7890,12 +7890,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7905,7 +7905,7 @@
         <v>128884861</v>
       </c>
       <c r="B68" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884865</v>
+        <v>128884871</v>
       </c>
       <c r="B70" t="n">
-        <v>91008</v>
+        <v>87025</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,23 +8108,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5741</v>
+        <v>3624</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8132,10 +8128,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705416</v>
+        <v>705290</v>
       </c>
       <c r="R70" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8176,7 +8172,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8195,32 +8190,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884898</v>
+        <v>128884886</v>
       </c>
       <c r="B71" t="n">
-        <v>92823</v>
+        <v>86860</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8233,10 +8228,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705425</v>
+        <v>705473</v>
       </c>
       <c r="R71" t="n">
-        <v>6396809</v>
+        <v>6396572</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8296,10 +8291,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884871</v>
+        <v>128884865</v>
       </c>
       <c r="B72" t="n">
-        <v>87024</v>
+        <v>91013</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8307,19 +8302,23 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3624</v>
+        <v>5741</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8327,10 +8326,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705290</v>
+        <v>705416</v>
       </c>
       <c r="R72" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8371,6 +8370,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884886</v>
+        <v>128884898</v>
       </c>
       <c r="B73" t="n">
-        <v>86859</v>
+        <v>92830</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705473</v>
+        <v>705425</v>
       </c>
       <c r="R73" t="n">
-        <v>6396572</v>
+        <v>6396809</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8493,7 +8493,7 @@
         <v>128884868</v>
       </c>
       <c r="B74" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>128884867</v>
       </c>
       <c r="B76" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>128884890</v>
       </c>
       <c r="B77" t="n">
-        <v>105675</v>
+        <v>105682</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,48 +8878,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884873</v>
+        <v>128884296</v>
       </c>
       <c r="B78" t="n">
-        <v>90297</v>
+        <v>91013</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>705314</v>
+        <v>705419</v>
       </c>
       <c r="R78" t="n">
-        <v>6396809</v>
+        <v>6396769</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8949,75 +8946,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884296</v>
+        <v>128884873</v>
       </c>
       <c r="B79" t="n">
-        <v>91008</v>
+        <v>90302</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>705419</v>
+        <v>705314</v>
       </c>
       <c r="R79" t="n">
-        <v>6396769</v>
+        <v>6396809</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9047,39 +9056,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
         <v>128884299</v>
       </c>
       <c r="B80" t="n">
-        <v>86859</v>
+        <v>86860</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>128884305</v>
       </c>
       <c r="B81" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9300,48 +9300,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884881</v>
+        <v>128884866</v>
       </c>
       <c r="B82" t="n">
-        <v>86945</v>
+        <v>91013</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>705474</v>
+        <v>705433</v>
       </c>
       <c r="R82" t="n">
-        <v>6396574</v>
+        <v>6396684</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9382,7 +9379,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9401,45 +9397,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128884866</v>
+        <v>128884881</v>
       </c>
       <c r="B83" t="n">
-        <v>91008</v>
+        <v>86946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>705433</v>
+        <v>705474</v>
       </c>
       <c r="R83" t="n">
-        <v>6396684</v>
+        <v>6396574</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9480,6 +9479,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9595,45 +9595,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884862</v>
+        <v>128889624</v>
       </c>
       <c r="B85" t="n">
-        <v>87003</v>
+        <v>90302</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3767</v>
+        <v>2072</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705398</v>
+        <v>705513</v>
       </c>
       <c r="R85" t="n">
-        <v>6396569</v>
+        <v>6396594</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,9 +9663,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9680,60 +9690,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884909</v>
+        <v>128884862</v>
       </c>
       <c r="B86" t="n">
-        <v>86713</v>
+        <v>87004</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705257</v>
+        <v>705398</v>
       </c>
       <c r="R86" t="n">
-        <v>6396921</v>
+        <v>6396569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9774,7 +9781,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9793,32 +9799,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128889624</v>
+        <v>128884300</v>
       </c>
       <c r="B87" t="n">
-        <v>90297</v>
+        <v>86806</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2072</v>
+        <v>424</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9828,10 +9834,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>705513</v>
+        <v>705540</v>
       </c>
       <c r="R87" t="n">
-        <v>6396594</v>
+        <v>6396625</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9863,7 +9869,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9873,7 +9879,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9900,32 +9906,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128884878</v>
+        <v>128884870</v>
       </c>
       <c r="B88" t="n">
-        <v>86958</v>
+        <v>86806</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9935,10 +9941,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>705291</v>
+        <v>705479</v>
       </c>
       <c r="R88" t="n">
-        <v>6396809</v>
+        <v>6396566</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9979,7 +9985,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9998,45 +10003,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128884870</v>
+        <v>128884298</v>
       </c>
       <c r="B89" t="n">
-        <v>86806</v>
+        <v>90302</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>2072</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>705479</v>
+        <v>705518</v>
       </c>
       <c r="R89" t="n">
-        <v>6396566</v>
+        <v>6396658</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10066,74 +10071,85 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884300</v>
+        <v>128884878</v>
       </c>
       <c r="B90" t="n">
-        <v>86806</v>
+        <v>86959</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705540</v>
+        <v>705291</v>
       </c>
       <c r="R90" t="n">
-        <v>6396625</v>
+        <v>6396809</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10163,84 +10179,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884298</v>
+        <v>128884864</v>
       </c>
       <c r="B91" t="n">
-        <v>90297</v>
+        <v>91013</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705518</v>
+        <v>705252</v>
       </c>
       <c r="R91" t="n">
-        <v>6396658</v>
+        <v>6396894</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10270,19 +10277,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10298,57 +10295,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884907</v>
+        <v>128884896</v>
       </c>
       <c r="B92" t="n">
-        <v>90240</v>
+        <v>92830</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>970</v>
+        <v>5964</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705399</v>
+        <v>705227</v>
       </c>
       <c r="R92" t="n">
-        <v>6396889</v>
+        <v>6396932</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10408,48 +10408,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884896</v>
+        <v>128884304</v>
       </c>
       <c r="B93" t="n">
-        <v>92823</v>
+        <v>86946</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705227</v>
+        <v>705475</v>
       </c>
       <c r="R93" t="n">
-        <v>6396932</v>
+        <v>6396577</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10479,62 +10476,71 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884864</v>
+        <v>128884907</v>
       </c>
       <c r="B94" t="n">
-        <v>91008</v>
+        <v>90245</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10544,10 +10550,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705252</v>
+        <v>705399</v>
       </c>
       <c r="R94" t="n">
-        <v>6396894</v>
+        <v>6396889</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10607,45 +10613,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884304</v>
+        <v>128884915</v>
       </c>
       <c r="B95" t="n">
-        <v>86945</v>
+        <v>86713</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3599</v>
+        <v>249278</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705475</v>
+        <v>705291</v>
       </c>
       <c r="R95" t="n">
-        <v>6396577</v>
+        <v>6396949</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10675,19 +10681,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10702,12 +10698,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10717,7 +10713,7 @@
         <v>128884876</v>
       </c>
       <c r="B96" t="n">
-        <v>90297</v>
+        <v>90302</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10815,10 +10811,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884915</v>
+        <v>128884306</v>
       </c>
       <c r="B97" t="n">
-        <v>86713</v>
+        <v>86860</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10826,34 +10822,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705291</v>
+        <v>705439</v>
       </c>
       <c r="R97" t="n">
-        <v>6396949</v>
+        <v>6396582</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10883,29 +10882,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10915,7 +10925,7 @@
         <v>128884900</v>
       </c>
       <c r="B98" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11013,32 +11023,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884306</v>
+        <v>128884899</v>
       </c>
       <c r="B99" t="n">
-        <v>86859</v>
+        <v>92830</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11047,14 +11057,14 @@
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705439</v>
+        <v>705436</v>
       </c>
       <c r="R99" t="n">
-        <v>6396582</v>
+        <v>6396834</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11084,19 +11094,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11112,57 +11112,60 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884303</v>
+        <v>128884897</v>
       </c>
       <c r="B100" t="n">
-        <v>86859</v>
+        <v>92830</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705477</v>
+        <v>705297</v>
       </c>
       <c r="R100" t="n">
-        <v>6396583</v>
+        <v>6396949</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11192,49 +11195,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884913</v>
+        <v>128884303</v>
       </c>
       <c r="B101" t="n">
-        <v>86713</v>
+        <v>86860</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11242,34 +11236,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705414</v>
+        <v>705477</v>
       </c>
       <c r="R101" t="n">
-        <v>6396611</v>
+        <v>6396583</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11299,78 +11293,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884897</v>
+        <v>128884913</v>
       </c>
       <c r="B102" t="n">
-        <v>92823</v>
+        <v>86713</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705297</v>
+        <v>705414</v>
       </c>
       <c r="R102" t="n">
-        <v>6396949</v>
+        <v>6396611</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11430,48 +11430,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128884899</v>
+        <v>128884910</v>
       </c>
       <c r="B103" t="n">
-        <v>92823</v>
+        <v>86713</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>705436</v>
+        <v>705273</v>
       </c>
       <c r="R103" t="n">
-        <v>6396834</v>
+        <v>6396934</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11531,45 +11528,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128884910</v>
+        <v>128884874</v>
       </c>
       <c r="B104" t="n">
-        <v>86713</v>
+        <v>90302</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>705273</v>
+        <v>705425</v>
       </c>
       <c r="R104" t="n">
-        <v>6396934</v>
+        <v>6396850</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11629,7 +11629,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884911</v>
+        <v>128884908</v>
       </c>
       <c r="B105" t="n">
         <v>86713</v>
@@ -11664,10 +11664,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705527</v>
+        <v>705320</v>
       </c>
       <c r="R105" t="n">
-        <v>6396694</v>
+        <v>6396829</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11727,48 +11727,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128884874</v>
+        <v>128884911</v>
       </c>
       <c r="B106" t="n">
-        <v>90297</v>
+        <v>86713</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>705425</v>
+        <v>705527</v>
       </c>
       <c r="R106" t="n">
-        <v>6396850</v>
+        <v>6396694</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11828,45 +11825,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128884908</v>
+        <v>128884877</v>
       </c>
       <c r="B107" t="n">
-        <v>86713</v>
+        <v>91039</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>249278</v>
+        <v>5747</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>705320</v>
+        <v>705444</v>
       </c>
       <c r="R107" t="n">
-        <v>6396829</v>
+        <v>6396874</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11901,6 +11901,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Kollekt taget</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11919,10 +11924,222 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128906402</v>
+      </c>
+      <c r="B108" t="n">
+        <v>86960</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>467</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Rostspindling</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Cortinarius russus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Bro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>705408</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6396839</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128884909</v>
+      </c>
+      <c r="B109" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>705257</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6396921</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY107" t="inlineStr"/>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AY143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6291,48 +6291,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884885</v>
+        <v>128884883</v>
       </c>
       <c r="B52" t="n">
-        <v>86860</v>
+        <v>86758</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3611</v>
+        <v>1985</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705360</v>
+        <v>705450</v>
       </c>
       <c r="R52" t="n">
-        <v>6396790</v>
+        <v>6396748</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6392,7 +6389,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884883</v>
+        <v>128884302</v>
       </c>
       <c r="B53" t="n">
         <v>86758</v>
@@ -6423,14 +6420,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705450</v>
+        <v>705513</v>
       </c>
       <c r="R53" t="n">
-        <v>6396748</v>
+        <v>6396594</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6460,75 +6457,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884302</v>
+        <v>128884885</v>
       </c>
       <c r="B54" t="n">
-        <v>86758</v>
+        <v>86860</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1985</v>
+        <v>3611</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>705513</v>
+        <v>705360</v>
       </c>
       <c r="R54" t="n">
-        <v>6396594</v>
+        <v>6396790</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,39 +6567,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6704,32 +6704,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884863</v>
+        <v>128884894</v>
       </c>
       <c r="B56" t="n">
-        <v>92201</v>
+        <v>90965</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705446</v>
+        <v>705317</v>
       </c>
       <c r="R56" t="n">
-        <v>6396726</v>
+        <v>6396863</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,32 +6801,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884894</v>
+        <v>128884863</v>
       </c>
       <c r="B57" t="n">
-        <v>90965</v>
+        <v>92201</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705317</v>
+        <v>705446</v>
       </c>
       <c r="R57" t="n">
-        <v>6396863</v>
+        <v>6396726</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884887</v>
+        <v>128884906</v>
       </c>
       <c r="B58" t="n">
-        <v>86935</v>
+        <v>92136</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1988</v>
+        <v>6031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705305</v>
+        <v>705291</v>
       </c>
       <c r="R58" t="n">
-        <v>6396830</v>
+        <v>6396952</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6995,10 +6995,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884906</v>
+        <v>128884884</v>
       </c>
       <c r="B59" t="n">
-        <v>92136</v>
+        <v>91013</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7006,21 +7006,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6031</v>
+        <v>5741</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705291</v>
+        <v>705475</v>
       </c>
       <c r="R59" t="n">
-        <v>6396952</v>
+        <v>6396574</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7074,6 +7074,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7199,10 +7200,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884872</v>
+        <v>128884887</v>
       </c>
       <c r="B61" t="n">
-        <v>92806</v>
+        <v>86935</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7210,21 +7211,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>1988</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7234,10 +7235,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705338</v>
+        <v>705305</v>
       </c>
       <c r="R61" t="n">
-        <v>6396936</v>
+        <v>6396830</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7296,10 +7297,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884884</v>
+        <v>128884872</v>
       </c>
       <c r="B62" t="n">
-        <v>91013</v>
+        <v>92806</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7307,21 +7308,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7331,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705475</v>
+        <v>705338</v>
       </c>
       <c r="R62" t="n">
-        <v>6396574</v>
+        <v>6396936</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7375,7 +7376,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7501,45 +7501,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884294</v>
+        <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>86713</v>
+        <v>90302</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705415</v>
+        <v>705428</v>
       </c>
       <c r="R64" t="n">
-        <v>6396763</v>
+        <v>6396833</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,47 +7569,36 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884912</v>
+        <v>128884294</v>
       </c>
       <c r="B65" t="n">
         <v>86713</v>
@@ -7640,14 +7629,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705461</v>
+        <v>705415</v>
       </c>
       <c r="R65" t="n">
-        <v>6396579</v>
+        <v>6396763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7677,9 +7666,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7695,44 +7694,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884875</v>
+        <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>90302</v>
+        <v>86713</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7742,10 +7741,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705428</v>
+        <v>705461</v>
       </c>
       <c r="R66" t="n">
-        <v>6396833</v>
+        <v>6396579</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7786,6 +7785,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884882</v>
+        <v>128889624</v>
       </c>
       <c r="B84" t="n">
-        <v>86758</v>
+        <v>90302</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1985</v>
+        <v>2072</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705380</v>
+        <v>705513</v>
       </c>
       <c r="R84" t="n">
-        <v>6396917</v>
+        <v>6396594</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,9 +9566,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9583,57 +9593,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128889624</v>
+        <v>128884862</v>
       </c>
       <c r="B85" t="n">
-        <v>90302</v>
+        <v>87004</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2072</v>
+        <v>3767</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705513</v>
+        <v>705398</v>
       </c>
       <c r="R85" t="n">
-        <v>6396594</v>
+        <v>6396569</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,19 +9673,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,22 +9690,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884862</v>
+        <v>128884882</v>
       </c>
       <c r="B86" t="n">
-        <v>87004</v>
+        <v>86758</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705398</v>
+        <v>705380</v>
       </c>
       <c r="R86" t="n">
-        <v>6396569</v>
+        <v>6396917</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10003,45 +10003,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128884298</v>
+        <v>128884878</v>
       </c>
       <c r="B89" t="n">
-        <v>90302</v>
+        <v>86959</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2072</v>
+        <v>6003295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>705518</v>
+        <v>705291</v>
       </c>
       <c r="R89" t="n">
-        <v>6396658</v>
+        <v>6396809</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10071,19 +10071,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10099,22 +10089,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884878</v>
+        <v>128884907</v>
       </c>
       <c r="B90" t="n">
-        <v>86959</v>
+        <v>90245</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10122,21 +10112,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6003295</v>
+        <v>970</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10146,10 +10136,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705291</v>
+        <v>705399</v>
       </c>
       <c r="R90" t="n">
-        <v>6396809</v>
+        <v>6396889</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10209,45 +10199,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884864</v>
+        <v>128884304</v>
       </c>
       <c r="B91" t="n">
-        <v>91013</v>
+        <v>86946</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705252</v>
+        <v>705475</v>
       </c>
       <c r="R91" t="n">
-        <v>6396894</v>
+        <v>6396577</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10277,30 +10267,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10408,45 +10407,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884304</v>
+        <v>128884864</v>
       </c>
       <c r="B93" t="n">
-        <v>86946</v>
+        <v>91013</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705475</v>
+        <v>705252</v>
       </c>
       <c r="R93" t="n">
-        <v>6396577</v>
+        <v>6396894</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10476,84 +10475,78 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884907</v>
+        <v>128884900</v>
       </c>
       <c r="B94" t="n">
-        <v>90245</v>
+        <v>92830</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>970</v>
+        <v>5964</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705399</v>
+        <v>705445</v>
       </c>
       <c r="R94" t="n">
-        <v>6396889</v>
+        <v>6396819</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10613,45 +10606,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884915</v>
+        <v>128884876</v>
       </c>
       <c r="B95" t="n">
-        <v>86713</v>
+        <v>90302</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705291</v>
+        <v>705430</v>
       </c>
       <c r="R95" t="n">
-        <v>6396949</v>
+        <v>6396834</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10692,6 +10688,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10710,32 +10707,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884876</v>
+        <v>128884306</v>
       </c>
       <c r="B96" t="n">
-        <v>90302</v>
+        <v>86860</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2072</v>
+        <v>3611</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10744,14 +10741,14 @@
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705430</v>
+        <v>705439</v>
       </c>
       <c r="R96" t="n">
-        <v>6396834</v>
+        <v>6396582</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10781,9 +10778,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10799,22 +10806,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884306</v>
+        <v>128884915</v>
       </c>
       <c r="B97" t="n">
-        <v>86860</v>
+        <v>86713</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10822,37 +10829,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705439</v>
+        <v>705291</v>
       </c>
       <c r="R97" t="n">
-        <v>6396582</v>
+        <v>6396949</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10882,88 +10886,74 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884900</v>
+        <v>128884913</v>
       </c>
       <c r="B98" t="n">
-        <v>92830</v>
+        <v>86713</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705445</v>
+        <v>705414</v>
       </c>
       <c r="R98" t="n">
-        <v>6396819</v>
+        <v>6396611</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11023,48 +11013,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884899</v>
+        <v>128884910</v>
       </c>
       <c r="B99" t="n">
-        <v>92830</v>
+        <v>86713</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705436</v>
+        <v>705273</v>
       </c>
       <c r="R99" t="n">
-        <v>6396834</v>
+        <v>6396934</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11124,48 +11111,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884897</v>
+        <v>128884303</v>
       </c>
       <c r="B100" t="n">
-        <v>92830</v>
+        <v>86860</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705297</v>
+        <v>705477</v>
       </c>
       <c r="R100" t="n">
-        <v>6396949</v>
+        <v>6396583</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11195,75 +11179,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884303</v>
+        <v>128884897</v>
       </c>
       <c r="B101" t="n">
-        <v>86860</v>
+        <v>92830</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705477</v>
+        <v>705297</v>
       </c>
       <c r="R101" t="n">
-        <v>6396583</v>
+        <v>6396949</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11293,84 +11289,78 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884913</v>
+        <v>128884899</v>
       </c>
       <c r="B102" t="n">
-        <v>86713</v>
+        <v>92830</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705414</v>
+        <v>705436</v>
       </c>
       <c r="R102" t="n">
-        <v>6396611</v>
+        <v>6396834</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11430,45 +11420,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128884910</v>
+        <v>128884874</v>
       </c>
       <c r="B103" t="n">
-        <v>86713</v>
+        <v>90302</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>705273</v>
+        <v>705425</v>
       </c>
       <c r="R103" t="n">
-        <v>6396934</v>
+        <v>6396850</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11528,48 +11521,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128884874</v>
+        <v>128884908</v>
       </c>
       <c r="B104" t="n">
-        <v>90302</v>
+        <v>86713</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>705425</v>
+        <v>705320</v>
       </c>
       <c r="R104" t="n">
-        <v>6396850</v>
+        <v>6396829</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11629,7 +11619,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884908</v>
+        <v>128884911</v>
       </c>
       <c r="B105" t="n">
         <v>86713</v>
@@ -11664,10 +11654,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705320</v>
+        <v>705527</v>
       </c>
       <c r="R105" t="n">
-        <v>6396829</v>
+        <v>6396694</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11727,45 +11717,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128884911</v>
+        <v>128884877</v>
       </c>
       <c r="B106" t="n">
-        <v>86713</v>
+        <v>91039</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>249278</v>
+        <v>5747</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>705527</v>
+        <v>705444</v>
       </c>
       <c r="R106" t="n">
-        <v>6396694</v>
+        <v>6396874</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11800,6 +11793,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Kollekt taget</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -11818,17 +11816,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128884877</v>
+        <v>128906402</v>
       </c>
       <c r="B107" t="n">
-        <v>91039</v>
+        <v>86960</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11836,21 +11834,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5747</v>
+        <v>467</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Rostspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11859,14 +11857,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>705444</v>
+        <v>705408</v>
       </c>
       <c r="R107" t="n">
-        <v>6396874</v>
+        <v>6396839</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11896,14 +11894,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Kollekt taget</t>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11919,44 +11922,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128906402</v>
+        <v>128884909</v>
       </c>
       <c r="B108" t="n">
-        <v>86960</v>
+        <v>86713</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>467</v>
+        <v>249278</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rostspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11965,14 +11968,14 @@
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>705408</v>
+        <v>705257</v>
       </c>
       <c r="R108" t="n">
-        <v>6396839</v>
+        <v>6396921</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12002,19 +12005,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12030,19 +12023,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128884909</v>
+        <v>128912419</v>
       </c>
       <c r="B109" t="n">
         <v>86713</v>
@@ -12071,19 +12064,16 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705257</v>
+        <v>705420</v>
       </c>
       <c r="R109" t="n">
-        <v>6396921</v>
+        <v>6396917</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12124,22 +12114,3338 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128912424</v>
+      </c>
+      <c r="B110" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>705432</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6396615</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128912420</v>
+      </c>
+      <c r="B111" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>705443</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6396921</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128912404</v>
+      </c>
+      <c r="B112" t="n">
+        <v>86758</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mörkfjällig olivspindling</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Cortinarius melanotus</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>705405</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6396928</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128912417</v>
+      </c>
+      <c r="B113" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>705276</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6396964</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128912385</v>
+      </c>
+      <c r="B114" t="n">
+        <v>90302</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>705424</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6396848</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>3 st</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128912405</v>
+      </c>
+      <c r="B115" t="n">
+        <v>86860</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>705428</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6396801</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128912408</v>
+      </c>
+      <c r="B116" t="n">
+        <v>86860</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>705452</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6396728</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128912422</v>
+      </c>
+      <c r="B117" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>705469</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6396714</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128912388</v>
+      </c>
+      <c r="B118" t="n">
+        <v>90302</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>705434</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6396836</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128912380</v>
+      </c>
+      <c r="B119" t="n">
+        <v>91013</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>705428</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6396581</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128912402</v>
+      </c>
+      <c r="B120" t="n">
+        <v>86758</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Mörkfjällig olivspindling</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Cortinarius melanotus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>705258</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6396989</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128912379</v>
+      </c>
+      <c r="B121" t="n">
+        <v>91013</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>705404</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6396616</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128912421</v>
+      </c>
+      <c r="B122" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>705425</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6396872</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128912384</v>
+      </c>
+      <c r="B123" t="n">
+        <v>90291</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6268</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Rökmusseron</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Tricholoma fucatum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>705294</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6396977</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128912411</v>
+      </c>
+      <c r="B124" t="n">
+        <v>86981</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>449</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>705471</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6396777</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128912425</v>
+      </c>
+      <c r="B125" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>705415</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6396600</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128912416</v>
+      </c>
+      <c r="B126" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>705273</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6396936</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128912398</v>
+      </c>
+      <c r="B127" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>705492</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6396758</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128912394</v>
+      </c>
+      <c r="B128" t="n">
+        <v>86760</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>705421</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6396928</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128912406</v>
+      </c>
+      <c r="B129" t="n">
+        <v>86860</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>705470</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6396774</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128912410</v>
+      </c>
+      <c r="B130" t="n">
+        <v>86981</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>449</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>705430</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6396796</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128912423</v>
+      </c>
+      <c r="B131" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>705462</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6396694</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128912390</v>
+      </c>
+      <c r="B132" t="n">
+        <v>90302</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>705454</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6396691</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128912407</v>
+      </c>
+      <c r="B133" t="n">
+        <v>86860</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>705495</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6396756</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128912382</v>
+      </c>
+      <c r="B134" t="n">
+        <v>92808</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>705322</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6396888</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128912412</v>
+      </c>
+      <c r="B135" t="n">
+        <v>90965</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>705316</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6396862</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128912395</v>
+      </c>
+      <c r="B136" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>705266</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6396904</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128912396</v>
+      </c>
+      <c r="B137" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>705284</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6396977</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128912401</v>
+      </c>
+      <c r="B138" t="n">
+        <v>86758</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Mörkfjällig olivspindling</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Cortinarius melanotus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>705317</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6396871</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128912418</v>
+      </c>
+      <c r="B139" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>705286</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6396970</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128912409</v>
+      </c>
+      <c r="B140" t="n">
+        <v>86935</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>705284</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6396861</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128912415</v>
+      </c>
+      <c r="B141" t="n">
+        <v>86713</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>705249</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6396927</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128912399</v>
+      </c>
+      <c r="B142" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>705482</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6396750</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128912403</v>
+      </c>
+      <c r="B143" t="n">
+        <v>86758</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Mörkfjällig olivspindling</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Cortinarius melanotus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Bro Ytlings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>705401</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6396966</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6898,10 +6898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884906</v>
+        <v>128884872</v>
       </c>
       <c r="B58" t="n">
-        <v>92136</v>
+        <v>92806</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6031</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705291</v>
+        <v>705338</v>
       </c>
       <c r="R58" t="n">
-        <v>6396952</v>
+        <v>6396936</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6995,10 +6995,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884884</v>
+        <v>128884887</v>
       </c>
       <c r="B59" t="n">
-        <v>91013</v>
+        <v>86935</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7006,21 +7006,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5741</v>
+        <v>1988</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705475</v>
+        <v>705305</v>
       </c>
       <c r="R59" t="n">
-        <v>6396574</v>
+        <v>6396830</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7074,7 +7074,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7093,45 +7092,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884301</v>
+        <v>128884884</v>
       </c>
       <c r="B60" t="n">
-        <v>91039</v>
+        <v>91013</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>5741</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705546</v>
+        <v>705475</v>
       </c>
       <c r="R60" t="n">
-        <v>6396613</v>
+        <v>6396574</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7161,84 +7160,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884887</v>
+        <v>128884301</v>
       </c>
       <c r="B61" t="n">
-        <v>86935</v>
+        <v>91039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1988</v>
+        <v>5747</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705305</v>
+        <v>705546</v>
       </c>
       <c r="R61" t="n">
-        <v>6396830</v>
+        <v>6396613</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7268,9 +7258,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7285,22 +7285,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884872</v>
+        <v>128884906</v>
       </c>
       <c r="B62" t="n">
-        <v>92806</v>
+        <v>92136</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>6031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705338</v>
+        <v>705291</v>
       </c>
       <c r="R62" t="n">
-        <v>6396936</v>
+        <v>6396952</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884294</v>
+        <v>128884879</v>
       </c>
       <c r="B65" t="n">
-        <v>86713</v>
+        <v>86959</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7609,34 +7609,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705415</v>
+        <v>705537</v>
       </c>
       <c r="R65" t="n">
-        <v>6396763</v>
+        <v>6396616</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7666,19 +7666,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7694,19 +7684,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884912</v>
+        <v>128884294</v>
       </c>
       <c r="B66" t="n">
         <v>86713</v>
@@ -7737,14 +7727,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705461</v>
+        <v>705415</v>
       </c>
       <c r="R66" t="n">
-        <v>6396579</v>
+        <v>6396763</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7774,9 +7764,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7792,22 +7792,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884879</v>
+        <v>128884912</v>
       </c>
       <c r="B67" t="n">
-        <v>86959</v>
+        <v>86713</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705537</v>
+        <v>705461</v>
       </c>
       <c r="R67" t="n">
-        <v>6396616</v>
+        <v>6396579</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884871</v>
+        <v>128884865</v>
       </c>
       <c r="B70" t="n">
-        <v>87025</v>
+        <v>91013</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,19 +8108,23 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3624</v>
+        <v>5741</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8128,10 +8132,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705290</v>
+        <v>705416</v>
       </c>
       <c r="R70" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8172,6 +8176,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8190,32 +8195,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884886</v>
+        <v>128884898</v>
       </c>
       <c r="B71" t="n">
-        <v>86860</v>
+        <v>92830</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705473</v>
+        <v>705425</v>
       </c>
       <c r="R71" t="n">
-        <v>6396572</v>
+        <v>6396809</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8291,10 +8296,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884865</v>
+        <v>128884871</v>
       </c>
       <c r="B72" t="n">
-        <v>91013</v>
+        <v>87025</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8302,23 +8307,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5741</v>
+        <v>3624</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8326,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705416</v>
+        <v>705290</v>
       </c>
       <c r="R72" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8370,7 +8371,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884898</v>
+        <v>128884886</v>
       </c>
       <c r="B73" t="n">
-        <v>92830</v>
+        <v>86860</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705425</v>
+        <v>705473</v>
       </c>
       <c r="R73" t="n">
-        <v>6396809</v>
+        <v>6396572</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8878,45 +8878,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884296</v>
+        <v>128884873</v>
       </c>
       <c r="B78" t="n">
-        <v>91013</v>
+        <v>90302</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>705419</v>
+        <v>705314</v>
       </c>
       <c r="R78" t="n">
-        <v>6396769</v>
+        <v>6396809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8946,87 +8949,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884873</v>
+        <v>128884296</v>
       </c>
       <c r="B79" t="n">
-        <v>90302</v>
+        <v>91013</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>705314</v>
+        <v>705419</v>
       </c>
       <c r="R79" t="n">
-        <v>6396809</v>
+        <v>6396769</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9056,30 +9047,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9193,45 +9193,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884305</v>
+        <v>128884881</v>
       </c>
       <c r="B81" t="n">
-        <v>91013</v>
+        <v>86946</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>705468</v>
+        <v>705474</v>
       </c>
       <c r="R81" t="n">
-        <v>6396595</v>
+        <v>6396574</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9261,46 +9264,37 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884866</v>
+        <v>128884305</v>
       </c>
       <c r="B82" t="n">
         <v>91013</v>
@@ -9331,14 +9325,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>705433</v>
+        <v>705468</v>
       </c>
       <c r="R82" t="n">
-        <v>6396684</v>
+        <v>6396595</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9368,9 +9362,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9385,60 +9389,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128884881</v>
+        <v>128884866</v>
       </c>
       <c r="B83" t="n">
-        <v>86946</v>
+        <v>91013</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>705474</v>
+        <v>705433</v>
       </c>
       <c r="R83" t="n">
-        <v>6396574</v>
+        <v>6396684</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9479,7 +9480,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128889624</v>
+        <v>128884862</v>
       </c>
       <c r="B84" t="n">
-        <v>90302</v>
+        <v>87004</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2072</v>
+        <v>3767</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705513</v>
+        <v>705398</v>
       </c>
       <c r="R84" t="n">
-        <v>6396594</v>
+        <v>6396569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,19 +9566,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9593,57 +9583,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884862</v>
+        <v>128889624</v>
       </c>
       <c r="B85" t="n">
-        <v>87004</v>
+        <v>90302</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3767</v>
+        <v>2072</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705398</v>
+        <v>705513</v>
       </c>
       <c r="R85" t="n">
-        <v>6396569</v>
+        <v>6396594</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9673,9 +9663,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,12 +9690,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10101,45 +10101,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884907</v>
+        <v>128884304</v>
       </c>
       <c r="B90" t="n">
-        <v>90245</v>
+        <v>86946</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>970</v>
+        <v>3599</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705399</v>
+        <v>705475</v>
       </c>
       <c r="R90" t="n">
-        <v>6396889</v>
+        <v>6396577</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10169,75 +10169,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884304</v>
+        <v>128884907</v>
       </c>
       <c r="B91" t="n">
-        <v>86946</v>
+        <v>90245</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3599</v>
+        <v>970</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705475</v>
+        <v>705399</v>
       </c>
       <c r="R91" t="n">
-        <v>6396577</v>
+        <v>6396889</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10267,49 +10276,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884896</v>
+        <v>128884864</v>
       </c>
       <c r="B92" t="n">
-        <v>92830</v>
+        <v>91013</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10317,37 +10317,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705227</v>
+        <v>705252</v>
       </c>
       <c r="R92" t="n">
-        <v>6396932</v>
+        <v>6396894</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10407,10 +10404,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884864</v>
+        <v>128884896</v>
       </c>
       <c r="B93" t="n">
-        <v>91013</v>
+        <v>92830</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10418,34 +10415,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705252</v>
+        <v>705227</v>
       </c>
       <c r="R93" t="n">
-        <v>6396894</v>
+        <v>6396932</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10505,32 +10505,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884900</v>
+        <v>128884876</v>
       </c>
       <c r="B94" t="n">
-        <v>92830</v>
+        <v>90302</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5964</v>
+        <v>2072</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705445</v>
+        <v>705430</v>
       </c>
       <c r="R94" t="n">
-        <v>6396819</v>
+        <v>6396834</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10606,48 +10606,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884876</v>
+        <v>128884915</v>
       </c>
       <c r="B95" t="n">
-        <v>90302</v>
+        <v>86713</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705430</v>
+        <v>705291</v>
       </c>
       <c r="R95" t="n">
-        <v>6396834</v>
+        <v>6396949</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10688,7 +10685,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10818,45 +10814,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884915</v>
+        <v>128884900</v>
       </c>
       <c r="B97" t="n">
-        <v>86713</v>
+        <v>92830</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705291</v>
+        <v>705445</v>
       </c>
       <c r="R97" t="n">
-        <v>6396949</v>
+        <v>6396819</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10897,6 +10896,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11218,7 +11218,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884897</v>
+        <v>128884899</v>
       </c>
       <c r="B101" t="n">
         <v>92830</v>
@@ -11256,10 +11256,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705297</v>
+        <v>705436</v>
       </c>
       <c r="R101" t="n">
-        <v>6396949</v>
+        <v>6396834</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11319,7 +11319,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884899</v>
+        <v>128884897</v>
       </c>
       <c r="B102" t="n">
         <v>92830</v>
@@ -11357,10 +11357,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705436</v>
+        <v>705297</v>
       </c>
       <c r="R102" t="n">
-        <v>6396834</v>
+        <v>6396949</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912419</v>
+        <v>128912404</v>
       </c>
       <c r="B109" t="n">
-        <v>86713</v>
+        <v>86758</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705420</v>
+        <v>705405</v>
       </c>
       <c r="R109" t="n">
-        <v>6396917</v>
+        <v>6396928</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912424</v>
+        <v>128912420</v>
       </c>
       <c r="B110" t="n">
         <v>86713</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705432</v>
+        <v>705443</v>
       </c>
       <c r="R110" t="n">
-        <v>6396615</v>
+        <v>6396921</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,7 +12229,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912420</v>
+        <v>128912417</v>
       </c>
       <c r="B111" t="n">
         <v>86713</v>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705443</v>
+        <v>705276</v>
       </c>
       <c r="R111" t="n">
-        <v>6396921</v>
+        <v>6396964</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,32 +12326,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912404</v>
+        <v>128912419</v>
       </c>
       <c r="B112" t="n">
-        <v>86758</v>
+        <v>86713</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705405</v>
+        <v>705420</v>
       </c>
       <c r="R112" t="n">
-        <v>6396928</v>
+        <v>6396917</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,7 +12423,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912417</v>
+        <v>128912424</v>
       </c>
       <c r="B113" t="n">
         <v>86713</v>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705276</v>
+        <v>705432</v>
       </c>
       <c r="R113" t="n">
-        <v>6396964</v>
+        <v>6396615</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12816,32 +12816,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128912422</v>
+        <v>128912388</v>
       </c>
       <c r="B117" t="n">
-        <v>86713</v>
+        <v>90302</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12851,10 +12851,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>705469</v>
+        <v>705434</v>
       </c>
       <c r="R117" t="n">
-        <v>6396714</v>
+        <v>6396836</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12887,6 +12887,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12913,32 +12918,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128912388</v>
+        <v>128912380</v>
       </c>
       <c r="B118" t="n">
-        <v>90302</v>
+        <v>91013</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12948,10 +12953,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>705434</v>
+        <v>705428</v>
       </c>
       <c r="R118" t="n">
-        <v>6396836</v>
+        <v>6396581</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12984,11 +12989,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>4 st</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13015,32 +13015,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128912380</v>
+        <v>128912422</v>
       </c>
       <c r="B119" t="n">
-        <v>91013</v>
+        <v>86713</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5741</v>
+        <v>249278</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13050,10 +13050,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>705428</v>
+        <v>705469</v>
       </c>
       <c r="R119" t="n">
-        <v>6396581</v>
+        <v>6396714</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13209,32 +13209,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128912379</v>
+        <v>128912421</v>
       </c>
       <c r="B121" t="n">
-        <v>91013</v>
+        <v>86713</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5741</v>
+        <v>249278</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13244,10 +13244,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>705404</v>
+        <v>705425</v>
       </c>
       <c r="R121" t="n">
-        <v>6396616</v>
+        <v>6396872</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13306,32 +13306,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912421</v>
+        <v>128912379</v>
       </c>
       <c r="B122" t="n">
-        <v>86713</v>
+        <v>91013</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>249278</v>
+        <v>5741</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13341,10 +13341,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705425</v>
+        <v>705404</v>
       </c>
       <c r="R122" t="n">
-        <v>6396872</v>
+        <v>6396616</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13995,32 +13995,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912406</v>
+        <v>128912410</v>
       </c>
       <c r="B129" t="n">
-        <v>86860</v>
+        <v>86981</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3611</v>
+        <v>449</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705470</v>
+        <v>705430</v>
       </c>
       <c r="R129" t="n">
-        <v>6396774</v>
+        <v>6396796</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,32 +14092,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912410</v>
+        <v>128912406</v>
       </c>
       <c r="B130" t="n">
-        <v>86981</v>
+        <v>86860</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>449</v>
+        <v>3611</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705430</v>
+        <v>705470</v>
       </c>
       <c r="R130" t="n">
-        <v>6396796</v>
+        <v>6396774</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14480,30 +14480,34 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128912382</v>
+        <v>128912412</v>
       </c>
       <c r="B134" t="n">
-        <v>92808</v>
+        <v>90965</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6047725</v>
+        <v>3286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14511,10 +14515,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>705322</v>
+        <v>705316</v>
       </c>
       <c r="R134" t="n">
-        <v>6396888</v>
+        <v>6396862</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14573,34 +14577,30 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128912412</v>
+        <v>128912382</v>
       </c>
       <c r="B135" t="n">
-        <v>90965</v>
+        <v>92808</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14608,10 +14608,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>705316</v>
+        <v>705322</v>
       </c>
       <c r="R135" t="n">
-        <v>6396862</v>
+        <v>6396888</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15254,32 +15254,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128912399</v>
+        <v>128912403</v>
       </c>
       <c r="B142" t="n">
-        <v>86959</v>
+        <v>86758</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15289,10 +15289,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>705482</v>
+        <v>705401</v>
       </c>
       <c r="R142" t="n">
-        <v>6396750</v>
+        <v>6396966</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15333,7 +15333,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15352,32 +15351,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128912403</v>
+        <v>128912399</v>
       </c>
       <c r="B143" t="n">
-        <v>86758</v>
+        <v>86959</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15387,10 +15386,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>705401</v>
+        <v>705482</v>
       </c>
       <c r="R143" t="n">
-        <v>6396966</v>
+        <v>6396750</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15431,6 +15430,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6294,7 +6294,7 @@
         <v>128884883</v>
       </c>
       <c r="B52" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>128884302</v>
       </c>
       <c r="B53" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>128884885</v>
       </c>
       <c r="B54" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>128889600</v>
       </c>
       <c r="B55" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,32 +6704,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884894</v>
+        <v>128884887</v>
       </c>
       <c r="B56" t="n">
-        <v>90965</v>
+        <v>86939</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>1988</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705317</v>
+        <v>705305</v>
       </c>
       <c r="R56" t="n">
-        <v>6396863</v>
+        <v>6396830</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,10 +6801,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884863</v>
+        <v>128884906</v>
       </c>
       <c r="B57" t="n">
-        <v>92201</v>
+        <v>92140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6812,21 +6812,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6031</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705446</v>
+        <v>705291</v>
       </c>
       <c r="R57" t="n">
-        <v>6396726</v>
+        <v>6396952</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884872</v>
+        <v>128884884</v>
       </c>
       <c r="B58" t="n">
-        <v>92806</v>
+        <v>91017</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705338</v>
+        <v>705475</v>
       </c>
       <c r="R58" t="n">
-        <v>6396936</v>
+        <v>6396574</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6977,6 +6977,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6995,45 +6996,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884887</v>
+        <v>128884301</v>
       </c>
       <c r="B59" t="n">
-        <v>86935</v>
+        <v>91043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1988</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705305</v>
+        <v>705546</v>
       </c>
       <c r="R59" t="n">
-        <v>6396830</v>
+        <v>6396613</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7063,9 +7064,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7080,22 +7091,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884884</v>
+        <v>128884872</v>
       </c>
       <c r="B60" t="n">
-        <v>91013</v>
+        <v>92810</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,21 +7114,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7127,10 +7138,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705475</v>
+        <v>705338</v>
       </c>
       <c r="R60" t="n">
-        <v>6396574</v>
+        <v>6396936</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7171,7 +7182,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7190,45 +7200,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884301</v>
+        <v>128884894</v>
       </c>
       <c r="B61" t="n">
-        <v>91039</v>
+        <v>90969</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705546</v>
+        <v>705317</v>
       </c>
       <c r="R61" t="n">
-        <v>6396613</v>
+        <v>6396863</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7258,19 +7268,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7285,22 +7285,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884906</v>
+        <v>128884863</v>
       </c>
       <c r="B62" t="n">
-        <v>92136</v>
+        <v>92205</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6031</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705291</v>
+        <v>705446</v>
       </c>
       <c r="R62" t="n">
-        <v>6396952</v>
+        <v>6396726</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7397,7 +7397,7 @@
         <v>128890120</v>
       </c>
       <c r="B63" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7501,45 +7501,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884875</v>
+        <v>128884294</v>
       </c>
       <c r="B64" t="n">
-        <v>90302</v>
+        <v>86717</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705428</v>
+        <v>705415</v>
       </c>
       <c r="R64" t="n">
-        <v>6396833</v>
+        <v>6396763</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,39 +7569,50 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884879</v>
+        <v>128884912</v>
       </c>
       <c r="B65" t="n">
-        <v>86959</v>
+        <v>86717</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7609,21 +7620,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7633,10 +7644,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705537</v>
+        <v>705461</v>
       </c>
       <c r="R65" t="n">
-        <v>6396616</v>
+        <v>6396579</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7696,10 +7707,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884294</v>
+        <v>128884879</v>
       </c>
       <c r="B66" t="n">
-        <v>86713</v>
+        <v>86963</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7707,34 +7718,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705415</v>
+        <v>705537</v>
       </c>
       <c r="R66" t="n">
-        <v>6396763</v>
+        <v>6396616</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7764,19 +7775,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7792,44 +7793,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884912</v>
+        <v>128884875</v>
       </c>
       <c r="B67" t="n">
-        <v>86713</v>
+        <v>90306</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7839,10 +7840,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705461</v>
+        <v>705428</v>
       </c>
       <c r="R67" t="n">
-        <v>6396579</v>
+        <v>6396833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7883,7 +7884,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>128884861</v>
       </c>
       <c r="B68" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>128884914</v>
       </c>
       <c r="B69" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884865</v>
+        <v>128884871</v>
       </c>
       <c r="B70" t="n">
-        <v>91013</v>
+        <v>87029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,23 +8108,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5741</v>
+        <v>3624</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8132,10 +8128,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705416</v>
+        <v>705290</v>
       </c>
       <c r="R70" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8176,7 +8172,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8195,32 +8190,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884898</v>
+        <v>128884886</v>
       </c>
       <c r="B71" t="n">
-        <v>92830</v>
+        <v>86864</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8233,10 +8228,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705425</v>
+        <v>705473</v>
       </c>
       <c r="R71" t="n">
-        <v>6396809</v>
+        <v>6396572</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8296,10 +8291,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884871</v>
+        <v>128884865</v>
       </c>
       <c r="B72" t="n">
-        <v>87025</v>
+        <v>91017</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8307,19 +8302,23 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3624</v>
+        <v>5741</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8327,10 +8326,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705290</v>
+        <v>705416</v>
       </c>
       <c r="R72" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8371,6 +8370,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884886</v>
+        <v>128884898</v>
       </c>
       <c r="B73" t="n">
-        <v>86860</v>
+        <v>92834</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705473</v>
+        <v>705425</v>
       </c>
       <c r="R73" t="n">
-        <v>6396572</v>
+        <v>6396809</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8493,7 +8493,7 @@
         <v>128884868</v>
       </c>
       <c r="B74" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884869</v>
+        <v>128884867</v>
       </c>
       <c r="B75" t="n">
-        <v>86806</v>
+        <v>91017</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>5741</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>705297</v>
+        <v>705431</v>
       </c>
       <c r="R75" t="n">
-        <v>6396817</v>
+        <v>6396688</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8684,32 +8684,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884867</v>
+        <v>128884869</v>
       </c>
       <c r="B76" t="n">
-        <v>91013</v>
+        <v>86810</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5741</v>
+        <v>424</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>705431</v>
+        <v>705297</v>
       </c>
       <c r="R76" t="n">
-        <v>6396688</v>
+        <v>6396817</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8784,7 +8784,7 @@
         <v>128884890</v>
       </c>
       <c r="B77" t="n">
-        <v>105682</v>
+        <v>105686</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>128884873</v>
       </c>
       <c r="B78" t="n">
-        <v>90302</v>
+        <v>90306</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>128884296</v>
       </c>
       <c r="B79" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>128884299</v>
       </c>
       <c r="B80" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>128884881</v>
       </c>
       <c r="B81" t="n">
-        <v>86946</v>
+        <v>86950</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>128884305</v>
       </c>
       <c r="B82" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>128884866</v>
       </c>
       <c r="B83" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884862</v>
+        <v>128889624</v>
       </c>
       <c r="B84" t="n">
-        <v>87004</v>
+        <v>90306</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3767</v>
+        <v>2072</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705398</v>
+        <v>705513</v>
       </c>
       <c r="R84" t="n">
-        <v>6396569</v>
+        <v>6396594</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,9 +9566,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9583,57 +9593,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128889624</v>
+        <v>128884882</v>
       </c>
       <c r="B85" t="n">
-        <v>90302</v>
+        <v>86762</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2072</v>
+        <v>1985</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705513</v>
+        <v>705380</v>
       </c>
       <c r="R85" t="n">
-        <v>6396594</v>
+        <v>6396917</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,19 +9673,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,22 +9690,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884882</v>
+        <v>128884862</v>
       </c>
       <c r="B86" t="n">
-        <v>86758</v>
+        <v>87008</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705380</v>
+        <v>705398</v>
       </c>
       <c r="R86" t="n">
-        <v>6396917</v>
+        <v>6396569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9802,7 +9802,7 @@
         <v>128884300</v>
       </c>
       <c r="B87" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>128884870</v>
       </c>
       <c r="B88" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>128884878</v>
       </c>
       <c r="B89" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>128884304</v>
       </c>
       <c r="B90" t="n">
-        <v>86946</v>
+        <v>86950</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10208,32 +10208,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884907</v>
+        <v>128884864</v>
       </c>
       <c r="B91" t="n">
-        <v>90245</v>
+        <v>91017</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>970</v>
+        <v>5741</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10243,10 +10243,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705399</v>
+        <v>705252</v>
       </c>
       <c r="R91" t="n">
-        <v>6396889</v>
+        <v>6396894</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884864</v>
+        <v>128884896</v>
       </c>
       <c r="B92" t="n">
-        <v>91013</v>
+        <v>92834</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10317,34 +10317,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705252</v>
+        <v>705227</v>
       </c>
       <c r="R92" t="n">
-        <v>6396894</v>
+        <v>6396932</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10404,48 +10407,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884896</v>
+        <v>128884907</v>
       </c>
       <c r="B93" t="n">
-        <v>92830</v>
+        <v>90249</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5964</v>
+        <v>970</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705227</v>
+        <v>705399</v>
       </c>
       <c r="R93" t="n">
-        <v>6396932</v>
+        <v>6396889</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
         <v>128884876</v>
       </c>
       <c r="B94" t="n">
-        <v>90302</v>
+        <v>90306</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10606,10 +10606,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884915</v>
+        <v>128884306</v>
       </c>
       <c r="B95" t="n">
-        <v>86713</v>
+        <v>86864</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10617,34 +10617,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705291</v>
+        <v>705439</v>
       </c>
       <c r="R95" t="n">
-        <v>6396949</v>
+        <v>6396582</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10674,61 +10677,72 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884306</v>
+        <v>128884900</v>
       </c>
       <c r="B96" t="n">
-        <v>86860</v>
+        <v>92834</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10737,14 +10751,14 @@
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705439</v>
+        <v>705445</v>
       </c>
       <c r="R96" t="n">
-        <v>6396582</v>
+        <v>6396819</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10774,19 +10788,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10802,60 +10806,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884900</v>
+        <v>128884915</v>
       </c>
       <c r="B97" t="n">
-        <v>92830</v>
+        <v>86717</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705445</v>
+        <v>705291</v>
       </c>
       <c r="R97" t="n">
-        <v>6396819</v>
+        <v>6396949</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10896,7 +10897,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>128884913</v>
       </c>
       <c r="B98" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>128884910</v>
       </c>
       <c r="B99" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11111,45 +11111,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884303</v>
+        <v>128884899</v>
       </c>
       <c r="B100" t="n">
-        <v>86860</v>
+        <v>92834</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705477</v>
+        <v>705436</v>
       </c>
       <c r="R100" t="n">
-        <v>6396583</v>
+        <v>6396834</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11179,49 +11182,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884899</v>
+        <v>128884897</v>
       </c>
       <c r="B101" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11256,10 +11250,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705436</v>
+        <v>705297</v>
       </c>
       <c r="R101" t="n">
-        <v>6396834</v>
+        <v>6396949</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11319,48 +11313,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884897</v>
+        <v>128884303</v>
       </c>
       <c r="B102" t="n">
-        <v>92830</v>
+        <v>86864</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705297</v>
+        <v>705477</v>
       </c>
       <c r="R102" t="n">
-        <v>6396949</v>
+        <v>6396583</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11390,30 +11381,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11423,7 +11423,7 @@
         <v>128884874</v>
       </c>
       <c r="B103" t="n">
-        <v>90302</v>
+        <v>90306</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>128884908</v>
       </c>
       <c r="B104" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>128884911</v>
       </c>
       <c r="B105" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>128884877</v>
       </c>
       <c r="B106" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>128906402</v>
       </c>
       <c r="B107" t="n">
-        <v>86960</v>
+        <v>86964</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>128884909</v>
       </c>
       <c r="B108" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>128912404</v>
       </c>
       <c r="B109" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12132,10 +12132,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912420</v>
+        <v>128912419</v>
       </c>
       <c r="B110" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705443</v>
+        <v>705420</v>
       </c>
       <c r="R110" t="n">
-        <v>6396921</v>
+        <v>6396917</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,10 +12229,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912417</v>
+        <v>128912424</v>
       </c>
       <c r="B111" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705276</v>
+        <v>705432</v>
       </c>
       <c r="R111" t="n">
-        <v>6396964</v>
+        <v>6396615</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912419</v>
+        <v>128912420</v>
       </c>
       <c r="B112" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705420</v>
+        <v>705443</v>
       </c>
       <c r="R112" t="n">
-        <v>6396917</v>
+        <v>6396921</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,10 +12423,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912424</v>
+        <v>128912417</v>
       </c>
       <c r="B113" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705432</v>
+        <v>705276</v>
       </c>
       <c r="R113" t="n">
-        <v>6396615</v>
+        <v>6396964</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
         <v>128912385</v>
       </c>
       <c r="B114" t="n">
-        <v>90302</v>
+        <v>90306</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>128912405</v>
       </c>
       <c r="B115" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>128912408</v>
       </c>
       <c r="B116" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>128912388</v>
       </c>
       <c r="B117" t="n">
-        <v>90302</v>
+        <v>90306</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>128912380</v>
       </c>
       <c r="B118" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>128912422</v>
       </c>
       <c r="B119" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>128912402</v>
       </c>
       <c r="B120" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13209,32 +13209,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128912421</v>
+        <v>128912379</v>
       </c>
       <c r="B121" t="n">
-        <v>86713</v>
+        <v>91017</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>249278</v>
+        <v>5741</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13244,10 +13244,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>705425</v>
+        <v>705404</v>
       </c>
       <c r="R121" t="n">
-        <v>6396872</v>
+        <v>6396616</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13306,10 +13306,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912379</v>
+        <v>128912384</v>
       </c>
       <c r="B122" t="n">
-        <v>91013</v>
+        <v>90295</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13317,34 +13317,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5741</v>
+        <v>6268</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705404</v>
+        <v>705294</v>
       </c>
       <c r="R122" t="n">
-        <v>6396616</v>
+        <v>6396977</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13379,12 +13382,18 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13403,48 +13412,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128912384</v>
+        <v>128912421</v>
       </c>
       <c r="B123" t="n">
-        <v>90291</v>
+        <v>86717</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6268</v>
+        <v>249278</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>705294</v>
+        <v>705425</v>
       </c>
       <c r="R123" t="n">
-        <v>6396977</v>
+        <v>6396872</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13479,18 +13485,12 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Utbrett mycel med minst 10 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13512,7 +13512,7 @@
         <v>128912411</v>
       </c>
       <c r="B124" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>128912425</v>
       </c>
       <c r="B125" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>128912416</v>
       </c>
       <c r="B126" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>128912398</v>
       </c>
       <c r="B127" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>128912394</v>
       </c>
       <c r="B128" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>128912410</v>
       </c>
       <c r="B129" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>128912406</v>
       </c>
       <c r="B130" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>128912423</v>
       </c>
       <c r="B131" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>128912390</v>
       </c>
       <c r="B132" t="n">
-        <v>90302</v>
+        <v>90306</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>128912407</v>
       </c>
       <c r="B133" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14480,34 +14480,30 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128912412</v>
+        <v>128912382</v>
       </c>
       <c r="B134" t="n">
-        <v>90965</v>
+        <v>92812</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14515,10 +14511,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>705316</v>
+        <v>705322</v>
       </c>
       <c r="R134" t="n">
-        <v>6396862</v>
+        <v>6396888</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14577,30 +14573,34 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128912382</v>
+        <v>128912412</v>
       </c>
       <c r="B135" t="n">
-        <v>92808</v>
+        <v>90969</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6047725</v>
+        <v>3286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14608,10 +14608,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>705322</v>
+        <v>705316</v>
       </c>
       <c r="R135" t="n">
-        <v>6396888</v>
+        <v>6396862</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14673,7 +14673,7 @@
         <v>128912395</v>
       </c>
       <c r="B136" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>128912396</v>
       </c>
       <c r="B137" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>128912401</v>
       </c>
       <c r="B138" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>128912418</v>
       </c>
       <c r="B139" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15060,32 +15060,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128912409</v>
+        <v>128912415</v>
       </c>
       <c r="B140" t="n">
-        <v>86935</v>
+        <v>86717</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>705284</v>
+        <v>705249</v>
       </c>
       <c r="R140" t="n">
-        <v>6396861</v>
+        <v>6396927</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15157,32 +15157,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128912415</v>
+        <v>128912409</v>
       </c>
       <c r="B141" t="n">
-        <v>86713</v>
+        <v>86939</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15192,10 +15192,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>705249</v>
+        <v>705284</v>
       </c>
       <c r="R141" t="n">
-        <v>6396927</v>
+        <v>6396861</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15257,7 +15257,7 @@
         <v>128912403</v>
       </c>
       <c r="B142" t="n">
-        <v>86758</v>
+        <v>86762</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>128912399</v>
       </c>
       <c r="B143" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6291,45 +6291,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884883</v>
+        <v>128884885</v>
       </c>
       <c r="B52" t="n">
-        <v>86762</v>
+        <v>86864</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1985</v>
+        <v>3611</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705450</v>
+        <v>705360</v>
       </c>
       <c r="R52" t="n">
-        <v>6396748</v>
+        <v>6396790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6389,7 +6392,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884302</v>
+        <v>128884883</v>
       </c>
       <c r="B53" t="n">
         <v>86762</v>
@@ -6420,14 +6423,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705513</v>
+        <v>705450</v>
       </c>
       <c r="R53" t="n">
-        <v>6396594</v>
+        <v>6396748</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6457,87 +6460,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884885</v>
+        <v>128884302</v>
       </c>
       <c r="B54" t="n">
-        <v>86864</v>
+        <v>86762</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3611</v>
+        <v>1985</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>705360</v>
+        <v>705513</v>
       </c>
       <c r="R54" t="n">
-        <v>6396790</v>
+        <v>6396594</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,30 +6558,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6704,32 +6704,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884887</v>
+        <v>128884894</v>
       </c>
       <c r="B56" t="n">
-        <v>86939</v>
+        <v>90969</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1988</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705305</v>
+        <v>705317</v>
       </c>
       <c r="R56" t="n">
-        <v>6396830</v>
+        <v>6396863</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,10 +6801,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884906</v>
+        <v>128884863</v>
       </c>
       <c r="B57" t="n">
-        <v>92140</v>
+        <v>92205</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6812,21 +6812,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6031</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705291</v>
+        <v>705446</v>
       </c>
       <c r="R57" t="n">
-        <v>6396952</v>
+        <v>6396726</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884884</v>
+        <v>128884906</v>
       </c>
       <c r="B58" t="n">
-        <v>91017</v>
+        <v>92140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5741</v>
+        <v>6031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705475</v>
+        <v>705291</v>
       </c>
       <c r="R58" t="n">
-        <v>6396574</v>
+        <v>6396952</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6977,7 +6977,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6996,45 +6995,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884301</v>
+        <v>128884887</v>
       </c>
       <c r="B59" t="n">
-        <v>91043</v>
+        <v>86939</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>1988</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705546</v>
+        <v>705305</v>
       </c>
       <c r="R59" t="n">
-        <v>6396613</v>
+        <v>6396830</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7064,19 +7063,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7091,22 +7080,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884872</v>
+        <v>128884884</v>
       </c>
       <c r="B60" t="n">
-        <v>92810</v>
+        <v>91017</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7114,21 +7103,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7138,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705338</v>
+        <v>705475</v>
       </c>
       <c r="R60" t="n">
-        <v>6396936</v>
+        <v>6396574</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7182,6 +7171,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7200,45 +7190,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884894</v>
+        <v>128884301</v>
       </c>
       <c r="B61" t="n">
-        <v>90969</v>
+        <v>91043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705317</v>
+        <v>705546</v>
       </c>
       <c r="R61" t="n">
-        <v>6396863</v>
+        <v>6396613</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7268,9 +7258,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7285,22 +7285,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884863</v>
+        <v>128884872</v>
       </c>
       <c r="B62" t="n">
-        <v>92205</v>
+        <v>92810</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705446</v>
+        <v>705338</v>
       </c>
       <c r="R62" t="n">
-        <v>6396726</v>
+        <v>6396936</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7501,10 +7501,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884294</v>
+        <v>128884879</v>
       </c>
       <c r="B64" t="n">
-        <v>86717</v>
+        <v>86963</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7512,34 +7512,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705415</v>
+        <v>705537</v>
       </c>
       <c r="R64" t="n">
-        <v>6396763</v>
+        <v>6396616</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,19 +7569,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7597,19 +7587,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884912</v>
+        <v>128884294</v>
       </c>
       <c r="B65" t="n">
         <v>86717</v>
@@ -7640,14 +7630,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705461</v>
+        <v>705415</v>
       </c>
       <c r="R65" t="n">
-        <v>6396579</v>
+        <v>6396763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7677,9 +7667,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7695,22 +7695,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884879</v>
+        <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>86963</v>
+        <v>86717</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7718,21 +7718,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7742,10 +7742,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705537</v>
+        <v>705461</v>
       </c>
       <c r="R66" t="n">
-        <v>6396616</v>
+        <v>6396579</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884867</v>
+        <v>128884869</v>
       </c>
       <c r="B75" t="n">
-        <v>91017</v>
+        <v>86810</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5741</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>705431</v>
+        <v>705297</v>
       </c>
       <c r="R75" t="n">
-        <v>6396688</v>
+        <v>6396817</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8684,32 +8684,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884869</v>
+        <v>128884867</v>
       </c>
       <c r="B76" t="n">
-        <v>86810</v>
+        <v>91017</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>424</v>
+        <v>5741</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>705297</v>
+        <v>705431</v>
       </c>
       <c r="R76" t="n">
-        <v>6396817</v>
+        <v>6396688</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8878,48 +8878,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884873</v>
+        <v>128884296</v>
       </c>
       <c r="B78" t="n">
-        <v>90306</v>
+        <v>91017</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>705314</v>
+        <v>705419</v>
       </c>
       <c r="R78" t="n">
-        <v>6396809</v>
+        <v>6396769</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8949,75 +8946,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884296</v>
+        <v>128884873</v>
       </c>
       <c r="B79" t="n">
-        <v>91017</v>
+        <v>90306</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>705419</v>
+        <v>705314</v>
       </c>
       <c r="R79" t="n">
-        <v>6396769</v>
+        <v>6396809</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9047,39 +9056,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128889624</v>
+        <v>128884862</v>
       </c>
       <c r="B84" t="n">
-        <v>90306</v>
+        <v>87008</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2072</v>
+        <v>3767</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705513</v>
+        <v>705398</v>
       </c>
       <c r="R84" t="n">
-        <v>6396594</v>
+        <v>6396569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,19 +9566,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9593,57 +9583,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884882</v>
+        <v>128889624</v>
       </c>
       <c r="B85" t="n">
-        <v>86762</v>
+        <v>90306</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1985</v>
+        <v>2072</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705380</v>
+        <v>705513</v>
       </c>
       <c r="R85" t="n">
-        <v>6396917</v>
+        <v>6396594</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9673,9 +9663,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,22 +9690,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884862</v>
+        <v>128884882</v>
       </c>
       <c r="B86" t="n">
-        <v>87008</v>
+        <v>86762</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705398</v>
+        <v>705380</v>
       </c>
       <c r="R86" t="n">
-        <v>6396569</v>
+        <v>6396917</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10208,32 +10208,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884864</v>
+        <v>128884907</v>
       </c>
       <c r="B91" t="n">
-        <v>91017</v>
+        <v>90249</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10243,10 +10243,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705252</v>
+        <v>705399</v>
       </c>
       <c r="R91" t="n">
-        <v>6396894</v>
+        <v>6396889</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884896</v>
+        <v>128884864</v>
       </c>
       <c r="B92" t="n">
-        <v>92834</v>
+        <v>91017</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10317,37 +10317,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705227</v>
+        <v>705252</v>
       </c>
       <c r="R92" t="n">
-        <v>6396932</v>
+        <v>6396894</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10407,45 +10404,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884907</v>
+        <v>128884896</v>
       </c>
       <c r="B93" t="n">
-        <v>90249</v>
+        <v>92834</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>970</v>
+        <v>5964</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705399</v>
+        <v>705227</v>
       </c>
       <c r="R93" t="n">
-        <v>6396889</v>
+        <v>6396932</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10505,32 +10505,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884876</v>
+        <v>128884306</v>
       </c>
       <c r="B94" t="n">
-        <v>90306</v>
+        <v>86864</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2072</v>
+        <v>3611</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10539,14 +10539,14 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705430</v>
+        <v>705439</v>
       </c>
       <c r="R94" t="n">
-        <v>6396834</v>
+        <v>6396582</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10576,9 +10576,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10594,44 +10604,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884306</v>
+        <v>128884876</v>
       </c>
       <c r="B95" t="n">
-        <v>86864</v>
+        <v>90306</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3611</v>
+        <v>2072</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10640,14 +10650,14 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705439</v>
+        <v>705430</v>
       </c>
       <c r="R95" t="n">
-        <v>6396582</v>
+        <v>6396834</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10677,19 +10687,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10705,12 +10705,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10915,10 +10915,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884913</v>
+        <v>128884303</v>
       </c>
       <c r="B98" t="n">
-        <v>86717</v>
+        <v>86864</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705414</v>
+        <v>705477</v>
       </c>
       <c r="R98" t="n">
-        <v>6396611</v>
+        <v>6396583</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10983,75 +10983,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884910</v>
+        <v>128884899</v>
       </c>
       <c r="B99" t="n">
-        <v>86717</v>
+        <v>92834</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705273</v>
+        <v>705436</v>
       </c>
       <c r="R99" t="n">
-        <v>6396934</v>
+        <v>6396834</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11111,7 +11123,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884899</v>
+        <v>128884897</v>
       </c>
       <c r="B100" t="n">
         <v>92834</v>
@@ -11149,10 +11161,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705436</v>
+        <v>705297</v>
       </c>
       <c r="R100" t="n">
-        <v>6396834</v>
+        <v>6396949</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11212,48 +11224,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884897</v>
+        <v>128884913</v>
       </c>
       <c r="B101" t="n">
-        <v>92834</v>
+        <v>86717</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705297</v>
+        <v>705414</v>
       </c>
       <c r="R101" t="n">
-        <v>6396949</v>
+        <v>6396611</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11313,10 +11322,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884303</v>
+        <v>128884910</v>
       </c>
       <c r="B102" t="n">
-        <v>86864</v>
+        <v>86717</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11324,34 +11333,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705477</v>
+        <v>705273</v>
       </c>
       <c r="R102" t="n">
-        <v>6396583</v>
+        <v>6396934</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11381,39 +11390,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912404</v>
+        <v>128912419</v>
       </c>
       <c r="B109" t="n">
-        <v>86762</v>
+        <v>86717</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705405</v>
+        <v>705420</v>
       </c>
       <c r="R109" t="n">
-        <v>6396928</v>
+        <v>6396917</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912419</v>
+        <v>128912424</v>
       </c>
       <c r="B110" t="n">
         <v>86717</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705420</v>
+        <v>705432</v>
       </c>
       <c r="R110" t="n">
-        <v>6396917</v>
+        <v>6396615</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,7 +12229,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912424</v>
+        <v>128912420</v>
       </c>
       <c r="B111" t="n">
         <v>86717</v>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705432</v>
+        <v>705443</v>
       </c>
       <c r="R111" t="n">
-        <v>6396615</v>
+        <v>6396921</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,7 +12326,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912420</v>
+        <v>128912417</v>
       </c>
       <c r="B112" t="n">
         <v>86717</v>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705443</v>
+        <v>705276</v>
       </c>
       <c r="R112" t="n">
-        <v>6396921</v>
+        <v>6396964</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,32 +12423,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912417</v>
+        <v>128912404</v>
       </c>
       <c r="B113" t="n">
-        <v>86717</v>
+        <v>86762</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705276</v>
+        <v>705405</v>
       </c>
       <c r="R113" t="n">
-        <v>6396964</v>
+        <v>6396928</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13800,32 +13800,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128912398</v>
+        <v>128912394</v>
       </c>
       <c r="B127" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13835,10 +13835,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>705492</v>
+        <v>705421</v>
       </c>
       <c r="R127" t="n">
-        <v>6396758</v>
+        <v>6396928</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13879,7 +13879,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13898,32 +13897,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128912394</v>
+        <v>128912398</v>
       </c>
       <c r="B128" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13933,10 +13932,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>705421</v>
+        <v>705492</v>
       </c>
       <c r="R128" t="n">
-        <v>6396928</v>
+        <v>6396758</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13977,6 +13976,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13995,32 +13995,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912410</v>
+        <v>128912406</v>
       </c>
       <c r="B129" t="n">
-        <v>86985</v>
+        <v>86864</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>449</v>
+        <v>3611</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705430</v>
+        <v>705470</v>
       </c>
       <c r="R129" t="n">
-        <v>6396796</v>
+        <v>6396774</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,32 +14092,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912406</v>
+        <v>128912410</v>
       </c>
       <c r="B130" t="n">
-        <v>86864</v>
+        <v>86985</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3611</v>
+        <v>449</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705470</v>
+        <v>705430</v>
       </c>
       <c r="R130" t="n">
-        <v>6396774</v>
+        <v>6396796</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14480,30 +14480,34 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128912382</v>
+        <v>128912412</v>
       </c>
       <c r="B134" t="n">
-        <v>92812</v>
+        <v>90969</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6047725</v>
+        <v>3286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14511,10 +14515,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>705322</v>
+        <v>705316</v>
       </c>
       <c r="R134" t="n">
-        <v>6396888</v>
+        <v>6396862</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14573,34 +14577,30 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128912412</v>
+        <v>128912382</v>
       </c>
       <c r="B135" t="n">
-        <v>90969</v>
+        <v>92812</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14608,10 +14608,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>705316</v>
+        <v>705322</v>
       </c>
       <c r="R135" t="n">
-        <v>6396862</v>
+        <v>6396888</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14670,7 +14670,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128912395</v>
+        <v>128912396</v>
       </c>
       <c r="B136" t="n">
         <v>86963</v>
@@ -14705,10 +14705,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>705266</v>
+        <v>705284</v>
       </c>
       <c r="R136" t="n">
-        <v>6396904</v>
+        <v>6396977</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14768,7 +14768,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128912396</v>
+        <v>128912395</v>
       </c>
       <c r="B137" t="n">
         <v>86963</v>
@@ -14803,10 +14803,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>705284</v>
+        <v>705266</v>
       </c>
       <c r="R137" t="n">
-        <v>6396977</v>
+        <v>6396904</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15060,32 +15060,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128912415</v>
+        <v>128912409</v>
       </c>
       <c r="B140" t="n">
-        <v>86717</v>
+        <v>86939</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>705249</v>
+        <v>705284</v>
       </c>
       <c r="R140" t="n">
-        <v>6396927</v>
+        <v>6396861</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15157,32 +15157,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128912409</v>
+        <v>128912415</v>
       </c>
       <c r="B141" t="n">
-        <v>86939</v>
+        <v>86717</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15192,10 +15192,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>705284</v>
+        <v>705249</v>
       </c>
       <c r="R141" t="n">
-        <v>6396861</v>
+        <v>6396927</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6291,48 +6291,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884885</v>
+        <v>128884883</v>
       </c>
       <c r="B52" t="n">
-        <v>86864</v>
+        <v>86762</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3611</v>
+        <v>1985</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705360</v>
+        <v>705450</v>
       </c>
       <c r="R52" t="n">
-        <v>6396790</v>
+        <v>6396748</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6392,7 +6389,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884883</v>
+        <v>128884302</v>
       </c>
       <c r="B53" t="n">
         <v>86762</v>
@@ -6423,14 +6420,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705450</v>
+        <v>705513</v>
       </c>
       <c r="R53" t="n">
-        <v>6396748</v>
+        <v>6396594</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6460,75 +6457,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884302</v>
+        <v>128884885</v>
       </c>
       <c r="B54" t="n">
-        <v>86762</v>
+        <v>86864</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1985</v>
+        <v>3611</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>705513</v>
+        <v>705360</v>
       </c>
       <c r="R54" t="n">
-        <v>6396594</v>
+        <v>6396790</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,39 +6567,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884906</v>
+        <v>128884884</v>
       </c>
       <c r="B58" t="n">
-        <v>92140</v>
+        <v>91017</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6031</v>
+        <v>5741</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705291</v>
+        <v>705475</v>
       </c>
       <c r="R58" t="n">
-        <v>6396952</v>
+        <v>6396574</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6977,6 +6977,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6995,45 +6996,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884887</v>
+        <v>128884301</v>
       </c>
       <c r="B59" t="n">
-        <v>86939</v>
+        <v>91043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1988</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705305</v>
+        <v>705546</v>
       </c>
       <c r="R59" t="n">
-        <v>6396830</v>
+        <v>6396613</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7063,9 +7064,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7080,22 +7091,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884884</v>
+        <v>128884906</v>
       </c>
       <c r="B60" t="n">
-        <v>91017</v>
+        <v>92140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,21 +7114,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5741</v>
+        <v>6031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7127,10 +7138,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705475</v>
+        <v>705291</v>
       </c>
       <c r="R60" t="n">
-        <v>6396574</v>
+        <v>6396952</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7171,7 +7182,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7190,45 +7200,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884301</v>
+        <v>128884872</v>
       </c>
       <c r="B61" t="n">
-        <v>91043</v>
+        <v>92810</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705546</v>
+        <v>705338</v>
       </c>
       <c r="R61" t="n">
-        <v>6396613</v>
+        <v>6396936</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7258,19 +7268,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7285,22 +7285,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884872</v>
+        <v>128884887</v>
       </c>
       <c r="B62" t="n">
-        <v>92810</v>
+        <v>86939</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>1988</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705338</v>
+        <v>705305</v>
       </c>
       <c r="R62" t="n">
-        <v>6396936</v>
+        <v>6396830</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7501,32 +7501,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884879</v>
+        <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>86963</v>
+        <v>90306</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>2072</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705537</v>
+        <v>705428</v>
       </c>
       <c r="R64" t="n">
-        <v>6396616</v>
+        <v>6396833</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7580,7 +7580,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7599,10 +7598,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884294</v>
+        <v>128884879</v>
       </c>
       <c r="B65" t="n">
-        <v>86717</v>
+        <v>86963</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7610,34 +7609,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705415</v>
+        <v>705537</v>
       </c>
       <c r="R65" t="n">
-        <v>6396763</v>
+        <v>6396616</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7667,19 +7666,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7695,19 +7684,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884912</v>
+        <v>128884294</v>
       </c>
       <c r="B66" t="n">
         <v>86717</v>
@@ -7738,14 +7727,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705461</v>
+        <v>705415</v>
       </c>
       <c r="R66" t="n">
-        <v>6396579</v>
+        <v>6396763</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7775,9 +7764,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7793,44 +7792,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884875</v>
+        <v>128884912</v>
       </c>
       <c r="B67" t="n">
-        <v>90306</v>
+        <v>86717</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7840,10 +7839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705428</v>
+        <v>705461</v>
       </c>
       <c r="R67" t="n">
-        <v>6396833</v>
+        <v>6396579</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7884,6 +7883,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8291,10 +8291,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884865</v>
+        <v>128884898</v>
       </c>
       <c r="B72" t="n">
-        <v>91017</v>
+        <v>92834</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8302,34 +8302,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705416</v>
+        <v>705425</v>
       </c>
       <c r="R72" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8389,10 +8392,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884898</v>
+        <v>128884865</v>
       </c>
       <c r="B73" t="n">
-        <v>92834</v>
+        <v>91017</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,37 +8403,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705425</v>
+        <v>705416</v>
       </c>
       <c r="R73" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9193,48 +9193,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884881</v>
+        <v>128884305</v>
       </c>
       <c r="B81" t="n">
-        <v>86950</v>
+        <v>91017</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>705474</v>
+        <v>705468</v>
       </c>
       <c r="R81" t="n">
-        <v>6396574</v>
+        <v>6396595</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9264,37 +9261,46 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884305</v>
+        <v>128884866</v>
       </c>
       <c r="B82" t="n">
         <v>91017</v>
@@ -9325,14 +9331,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>705468</v>
+        <v>705433</v>
       </c>
       <c r="R82" t="n">
-        <v>6396595</v>
+        <v>6396684</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9362,19 +9368,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9389,57 +9385,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128884866</v>
+        <v>128884881</v>
       </c>
       <c r="B83" t="n">
-        <v>91017</v>
+        <v>86950</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>705433</v>
+        <v>705474</v>
       </c>
       <c r="R83" t="n">
-        <v>6396684</v>
+        <v>6396574</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9480,6 +9479,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9595,45 +9595,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128889624</v>
+        <v>128884882</v>
       </c>
       <c r="B85" t="n">
-        <v>90306</v>
+        <v>86762</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2072</v>
+        <v>1985</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705513</v>
+        <v>705380</v>
       </c>
       <c r="R85" t="n">
-        <v>6396594</v>
+        <v>6396917</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,19 +9663,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,57 +9680,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884882</v>
+        <v>128889624</v>
       </c>
       <c r="B86" t="n">
-        <v>86762</v>
+        <v>90306</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1985</v>
+        <v>2072</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705380</v>
+        <v>705513</v>
       </c>
       <c r="R86" t="n">
-        <v>6396917</v>
+        <v>6396594</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9770,9 +9760,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9787,12 +9787,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10101,45 +10101,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884304</v>
+        <v>128884864</v>
       </c>
       <c r="B90" t="n">
-        <v>86950</v>
+        <v>91017</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705475</v>
+        <v>705252</v>
       </c>
       <c r="R90" t="n">
-        <v>6396577</v>
+        <v>6396894</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10169,84 +10169,78 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884907</v>
+        <v>128884896</v>
       </c>
       <c r="B91" t="n">
-        <v>90249</v>
+        <v>92834</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>970</v>
+        <v>5964</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705399</v>
+        <v>705227</v>
       </c>
       <c r="R91" t="n">
-        <v>6396889</v>
+        <v>6396932</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10306,45 +10300,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884864</v>
+        <v>128884304</v>
       </c>
       <c r="B92" t="n">
-        <v>91017</v>
+        <v>86950</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705252</v>
+        <v>705475</v>
       </c>
       <c r="R92" t="n">
-        <v>6396894</v>
+        <v>6396577</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10374,78 +10368,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884896</v>
+        <v>128884907</v>
       </c>
       <c r="B93" t="n">
-        <v>92834</v>
+        <v>90249</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5964</v>
+        <v>970</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705227</v>
+        <v>705399</v>
       </c>
       <c r="R93" t="n">
-        <v>6396932</v>
+        <v>6396889</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10915,10 +10915,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884303</v>
+        <v>128884913</v>
       </c>
       <c r="B98" t="n">
-        <v>86864</v>
+        <v>86717</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705477</v>
+        <v>705414</v>
       </c>
       <c r="R98" t="n">
-        <v>6396583</v>
+        <v>6396611</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10983,87 +10983,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884899</v>
+        <v>128884910</v>
       </c>
       <c r="B99" t="n">
-        <v>92834</v>
+        <v>86717</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705436</v>
+        <v>705273</v>
       </c>
       <c r="R99" t="n">
-        <v>6396834</v>
+        <v>6396934</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11123,48 +11111,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884897</v>
+        <v>128884303</v>
       </c>
       <c r="B100" t="n">
-        <v>92834</v>
+        <v>86864</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705297</v>
+        <v>705477</v>
       </c>
       <c r="R100" t="n">
-        <v>6396949</v>
+        <v>6396583</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11194,75 +11179,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884913</v>
+        <v>128884897</v>
       </c>
       <c r="B101" t="n">
-        <v>86717</v>
+        <v>92834</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705414</v>
+        <v>705297</v>
       </c>
       <c r="R101" t="n">
-        <v>6396611</v>
+        <v>6396949</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11322,45 +11319,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884910</v>
+        <v>128884899</v>
       </c>
       <c r="B102" t="n">
-        <v>86717</v>
+        <v>92834</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705273</v>
+        <v>705436</v>
       </c>
       <c r="R102" t="n">
-        <v>6396934</v>
+        <v>6396834</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11420,48 +11420,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128884874</v>
+        <v>128884908</v>
       </c>
       <c r="B103" t="n">
-        <v>90306</v>
+        <v>86717</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>705425</v>
+        <v>705320</v>
       </c>
       <c r="R103" t="n">
-        <v>6396850</v>
+        <v>6396829</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11521,7 +11518,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128884908</v>
+        <v>128884911</v>
       </c>
       <c r="B104" t="n">
         <v>86717</v>
@@ -11556,10 +11553,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>705320</v>
+        <v>705527</v>
       </c>
       <c r="R104" t="n">
-        <v>6396829</v>
+        <v>6396694</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11619,45 +11616,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884911</v>
+        <v>128884874</v>
       </c>
       <c r="B105" t="n">
-        <v>86717</v>
+        <v>90306</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705527</v>
+        <v>705425</v>
       </c>
       <c r="R105" t="n">
-        <v>6396694</v>
+        <v>6396850</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912419</v>
+        <v>128912404</v>
       </c>
       <c r="B109" t="n">
-        <v>86717</v>
+        <v>86762</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705420</v>
+        <v>705405</v>
       </c>
       <c r="R109" t="n">
-        <v>6396917</v>
+        <v>6396928</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912424</v>
+        <v>128912419</v>
       </c>
       <c r="B110" t="n">
         <v>86717</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705432</v>
+        <v>705420</v>
       </c>
       <c r="R110" t="n">
-        <v>6396615</v>
+        <v>6396917</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,7 +12229,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912420</v>
+        <v>128912424</v>
       </c>
       <c r="B111" t="n">
         <v>86717</v>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705443</v>
+        <v>705432</v>
       </c>
       <c r="R111" t="n">
-        <v>6396921</v>
+        <v>6396615</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,7 +12326,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912417</v>
+        <v>128912420</v>
       </c>
       <c r="B112" t="n">
         <v>86717</v>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705276</v>
+        <v>705443</v>
       </c>
       <c r="R112" t="n">
-        <v>6396964</v>
+        <v>6396921</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,32 +12423,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912404</v>
+        <v>128912417</v>
       </c>
       <c r="B113" t="n">
-        <v>86762</v>
+        <v>86717</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705405</v>
+        <v>705276</v>
       </c>
       <c r="R113" t="n">
-        <v>6396928</v>
+        <v>6396964</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13306,48 +13306,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912384</v>
+        <v>128912421</v>
       </c>
       <c r="B122" t="n">
-        <v>90295</v>
+        <v>86717</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6268</v>
+        <v>249278</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705294</v>
+        <v>705425</v>
       </c>
       <c r="R122" t="n">
-        <v>6396977</v>
+        <v>6396872</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13382,18 +13379,12 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Utbrett mycel med minst 10 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13412,45 +13403,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128912421</v>
+        <v>128912384</v>
       </c>
       <c r="B123" t="n">
-        <v>86717</v>
+        <v>90295</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>249278</v>
+        <v>6268</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>705425</v>
+        <v>705294</v>
       </c>
       <c r="R123" t="n">
-        <v>6396872</v>
+        <v>6396977</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13485,12 +13479,18 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13995,32 +13995,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912406</v>
+        <v>128912410</v>
       </c>
       <c r="B129" t="n">
-        <v>86864</v>
+        <v>86985</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3611</v>
+        <v>449</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705470</v>
+        <v>705430</v>
       </c>
       <c r="R129" t="n">
-        <v>6396774</v>
+        <v>6396796</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,32 +14092,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912410</v>
+        <v>128912406</v>
       </c>
       <c r="B130" t="n">
-        <v>86985</v>
+        <v>86864</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>449</v>
+        <v>3611</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705430</v>
+        <v>705470</v>
       </c>
       <c r="R130" t="n">
-        <v>6396796</v>
+        <v>6396774</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6291,45 +6291,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884883</v>
+        <v>128884885</v>
       </c>
       <c r="B52" t="n">
-        <v>86762</v>
+        <v>86869</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1985</v>
+        <v>3611</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705450</v>
+        <v>705360</v>
       </c>
       <c r="R52" t="n">
-        <v>6396748</v>
+        <v>6396790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6389,10 +6392,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884302</v>
+        <v>128884883</v>
       </c>
       <c r="B53" t="n">
-        <v>86762</v>
+        <v>86767</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6420,14 +6423,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705513</v>
+        <v>705450</v>
       </c>
       <c r="R53" t="n">
-        <v>6396594</v>
+        <v>6396748</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6457,87 +6460,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884885</v>
+        <v>128884302</v>
       </c>
       <c r="B54" t="n">
-        <v>86864</v>
+        <v>86767</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3611</v>
+        <v>1985</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>705360</v>
+        <v>705513</v>
       </c>
       <c r="R54" t="n">
-        <v>6396790</v>
+        <v>6396594</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,30 +6558,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6600,7 +6600,7 @@
         <v>128889600</v>
       </c>
       <c r="B55" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,32 +6704,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884894</v>
+        <v>128884887</v>
       </c>
       <c r="B56" t="n">
-        <v>90969</v>
+        <v>86944</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>1988</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705317</v>
+        <v>705305</v>
       </c>
       <c r="R56" t="n">
-        <v>6396863</v>
+        <v>6396830</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,10 +6801,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884863</v>
+        <v>128884884</v>
       </c>
       <c r="B57" t="n">
-        <v>92205</v>
+        <v>91022</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6812,21 +6812,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>5741</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705446</v>
+        <v>705475</v>
       </c>
       <c r="R57" t="n">
-        <v>6396726</v>
+        <v>6396574</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6880,6 +6880,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6898,45 +6899,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884884</v>
+        <v>128884301</v>
       </c>
       <c r="B58" t="n">
-        <v>91017</v>
+        <v>91048</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5741</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705475</v>
+        <v>705546</v>
       </c>
       <c r="R58" t="n">
-        <v>6396574</v>
+        <v>6396613</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6966,75 +6967,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884301</v>
+        <v>128884906</v>
       </c>
       <c r="B59" t="n">
-        <v>91043</v>
+        <v>92145</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>6031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705546</v>
+        <v>705291</v>
       </c>
       <c r="R59" t="n">
-        <v>6396613</v>
+        <v>6396952</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7064,19 +7074,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7091,22 +7091,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884906</v>
+        <v>128884863</v>
       </c>
       <c r="B60" t="n">
-        <v>92140</v>
+        <v>92210</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7114,21 +7114,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6031</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705291</v>
+        <v>705446</v>
       </c>
       <c r="R60" t="n">
-        <v>6396952</v>
+        <v>6396726</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7200,32 +7200,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884872</v>
+        <v>128884894</v>
       </c>
       <c r="B61" t="n">
-        <v>92810</v>
+        <v>90974</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>3286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705338</v>
+        <v>705317</v>
       </c>
       <c r="R61" t="n">
-        <v>6396936</v>
+        <v>6396863</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7297,10 +7297,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884887</v>
+        <v>128884872</v>
       </c>
       <c r="B62" t="n">
-        <v>86939</v>
+        <v>92815</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1988</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705305</v>
+        <v>705338</v>
       </c>
       <c r="R62" t="n">
-        <v>6396830</v>
+        <v>6396936</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7397,7 +7397,7 @@
         <v>128890120</v>
       </c>
       <c r="B63" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>90306</v>
+        <v>90311</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884879</v>
+        <v>128884294</v>
       </c>
       <c r="B65" t="n">
-        <v>86963</v>
+        <v>86722</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7609,34 +7609,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705537</v>
+        <v>705415</v>
       </c>
       <c r="R65" t="n">
-        <v>6396616</v>
+        <v>6396763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7666,9 +7666,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7684,22 +7694,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884294</v>
+        <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7727,14 +7737,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705415</v>
+        <v>705461</v>
       </c>
       <c r="R66" t="n">
-        <v>6396763</v>
+        <v>6396579</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7764,19 +7774,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7792,22 +7792,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884912</v>
+        <v>128884879</v>
       </c>
       <c r="B67" t="n">
-        <v>86717</v>
+        <v>86968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705461</v>
+        <v>705537</v>
       </c>
       <c r="R67" t="n">
-        <v>6396579</v>
+        <v>6396616</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7905,7 +7905,7 @@
         <v>128884861</v>
       </c>
       <c r="B68" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>128884914</v>
       </c>
       <c r="B69" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>128884871</v>
       </c>
       <c r="B70" t="n">
-        <v>87029</v>
+        <v>87034</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>128884886</v>
       </c>
       <c r="B71" t="n">
-        <v>86864</v>
+        <v>86869</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,10 +8291,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884898</v>
+        <v>128884865</v>
       </c>
       <c r="B72" t="n">
-        <v>92834</v>
+        <v>91022</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8302,37 +8302,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705425</v>
+        <v>705416</v>
       </c>
       <c r="R72" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8392,10 +8389,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884865</v>
+        <v>128884898</v>
       </c>
       <c r="B73" t="n">
-        <v>91017</v>
+        <v>92839</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8403,34 +8400,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705416</v>
+        <v>705425</v>
       </c>
       <c r="R73" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8493,7 +8493,7 @@
         <v>128884868</v>
       </c>
       <c r="B74" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>128884869</v>
       </c>
       <c r="B75" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>128884867</v>
       </c>
       <c r="B76" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>128884890</v>
       </c>
       <c r="B77" t="n">
-        <v>105686</v>
+        <v>105693</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>128884296</v>
       </c>
       <c r="B78" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>128884873</v>
       </c>
       <c r="B79" t="n">
-        <v>90306</v>
+        <v>90311</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>128884299</v>
       </c>
       <c r="B80" t="n">
-        <v>86864</v>
+        <v>86869</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9193,45 +9193,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884305</v>
+        <v>128884881</v>
       </c>
       <c r="B81" t="n">
-        <v>91017</v>
+        <v>86955</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>705468</v>
+        <v>705474</v>
       </c>
       <c r="R81" t="n">
-        <v>6396595</v>
+        <v>6396574</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9261,49 +9264,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884866</v>
+        <v>128884305</v>
       </c>
       <c r="B82" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9331,14 +9325,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>705433</v>
+        <v>705468</v>
       </c>
       <c r="R82" t="n">
-        <v>6396684</v>
+        <v>6396595</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9368,9 +9362,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9385,60 +9389,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128884881</v>
+        <v>128884866</v>
       </c>
       <c r="B83" t="n">
-        <v>86950</v>
+        <v>91022</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>705474</v>
+        <v>705433</v>
       </c>
       <c r="R83" t="n">
-        <v>6396574</v>
+        <v>6396684</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9479,7 +9480,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9498,10 +9498,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884862</v>
+        <v>128884882</v>
       </c>
       <c r="B84" t="n">
-        <v>87008</v>
+        <v>86767</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9509,21 +9509,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705398</v>
+        <v>705380</v>
       </c>
       <c r="R84" t="n">
-        <v>6396569</v>
+        <v>6396917</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9595,10 +9595,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884882</v>
+        <v>128884862</v>
       </c>
       <c r="B85" t="n">
-        <v>86762</v>
+        <v>87013</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9606,21 +9606,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9630,10 +9630,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705380</v>
+        <v>705398</v>
       </c>
       <c r="R85" t="n">
-        <v>6396917</v>
+        <v>6396569</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9695,7 +9695,7 @@
         <v>128889624</v>
       </c>
       <c r="B86" t="n">
-        <v>90306</v>
+        <v>90311</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>128884300</v>
       </c>
       <c r="B87" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>128884870</v>
       </c>
       <c r="B88" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>128884878</v>
       </c>
       <c r="B89" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10101,32 +10101,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884864</v>
+        <v>128884907</v>
       </c>
       <c r="B90" t="n">
-        <v>91017</v>
+        <v>90254</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705252</v>
+        <v>705399</v>
       </c>
       <c r="R90" t="n">
-        <v>6396894</v>
+        <v>6396889</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10199,48 +10199,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884896</v>
+        <v>128884304</v>
       </c>
       <c r="B91" t="n">
-        <v>92834</v>
+        <v>86955</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705227</v>
+        <v>705475</v>
       </c>
       <c r="R91" t="n">
-        <v>6396932</v>
+        <v>6396577</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10270,75 +10267,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884304</v>
+        <v>128884864</v>
       </c>
       <c r="B92" t="n">
-        <v>86950</v>
+        <v>91022</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705475</v>
+        <v>705252</v>
       </c>
       <c r="R92" t="n">
-        <v>6396577</v>
+        <v>6396894</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10368,84 +10374,78 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884907</v>
+        <v>128884896</v>
       </c>
       <c r="B93" t="n">
-        <v>90249</v>
+        <v>92839</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>970</v>
+        <v>5964</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705399</v>
+        <v>705227</v>
       </c>
       <c r="R93" t="n">
-        <v>6396889</v>
+        <v>6396932</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10505,32 +10505,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884306</v>
+        <v>128884876</v>
       </c>
       <c r="B94" t="n">
-        <v>86864</v>
+        <v>90311</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3611</v>
+        <v>2072</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10539,14 +10539,14 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705439</v>
+        <v>705430</v>
       </c>
       <c r="R94" t="n">
-        <v>6396582</v>
+        <v>6396834</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10576,19 +10576,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10604,44 +10594,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884876</v>
+        <v>128884306</v>
       </c>
       <c r="B95" t="n">
-        <v>90306</v>
+        <v>86869</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2072</v>
+        <v>3611</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10650,14 +10640,14 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705430</v>
+        <v>705439</v>
       </c>
       <c r="R95" t="n">
-        <v>6396834</v>
+        <v>6396582</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10687,9 +10677,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10705,12 +10705,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10720,7 +10720,7 @@
         <v>128884900</v>
       </c>
       <c r="B96" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>128884915</v>
       </c>
       <c r="B97" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10915,10 +10915,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884913</v>
+        <v>128884303</v>
       </c>
       <c r="B98" t="n">
-        <v>86717</v>
+        <v>86869</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705414</v>
+        <v>705477</v>
       </c>
       <c r="R98" t="n">
-        <v>6396611</v>
+        <v>6396583</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10983,75 +10983,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884910</v>
+        <v>128884899</v>
       </c>
       <c r="B99" t="n">
-        <v>86717</v>
+        <v>92839</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705273</v>
+        <v>705436</v>
       </c>
       <c r="R99" t="n">
-        <v>6396934</v>
+        <v>6396834</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11111,45 +11123,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884303</v>
+        <v>128884897</v>
       </c>
       <c r="B100" t="n">
-        <v>86864</v>
+        <v>92839</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705477</v>
+        <v>705297</v>
       </c>
       <c r="R100" t="n">
-        <v>6396583</v>
+        <v>6396949</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11179,87 +11194,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884897</v>
+        <v>128884913</v>
       </c>
       <c r="B101" t="n">
-        <v>92834</v>
+        <v>86722</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705297</v>
+        <v>705414</v>
       </c>
       <c r="R101" t="n">
-        <v>6396949</v>
+        <v>6396611</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11319,48 +11322,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884899</v>
+        <v>128884910</v>
       </c>
       <c r="B102" t="n">
-        <v>92834</v>
+        <v>86722</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705436</v>
+        <v>705273</v>
       </c>
       <c r="R102" t="n">
-        <v>6396834</v>
+        <v>6396934</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11420,45 +11420,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128884908</v>
+        <v>128884874</v>
       </c>
       <c r="B103" t="n">
-        <v>86717</v>
+        <v>90311</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>705320</v>
+        <v>705425</v>
       </c>
       <c r="R103" t="n">
-        <v>6396829</v>
+        <v>6396850</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11518,10 +11521,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128884911</v>
+        <v>128884908</v>
       </c>
       <c r="B104" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11553,10 +11556,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>705527</v>
+        <v>705320</v>
       </c>
       <c r="R104" t="n">
-        <v>6396694</v>
+        <v>6396829</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11616,48 +11619,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884874</v>
+        <v>128884911</v>
       </c>
       <c r="B105" t="n">
-        <v>90306</v>
+        <v>86722</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705425</v>
+        <v>705527</v>
       </c>
       <c r="R105" t="n">
-        <v>6396850</v>
+        <v>6396694</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
         <v>128884877</v>
       </c>
       <c r="B106" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>128906402</v>
       </c>
       <c r="B107" t="n">
-        <v>86964</v>
+        <v>86969</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>128884909</v>
       </c>
       <c r="B108" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>128912404</v>
       </c>
       <c r="B109" t="n">
-        <v>86762</v>
+        <v>86767</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12132,10 +12132,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912419</v>
+        <v>128912417</v>
       </c>
       <c r="B110" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705420</v>
+        <v>705276</v>
       </c>
       <c r="R110" t="n">
-        <v>6396917</v>
+        <v>6396964</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,10 +12229,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912424</v>
+        <v>128912420</v>
       </c>
       <c r="B111" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705432</v>
+        <v>705443</v>
       </c>
       <c r="R111" t="n">
-        <v>6396615</v>
+        <v>6396921</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912420</v>
+        <v>128912424</v>
       </c>
       <c r="B112" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705443</v>
+        <v>705432</v>
       </c>
       <c r="R112" t="n">
-        <v>6396921</v>
+        <v>6396615</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,10 +12423,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912417</v>
+        <v>128912419</v>
       </c>
       <c r="B113" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705276</v>
+        <v>705420</v>
       </c>
       <c r="R113" t="n">
-        <v>6396964</v>
+        <v>6396917</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
         <v>128912385</v>
       </c>
       <c r="B114" t="n">
-        <v>90306</v>
+        <v>90311</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>128912405</v>
       </c>
       <c r="B115" t="n">
-        <v>86864</v>
+        <v>86869</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>128912408</v>
       </c>
       <c r="B116" t="n">
-        <v>86864</v>
+        <v>86869</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>128912388</v>
       </c>
       <c r="B117" t="n">
-        <v>90306</v>
+        <v>90311</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12918,32 +12918,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128912380</v>
+        <v>128912422</v>
       </c>
       <c r="B118" t="n">
-        <v>91017</v>
+        <v>86722</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5741</v>
+        <v>249278</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12953,10 +12953,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>705428</v>
+        <v>705469</v>
       </c>
       <c r="R118" t="n">
-        <v>6396581</v>
+        <v>6396714</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13015,32 +13015,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128912422</v>
+        <v>128912380</v>
       </c>
       <c r="B119" t="n">
-        <v>86717</v>
+        <v>91022</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>249278</v>
+        <v>5741</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13050,10 +13050,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>705469</v>
+        <v>705428</v>
       </c>
       <c r="R119" t="n">
-        <v>6396714</v>
+        <v>6396581</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13115,7 +13115,7 @@
         <v>128912402</v>
       </c>
       <c r="B120" t="n">
-        <v>86762</v>
+        <v>86767</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>128912379</v>
       </c>
       <c r="B121" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13306,45 +13306,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912421</v>
+        <v>128912384</v>
       </c>
       <c r="B122" t="n">
-        <v>86717</v>
+        <v>90300</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>249278</v>
+        <v>6268</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705425</v>
+        <v>705294</v>
       </c>
       <c r="R122" t="n">
-        <v>6396872</v>
+        <v>6396977</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13379,12 +13382,18 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13403,48 +13412,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128912384</v>
+        <v>128912421</v>
       </c>
       <c r="B123" t="n">
-        <v>90295</v>
+        <v>86722</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6268</v>
+        <v>249278</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>705294</v>
+        <v>705425</v>
       </c>
       <c r="R123" t="n">
-        <v>6396977</v>
+        <v>6396872</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13479,18 +13485,12 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Utbrett mycel med minst 10 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13512,7 +13512,7 @@
         <v>128912411</v>
       </c>
       <c r="B124" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13606,10 +13606,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128912425</v>
+        <v>128912416</v>
       </c>
       <c r="B125" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>705415</v>
+        <v>705273</v>
       </c>
       <c r="R125" t="n">
-        <v>6396600</v>
+        <v>6396936</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13703,10 +13703,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128912416</v>
+        <v>128912425</v>
       </c>
       <c r="B126" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13738,10 +13738,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>705273</v>
+        <v>705415</v>
       </c>
       <c r="R126" t="n">
-        <v>6396936</v>
+        <v>6396600</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13803,7 +13803,7 @@
         <v>128912394</v>
       </c>
       <c r="B127" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>128912398</v>
       </c>
       <c r="B128" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13995,32 +13995,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912410</v>
+        <v>128912423</v>
       </c>
       <c r="B129" t="n">
-        <v>86985</v>
+        <v>86722</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>449</v>
+        <v>249278</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705430</v>
+        <v>705462</v>
       </c>
       <c r="R129" t="n">
-        <v>6396796</v>
+        <v>6396694</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,32 +14092,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912406</v>
+        <v>128912410</v>
       </c>
       <c r="B130" t="n">
-        <v>86864</v>
+        <v>86990</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3611</v>
+        <v>449</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705470</v>
+        <v>705430</v>
       </c>
       <c r="R130" t="n">
-        <v>6396774</v>
+        <v>6396796</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14189,10 +14189,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128912423</v>
+        <v>128912406</v>
       </c>
       <c r="B131" t="n">
-        <v>86717</v>
+        <v>86869</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14200,21 +14200,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14224,10 +14224,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>705462</v>
+        <v>705470</v>
       </c>
       <c r="R131" t="n">
-        <v>6396694</v>
+        <v>6396774</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14289,7 +14289,7 @@
         <v>128912390</v>
       </c>
       <c r="B132" t="n">
-        <v>90306</v>
+        <v>90311</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>128912407</v>
       </c>
       <c r="B133" t="n">
-        <v>86864</v>
+        <v>86869</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>128912412</v>
       </c>
       <c r="B134" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>128912382</v>
       </c>
       <c r="B135" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14670,10 +14670,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128912396</v>
+        <v>128912395</v>
       </c>
       <c r="B136" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14705,10 +14705,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>705284</v>
+        <v>705266</v>
       </c>
       <c r="R136" t="n">
-        <v>6396977</v>
+        <v>6396904</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14768,10 +14768,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128912395</v>
+        <v>128912396</v>
       </c>
       <c r="B137" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14803,10 +14803,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>705266</v>
+        <v>705284</v>
       </c>
       <c r="R137" t="n">
-        <v>6396904</v>
+        <v>6396977</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14869,7 +14869,7 @@
         <v>128912401</v>
       </c>
       <c r="B138" t="n">
-        <v>86762</v>
+        <v>86767</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>128912418</v>
       </c>
       <c r="B139" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>128912409</v>
       </c>
       <c r="B140" t="n">
-        <v>86939</v>
+        <v>86944</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>128912415</v>
       </c>
       <c r="B141" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>128912403</v>
       </c>
       <c r="B142" t="n">
-        <v>86762</v>
+        <v>86767</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>128912399</v>
       </c>
       <c r="B143" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -7103,10 +7103,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884872</v>
+        <v>128884863</v>
       </c>
       <c r="B60" t="n">
-        <v>92823</v>
+        <v>92218</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7114,21 +7114,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705338</v>
+        <v>705446</v>
       </c>
       <c r="R60" t="n">
-        <v>6396936</v>
+        <v>6396726</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7200,32 +7200,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884894</v>
+        <v>128884872</v>
       </c>
       <c r="B61" t="n">
-        <v>90981</v>
+        <v>92823</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3286</v>
+        <v>4366</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705317</v>
+        <v>705338</v>
       </c>
       <c r="R61" t="n">
-        <v>6396863</v>
+        <v>6396936</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7297,32 +7297,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884863</v>
+        <v>128884894</v>
       </c>
       <c r="B62" t="n">
-        <v>92218</v>
+        <v>90981</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>3286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705446</v>
+        <v>705317</v>
       </c>
       <c r="R62" t="n">
-        <v>6396726</v>
+        <v>6396863</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7501,45 +7501,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884875</v>
+        <v>128884294</v>
       </c>
       <c r="B64" t="n">
-        <v>90318</v>
+        <v>86729</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705428</v>
+        <v>705415</v>
       </c>
       <c r="R64" t="n">
-        <v>6396833</v>
+        <v>6396763</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,36 +7569,47 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884294</v>
+        <v>128884912</v>
       </c>
       <c r="B65" t="n">
         <v>86729</v>
@@ -7629,14 +7640,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705415</v>
+        <v>705461</v>
       </c>
       <c r="R65" t="n">
-        <v>6396763</v>
+        <v>6396579</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7666,19 +7677,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7694,22 +7695,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884912</v>
+        <v>128884879</v>
       </c>
       <c r="B66" t="n">
-        <v>86729</v>
+        <v>86975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,21 +7718,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7741,10 +7742,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705461</v>
+        <v>705537</v>
       </c>
       <c r="R66" t="n">
-        <v>6396579</v>
+        <v>6396616</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7804,32 +7805,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884879</v>
+        <v>128884875</v>
       </c>
       <c r="B67" t="n">
-        <v>86975</v>
+        <v>90318</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>2072</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7839,10 +7840,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705537</v>
+        <v>705428</v>
       </c>
       <c r="R67" t="n">
-        <v>6396616</v>
+        <v>6396833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7883,7 +7884,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884862</v>
+        <v>128889624</v>
       </c>
       <c r="B84" t="n">
-        <v>87020</v>
+        <v>90318</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3767</v>
+        <v>2072</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705398</v>
+        <v>705513</v>
       </c>
       <c r="R84" t="n">
-        <v>6396569</v>
+        <v>6396594</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,9 +9566,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9583,57 +9593,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128889624</v>
+        <v>128884882</v>
       </c>
       <c r="B85" t="n">
-        <v>90318</v>
+        <v>86774</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2072</v>
+        <v>1985</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705513</v>
+        <v>705380</v>
       </c>
       <c r="R85" t="n">
-        <v>6396594</v>
+        <v>6396917</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,19 +9673,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,22 +9690,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884882</v>
+        <v>128884862</v>
       </c>
       <c r="B86" t="n">
-        <v>86774</v>
+        <v>87020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705380</v>
+        <v>705398</v>
       </c>
       <c r="R86" t="n">
-        <v>6396917</v>
+        <v>6396569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9799,45 +9799,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128884878</v>
+        <v>128884300</v>
       </c>
       <c r="B87" t="n">
-        <v>86975</v>
+        <v>86822</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>705291</v>
+        <v>705540</v>
       </c>
       <c r="R87" t="n">
-        <v>6396809</v>
+        <v>6396625</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9867,37 +9867,46 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128884300</v>
+        <v>128884870</v>
       </c>
       <c r="B88" t="n">
         <v>86822</v>
@@ -9928,14 +9937,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>705540</v>
+        <v>705479</v>
       </c>
       <c r="R88" t="n">
-        <v>6396625</v>
+        <v>6396566</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9965,19 +9974,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9992,44 +9991,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128884870</v>
+        <v>128884878</v>
       </c>
       <c r="B89" t="n">
-        <v>86822</v>
+        <v>86975</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10039,10 +10038,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>705479</v>
+        <v>705291</v>
       </c>
       <c r="R89" t="n">
-        <v>6396566</v>
+        <v>6396809</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10083,6 +10082,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10101,45 +10101,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884304</v>
+        <v>128884864</v>
       </c>
       <c r="B90" t="n">
-        <v>86962</v>
+        <v>91029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705475</v>
+        <v>705252</v>
       </c>
       <c r="R90" t="n">
-        <v>6396577</v>
+        <v>6396894</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10169,84 +10169,78 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884907</v>
+        <v>128884896</v>
       </c>
       <c r="B91" t="n">
-        <v>90261</v>
+        <v>92847</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>970</v>
+        <v>5964</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705399</v>
+        <v>705227</v>
       </c>
       <c r="R91" t="n">
-        <v>6396889</v>
+        <v>6396932</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10306,32 +10300,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884864</v>
+        <v>128884907</v>
       </c>
       <c r="B92" t="n">
-        <v>91029</v>
+        <v>90261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10341,10 +10335,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705252</v>
+        <v>705399</v>
       </c>
       <c r="R92" t="n">
-        <v>6396894</v>
+        <v>6396889</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10404,48 +10398,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884896</v>
+        <v>128884304</v>
       </c>
       <c r="B93" t="n">
-        <v>92847</v>
+        <v>86962</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705227</v>
+        <v>705475</v>
       </c>
       <c r="R93" t="n">
-        <v>6396932</v>
+        <v>6396577</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10475,30 +10466,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11420,48 +11420,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128884874</v>
+        <v>128884911</v>
       </c>
       <c r="B103" t="n">
-        <v>90318</v>
+        <v>86729</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>705425</v>
+        <v>705527</v>
       </c>
       <c r="R103" t="n">
-        <v>6396850</v>
+        <v>6396694</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11521,7 +11518,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128884911</v>
+        <v>128884908</v>
       </c>
       <c r="B104" t="n">
         <v>86729</v>
@@ -11556,10 +11553,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>705527</v>
+        <v>705320</v>
       </c>
       <c r="R104" t="n">
-        <v>6396694</v>
+        <v>6396829</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11619,45 +11616,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884908</v>
+        <v>128884874</v>
       </c>
       <c r="B105" t="n">
-        <v>86729</v>
+        <v>90318</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705320</v>
+        <v>705425</v>
       </c>
       <c r="R105" t="n">
-        <v>6396829</v>
+        <v>6396850</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13800,32 +13800,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128912398</v>
+        <v>128912394</v>
       </c>
       <c r="B127" t="n">
-        <v>86975</v>
+        <v>86776</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13835,10 +13835,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>705492</v>
+        <v>705421</v>
       </c>
       <c r="R127" t="n">
-        <v>6396758</v>
+        <v>6396928</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13879,7 +13879,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13898,32 +13897,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128912394</v>
+        <v>128912398</v>
       </c>
       <c r="B128" t="n">
-        <v>86776</v>
+        <v>86975</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13933,10 +13932,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>705421</v>
+        <v>705492</v>
       </c>
       <c r="R128" t="n">
-        <v>6396928</v>
+        <v>6396758</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13977,6 +13976,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14480,34 +14480,30 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128912412</v>
+        <v>128912382</v>
       </c>
       <c r="B134" t="n">
-        <v>90981</v>
+        <v>92825</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14515,10 +14511,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>705316</v>
+        <v>705322</v>
       </c>
       <c r="R134" t="n">
-        <v>6396862</v>
+        <v>6396888</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14577,30 +14573,34 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128912382</v>
+        <v>128912412</v>
       </c>
       <c r="B135" t="n">
-        <v>92825</v>
+        <v>90981</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6047725</v>
+        <v>3286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14608,10 +14608,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>705322</v>
+        <v>705316</v>
       </c>
       <c r="R135" t="n">
-        <v>6396888</v>
+        <v>6396862</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15060,32 +15060,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128912409</v>
+        <v>128912415</v>
       </c>
       <c r="B140" t="n">
-        <v>86951</v>
+        <v>86729</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>705284</v>
+        <v>705249</v>
       </c>
       <c r="R140" t="n">
-        <v>6396861</v>
+        <v>6396927</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15157,32 +15157,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128912415</v>
+        <v>128912409</v>
       </c>
       <c r="B141" t="n">
-        <v>86729</v>
+        <v>86951</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15192,10 +15192,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>705249</v>
+        <v>705284</v>
       </c>
       <c r="R141" t="n">
-        <v>6396927</v>
+        <v>6396861</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6294,7 +6294,7 @@
         <v>128884885</v>
       </c>
       <c r="B52" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>128884883</v>
       </c>
       <c r="B53" t="n">
-        <v>86774</v>
+        <v>86777</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>128884302</v>
       </c>
       <c r="B54" t="n">
-        <v>86774</v>
+        <v>86777</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>128889600</v>
       </c>
       <c r="B55" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884906</v>
+        <v>128884887</v>
       </c>
       <c r="B56" t="n">
-        <v>92153</v>
+        <v>86954</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6715,21 +6715,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6031</v>
+        <v>1988</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705291</v>
+        <v>705305</v>
       </c>
       <c r="R56" t="n">
-        <v>6396952</v>
+        <v>6396830</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,32 +6801,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884884</v>
+        <v>128884894</v>
       </c>
       <c r="B57" t="n">
-        <v>91029</v>
+        <v>90984</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5741</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705475</v>
+        <v>705317</v>
       </c>
       <c r="R57" t="n">
-        <v>6396574</v>
+        <v>6396863</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6880,7 +6880,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6899,45 +6898,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884301</v>
+        <v>128884863</v>
       </c>
       <c r="B58" t="n">
-        <v>91055</v>
+        <v>92223</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705546</v>
+        <v>705446</v>
       </c>
       <c r="R58" t="n">
-        <v>6396613</v>
+        <v>6396726</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6967,19 +6966,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6994,22 +6983,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884887</v>
+        <v>128884872</v>
       </c>
       <c r="B59" t="n">
-        <v>86951</v>
+        <v>92828</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7017,21 +7006,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1988</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7041,10 +7030,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705305</v>
+        <v>705338</v>
       </c>
       <c r="R59" t="n">
-        <v>6396830</v>
+        <v>6396936</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7103,10 +7092,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884863</v>
+        <v>128884884</v>
       </c>
       <c r="B60" t="n">
-        <v>92218</v>
+        <v>91032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7114,21 +7103,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>5741</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7138,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705446</v>
+        <v>705475</v>
       </c>
       <c r="R60" t="n">
-        <v>6396726</v>
+        <v>6396574</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7182,6 +7171,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7200,10 +7190,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884872</v>
+        <v>128884906</v>
       </c>
       <c r="B61" t="n">
-        <v>92823</v>
+        <v>92158</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7211,21 +7201,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>6031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7235,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705338</v>
+        <v>705291</v>
       </c>
       <c r="R61" t="n">
-        <v>6396936</v>
+        <v>6396952</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7297,45 +7287,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884894</v>
+        <v>128884301</v>
       </c>
       <c r="B62" t="n">
-        <v>90981</v>
+        <v>91058</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705317</v>
+        <v>705546</v>
       </c>
       <c r="R62" t="n">
-        <v>6396863</v>
+        <v>6396613</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7365,9 +7355,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7382,12 +7382,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7397,7 +7397,7 @@
         <v>128890120</v>
       </c>
       <c r="B63" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7501,45 +7501,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884294</v>
+        <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>86729</v>
+        <v>90321</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705415</v>
+        <v>705428</v>
       </c>
       <c r="R64" t="n">
-        <v>6396763</v>
+        <v>6396833</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,50 +7569,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884912</v>
+        <v>128884294</v>
       </c>
       <c r="B65" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7640,14 +7629,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705461</v>
+        <v>705415</v>
       </c>
       <c r="R65" t="n">
-        <v>6396579</v>
+        <v>6396763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7677,9 +7666,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7695,22 +7694,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884879</v>
+        <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>86975</v>
+        <v>86732</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7718,21 +7717,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7742,10 +7741,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705537</v>
+        <v>705461</v>
       </c>
       <c r="R66" t="n">
-        <v>6396616</v>
+        <v>6396579</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7805,32 +7804,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884875</v>
+        <v>128884879</v>
       </c>
       <c r="B67" t="n">
-        <v>90318</v>
+        <v>86978</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2072</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7840,10 +7839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705428</v>
+        <v>705537</v>
       </c>
       <c r="R67" t="n">
-        <v>6396833</v>
+        <v>6396616</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7884,6 +7883,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>128884861</v>
       </c>
       <c r="B68" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>128884914</v>
       </c>
       <c r="B69" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8097,48 +8097,41 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884886</v>
+        <v>128884871</v>
       </c>
       <c r="B70" t="n">
-        <v>86876</v>
+        <v>87044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3611</v>
+        <v>3624</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705473</v>
+        <v>705290</v>
       </c>
       <c r="R70" t="n">
-        <v>6396572</v>
+        <v>6396809</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8179,7 +8172,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8198,45 +8190,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884865</v>
+        <v>128884886</v>
       </c>
       <c r="B71" t="n">
-        <v>91029</v>
+        <v>86879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5741</v>
+        <v>3611</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705416</v>
+        <v>705473</v>
       </c>
       <c r="R71" t="n">
-        <v>6396601</v>
+        <v>6396572</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8296,10 +8291,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884898</v>
+        <v>128884865</v>
       </c>
       <c r="B72" t="n">
-        <v>92847</v>
+        <v>91032</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8307,37 +8302,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705425</v>
+        <v>705416</v>
       </c>
       <c r="R72" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8397,10 +8389,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884871</v>
+        <v>128884898</v>
       </c>
       <c r="B73" t="n">
-        <v>87041</v>
+        <v>92852</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8408,27 +8400,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3624</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705290</v>
+        <v>705425</v>
       </c>
       <c r="R73" t="n">
         <v>6396809</v>
@@ -8472,6 +8471,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>128884868</v>
       </c>
       <c r="B74" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>128884867</v>
       </c>
       <c r="B75" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>128884869</v>
       </c>
       <c r="B76" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>128884890</v>
       </c>
       <c r="B77" t="n">
-        <v>105701</v>
+        <v>105706</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,48 +8878,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884873</v>
+        <v>128884296</v>
       </c>
       <c r="B78" t="n">
-        <v>90318</v>
+        <v>91032</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>705314</v>
+        <v>705419</v>
       </c>
       <c r="R78" t="n">
-        <v>6396809</v>
+        <v>6396769</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8949,75 +8946,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884296</v>
+        <v>128884873</v>
       </c>
       <c r="B79" t="n">
-        <v>91029</v>
+        <v>90321</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>705419</v>
+        <v>705314</v>
       </c>
       <c r="R79" t="n">
-        <v>6396769</v>
+        <v>6396809</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9047,39 +9056,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
         <v>128884299</v>
       </c>
       <c r="B80" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>128884305</v>
       </c>
       <c r="B81" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>128884866</v>
       </c>
       <c r="B82" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>128884881</v>
       </c>
       <c r="B83" t="n">
-        <v>86962</v>
+        <v>86965</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128889624</v>
+        <v>128884862</v>
       </c>
       <c r="B84" t="n">
-        <v>90318</v>
+        <v>87023</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2072</v>
+        <v>3767</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705513</v>
+        <v>705398</v>
       </c>
       <c r="R84" t="n">
-        <v>6396594</v>
+        <v>6396569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,19 +9566,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9593,57 +9583,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884882</v>
+        <v>128889624</v>
       </c>
       <c r="B85" t="n">
-        <v>86774</v>
+        <v>90321</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1985</v>
+        <v>2072</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705380</v>
+        <v>705513</v>
       </c>
       <c r="R85" t="n">
-        <v>6396917</v>
+        <v>6396594</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9673,9 +9663,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,22 +9690,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884862</v>
+        <v>128884882</v>
       </c>
       <c r="B86" t="n">
-        <v>87020</v>
+        <v>86777</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705398</v>
+        <v>705380</v>
       </c>
       <c r="R86" t="n">
-        <v>6396569</v>
+        <v>6396917</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9799,45 +9799,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128884300</v>
+        <v>128884878</v>
       </c>
       <c r="B87" t="n">
-        <v>86822</v>
+        <v>86978</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>705540</v>
+        <v>705291</v>
       </c>
       <c r="R87" t="n">
-        <v>6396625</v>
+        <v>6396809</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9867,49 +9867,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128884870</v>
+        <v>128884300</v>
       </c>
       <c r="B88" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9937,14 +9928,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>705479</v>
+        <v>705540</v>
       </c>
       <c r="R88" t="n">
-        <v>6396566</v>
+        <v>6396625</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9974,9 +9965,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9991,44 +9992,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128884878</v>
+        <v>128884870</v>
       </c>
       <c r="B89" t="n">
-        <v>86975</v>
+        <v>86825</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10038,10 +10039,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>705291</v>
+        <v>705479</v>
       </c>
       <c r="R89" t="n">
-        <v>6396809</v>
+        <v>6396566</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10082,7 +10083,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10101,32 +10101,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884864</v>
+        <v>128884907</v>
       </c>
       <c r="B90" t="n">
-        <v>91029</v>
+        <v>90264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5741</v>
+        <v>970</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705252</v>
+        <v>705399</v>
       </c>
       <c r="R90" t="n">
-        <v>6396894</v>
+        <v>6396889</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10199,48 +10199,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884896</v>
+        <v>128884304</v>
       </c>
       <c r="B91" t="n">
-        <v>92847</v>
+        <v>86965</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705227</v>
+        <v>705475</v>
       </c>
       <c r="R91" t="n">
-        <v>6396932</v>
+        <v>6396577</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10270,62 +10267,71 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884907</v>
+        <v>128884864</v>
       </c>
       <c r="B92" t="n">
-        <v>90261</v>
+        <v>91032</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>970</v>
+        <v>5741</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10335,10 +10341,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705399</v>
+        <v>705252</v>
       </c>
       <c r="R92" t="n">
-        <v>6396889</v>
+        <v>6396894</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10398,45 +10404,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884304</v>
+        <v>128884896</v>
       </c>
       <c r="B93" t="n">
-        <v>86962</v>
+        <v>92852</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705475</v>
+        <v>705227</v>
       </c>
       <c r="R93" t="n">
-        <v>6396577</v>
+        <v>6396932</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10466,71 +10475,62 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884306</v>
+        <v>128884900</v>
       </c>
       <c r="B94" t="n">
-        <v>86876</v>
+        <v>92852</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10539,14 +10539,14 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705439</v>
+        <v>705445</v>
       </c>
       <c r="R94" t="n">
-        <v>6396582</v>
+        <v>6396819</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10576,19 +10576,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10604,44 +10594,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884900</v>
+        <v>128884876</v>
       </c>
       <c r="B95" t="n">
-        <v>92847</v>
+        <v>90321</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5964</v>
+        <v>2072</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10654,10 +10644,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705445</v>
+        <v>705430</v>
       </c>
       <c r="R95" t="n">
-        <v>6396819</v>
+        <v>6396834</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10717,48 +10707,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884876</v>
+        <v>128884915</v>
       </c>
       <c r="B96" t="n">
-        <v>90318</v>
+        <v>86732</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705430</v>
+        <v>705291</v>
       </c>
       <c r="R96" t="n">
-        <v>6396834</v>
+        <v>6396949</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10799,7 +10786,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10818,10 +10804,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884915</v>
+        <v>128884306</v>
       </c>
       <c r="B97" t="n">
-        <v>86729</v>
+        <v>86879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10829,34 +10815,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705291</v>
+        <v>705439</v>
       </c>
       <c r="R97" t="n">
-        <v>6396949</v>
+        <v>6396582</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10886,77 +10875,85 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884899</v>
+        <v>128884303</v>
       </c>
       <c r="B98" t="n">
-        <v>92847</v>
+        <v>86879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705436</v>
+        <v>705477</v>
       </c>
       <c r="R98" t="n">
-        <v>6396834</v>
+        <v>6396583</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10986,40 +10983,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884897</v>
+        <v>128884899</v>
       </c>
       <c r="B99" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11054,10 +11060,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705297</v>
+        <v>705436</v>
       </c>
       <c r="R99" t="n">
-        <v>6396949</v>
+        <v>6396834</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11117,45 +11123,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884303</v>
+        <v>128884897</v>
       </c>
       <c r="B100" t="n">
-        <v>86876</v>
+        <v>92852</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705477</v>
+        <v>705297</v>
       </c>
       <c r="R100" t="n">
-        <v>6396583</v>
+        <v>6396949</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11185,39 +11194,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
         <v>128884913</v>
       </c>
       <c r="B101" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128884910</v>
       </c>
       <c r="B102" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11420,45 +11420,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128884911</v>
+        <v>128884874</v>
       </c>
       <c r="B103" t="n">
-        <v>86729</v>
+        <v>90321</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>705527</v>
+        <v>705425</v>
       </c>
       <c r="R103" t="n">
-        <v>6396694</v>
+        <v>6396850</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11521,7 +11524,7 @@
         <v>128884908</v>
       </c>
       <c r="B104" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11616,48 +11619,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884874</v>
+        <v>128884911</v>
       </c>
       <c r="B105" t="n">
-        <v>90318</v>
+        <v>86732</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705425</v>
+        <v>705527</v>
       </c>
       <c r="R105" t="n">
-        <v>6396850</v>
+        <v>6396694</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
         <v>128884877</v>
       </c>
       <c r="B106" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>128906402</v>
       </c>
       <c r="B107" t="n">
-        <v>86976</v>
+        <v>86979</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>128884909</v>
       </c>
       <c r="B108" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>128912404</v>
       </c>
       <c r="B109" t="n">
-        <v>86774</v>
+        <v>86777</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>128912419</v>
       </c>
       <c r="B110" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>128912424</v>
       </c>
       <c r="B111" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>128912420</v>
       </c>
       <c r="B112" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>128912417</v>
       </c>
       <c r="B113" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>128912385</v>
       </c>
       <c r="B114" t="n">
-        <v>90318</v>
+        <v>90321</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>128912405</v>
       </c>
       <c r="B115" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>128912408</v>
       </c>
       <c r="B116" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>128912388</v>
       </c>
       <c r="B117" t="n">
-        <v>90318</v>
+        <v>90321</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>128912380</v>
       </c>
       <c r="B118" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>128912422</v>
       </c>
       <c r="B119" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>128912402</v>
       </c>
       <c r="B120" t="n">
-        <v>86774</v>
+        <v>86777</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13209,10 +13209,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128912384</v>
+        <v>128912379</v>
       </c>
       <c r="B121" t="n">
-        <v>90307</v>
+        <v>91032</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13220,37 +13220,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6268</v>
+        <v>5741</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>705294</v>
+        <v>705404</v>
       </c>
       <c r="R121" t="n">
-        <v>6396977</v>
+        <v>6396616</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13285,18 +13282,12 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Utbrett mycel med minst 10 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13315,10 +13306,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912379</v>
+        <v>128912384</v>
       </c>
       <c r="B122" t="n">
-        <v>91029</v>
+        <v>90310</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13326,34 +13317,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5741</v>
+        <v>6268</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705404</v>
+        <v>705294</v>
       </c>
       <c r="R122" t="n">
-        <v>6396616</v>
+        <v>6396977</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13388,12 +13382,18 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>128912421</v>
       </c>
       <c r="B123" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>128912411</v>
       </c>
       <c r="B124" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>128912425</v>
       </c>
       <c r="B125" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>128912416</v>
       </c>
       <c r="B126" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>128912394</v>
       </c>
       <c r="B127" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>128912398</v>
       </c>
       <c r="B128" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>128912410</v>
       </c>
       <c r="B129" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>128912406</v>
       </c>
       <c r="B130" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>128912423</v>
       </c>
       <c r="B131" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>128912390</v>
       </c>
       <c r="B132" t="n">
-        <v>90318</v>
+        <v>90321</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>128912407</v>
       </c>
       <c r="B133" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14480,30 +14480,34 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128912382</v>
+        <v>128912412</v>
       </c>
       <c r="B134" t="n">
-        <v>92825</v>
+        <v>90984</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6047725</v>
+        <v>3286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14511,10 +14515,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>705322</v>
+        <v>705316</v>
       </c>
       <c r="R134" t="n">
-        <v>6396888</v>
+        <v>6396862</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14573,34 +14577,30 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128912412</v>
+        <v>128912382</v>
       </c>
       <c r="B135" t="n">
-        <v>90981</v>
+        <v>92830</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14608,10 +14608,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>705316</v>
+        <v>705322</v>
       </c>
       <c r="R135" t="n">
-        <v>6396862</v>
+        <v>6396888</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14673,7 +14673,7 @@
         <v>128912396</v>
       </c>
       <c r="B136" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>128912395</v>
       </c>
       <c r="B137" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14866,32 +14866,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128912401</v>
+        <v>128912418</v>
       </c>
       <c r="B138" t="n">
-        <v>86774</v>
+        <v>86732</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>705317</v>
+        <v>705286</v>
       </c>
       <c r="R138" t="n">
-        <v>6396871</v>
+        <v>6396970</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14963,32 +14963,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128912418</v>
+        <v>128912401</v>
       </c>
       <c r="B139" t="n">
-        <v>86729</v>
+        <v>86777</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14998,10 +14998,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>705286</v>
+        <v>705317</v>
       </c>
       <c r="R139" t="n">
-        <v>6396970</v>
+        <v>6396871</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15060,32 +15060,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128912415</v>
+        <v>128912409</v>
       </c>
       <c r="B140" t="n">
-        <v>86729</v>
+        <v>86954</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>705249</v>
+        <v>705284</v>
       </c>
       <c r="R140" t="n">
-        <v>6396927</v>
+        <v>6396861</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15157,32 +15157,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128912409</v>
+        <v>128912415</v>
       </c>
       <c r="B141" t="n">
-        <v>86951</v>
+        <v>86732</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15192,10 +15192,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>705284</v>
+        <v>705249</v>
       </c>
       <c r="R141" t="n">
-        <v>6396861</v>
+        <v>6396927</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15254,32 +15254,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128912403</v>
+        <v>128912399</v>
       </c>
       <c r="B142" t="n">
-        <v>86774</v>
+        <v>86978</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15289,10 +15289,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>705401</v>
+        <v>705482</v>
       </c>
       <c r="R142" t="n">
-        <v>6396966</v>
+        <v>6396750</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15333,6 +15333,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15351,32 +15352,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128912399</v>
+        <v>128912403</v>
       </c>
       <c r="B143" t="n">
-        <v>86975</v>
+        <v>86777</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15386,10 +15387,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>705482</v>
+        <v>705401</v>
       </c>
       <c r="R143" t="n">
-        <v>6396750</v>
+        <v>6396966</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15430,7 +15431,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6291,48 +6291,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884885</v>
+        <v>128884883</v>
       </c>
       <c r="B52" t="n">
-        <v>86879</v>
+        <v>86780</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3611</v>
+        <v>1985</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705360</v>
+        <v>705450</v>
       </c>
       <c r="R52" t="n">
-        <v>6396790</v>
+        <v>6396748</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6392,10 +6389,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884883</v>
+        <v>128884302</v>
       </c>
       <c r="B53" t="n">
-        <v>86777</v>
+        <v>86780</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6423,14 +6420,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705450</v>
+        <v>705513</v>
       </c>
       <c r="R53" t="n">
-        <v>6396748</v>
+        <v>6396594</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6460,75 +6457,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884302</v>
+        <v>128884885</v>
       </c>
       <c r="B54" t="n">
-        <v>86777</v>
+        <v>86882</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1985</v>
+        <v>3611</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>705513</v>
+        <v>705360</v>
       </c>
       <c r="R54" t="n">
-        <v>6396594</v>
+        <v>6396790</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,39 +6567,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6600,7 +6600,7 @@
         <v>128889600</v>
       </c>
       <c r="B55" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884887</v>
+        <v>128884884</v>
       </c>
       <c r="B56" t="n">
-        <v>86954</v>
+        <v>91035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6715,21 +6715,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1988</v>
+        <v>5741</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705305</v>
+        <v>705475</v>
       </c>
       <c r="R56" t="n">
-        <v>6396830</v>
+        <v>6396574</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6783,6 +6783,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6801,45 +6802,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884894</v>
+        <v>128884301</v>
       </c>
       <c r="B57" t="n">
-        <v>90984</v>
+        <v>91061</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705317</v>
+        <v>705546</v>
       </c>
       <c r="R57" t="n">
-        <v>6396863</v>
+        <v>6396613</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6869,9 +6870,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6886,22 +6897,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884863</v>
+        <v>128884887</v>
       </c>
       <c r="B58" t="n">
-        <v>92223</v>
+        <v>86957</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6909,21 +6920,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>1988</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6933,10 +6944,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705446</v>
+        <v>705305</v>
       </c>
       <c r="R58" t="n">
-        <v>6396726</v>
+        <v>6396830</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6998,7 +7009,7 @@
         <v>128884872</v>
       </c>
       <c r="B59" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7092,10 +7103,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884884</v>
+        <v>128884906</v>
       </c>
       <c r="B60" t="n">
-        <v>91032</v>
+        <v>92161</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,21 +7114,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5741</v>
+        <v>6031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7127,10 +7138,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705475</v>
+        <v>705291</v>
       </c>
       <c r="R60" t="n">
-        <v>6396574</v>
+        <v>6396952</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7171,7 +7182,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7190,32 +7200,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884906</v>
+        <v>128884894</v>
       </c>
       <c r="B61" t="n">
-        <v>92158</v>
+        <v>90987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6031</v>
+        <v>3286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7235,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705291</v>
+        <v>705317</v>
       </c>
       <c r="R61" t="n">
-        <v>6396952</v>
+        <v>6396863</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7287,45 +7297,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884301</v>
+        <v>128884863</v>
       </c>
       <c r="B62" t="n">
-        <v>91058</v>
+        <v>92226</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5747</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705546</v>
+        <v>705446</v>
       </c>
       <c r="R62" t="n">
-        <v>6396613</v>
+        <v>6396726</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7355,19 +7365,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7382,12 +7382,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7397,7 +7397,7 @@
         <v>128890120</v>
       </c>
       <c r="B63" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>90321</v>
+        <v>90324</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>128884294</v>
       </c>
       <c r="B65" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>128884879</v>
       </c>
       <c r="B67" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7902,32 +7902,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128884861</v>
+        <v>128884914</v>
       </c>
       <c r="B68" t="n">
-        <v>87023</v>
+        <v>86735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>705483</v>
+        <v>705401</v>
       </c>
       <c r="R68" t="n">
-        <v>6396620</v>
+        <v>6396625</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7981,6 +7981,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7999,32 +8000,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128884914</v>
+        <v>128884861</v>
       </c>
       <c r="B69" t="n">
-        <v>86732</v>
+        <v>87026</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8034,10 +8035,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>705401</v>
+        <v>705483</v>
       </c>
       <c r="R69" t="n">
-        <v>6396625</v>
+        <v>6396620</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8078,7 +8079,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884871</v>
+        <v>128884865</v>
       </c>
       <c r="B70" t="n">
-        <v>87044</v>
+        <v>91035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,19 +8108,23 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3624</v>
+        <v>5741</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8128,10 +8132,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705290</v>
+        <v>705416</v>
       </c>
       <c r="R70" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8172,6 +8176,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8190,32 +8195,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884886</v>
+        <v>128884898</v>
       </c>
       <c r="B71" t="n">
-        <v>86879</v>
+        <v>92855</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705473</v>
+        <v>705425</v>
       </c>
       <c r="R71" t="n">
-        <v>6396572</v>
+        <v>6396809</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8291,10 +8296,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884865</v>
+        <v>128884871</v>
       </c>
       <c r="B72" t="n">
-        <v>91032</v>
+        <v>87047</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8302,23 +8307,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5741</v>
+        <v>3624</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8326,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705416</v>
+        <v>705290</v>
       </c>
       <c r="R72" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8370,7 +8371,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884898</v>
+        <v>128884886</v>
       </c>
       <c r="B73" t="n">
-        <v>92852</v>
+        <v>86882</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705425</v>
+        <v>705473</v>
       </c>
       <c r="R73" t="n">
-        <v>6396809</v>
+        <v>6396572</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8493,7 +8493,7 @@
         <v>128884868</v>
       </c>
       <c r="B74" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>128884867</v>
       </c>
       <c r="B75" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>128884869</v>
       </c>
       <c r="B76" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>128884890</v>
       </c>
       <c r="B77" t="n">
-        <v>105706</v>
+        <v>105709</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,45 +8878,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884296</v>
+        <v>128884873</v>
       </c>
       <c r="B78" t="n">
-        <v>91032</v>
+        <v>90324</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>705419</v>
+        <v>705314</v>
       </c>
       <c r="R78" t="n">
-        <v>6396769</v>
+        <v>6396809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8946,87 +8949,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884873</v>
+        <v>128884296</v>
       </c>
       <c r="B79" t="n">
-        <v>90321</v>
+        <v>91035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>705314</v>
+        <v>705419</v>
       </c>
       <c r="R79" t="n">
-        <v>6396809</v>
+        <v>6396769</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9056,30 +9047,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
         <v>128884299</v>
       </c>
       <c r="B80" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>128884305</v>
       </c>
       <c r="B81" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>128884866</v>
       </c>
       <c r="B82" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>128884881</v>
       </c>
       <c r="B83" t="n">
-        <v>86965</v>
+        <v>86968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884862</v>
+        <v>128889624</v>
       </c>
       <c r="B84" t="n">
-        <v>87023</v>
+        <v>90324</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3767</v>
+        <v>2072</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705398</v>
+        <v>705513</v>
       </c>
       <c r="R84" t="n">
-        <v>6396569</v>
+        <v>6396594</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,9 +9566,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9583,57 +9593,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128889624</v>
+        <v>128884882</v>
       </c>
       <c r="B85" t="n">
-        <v>90321</v>
+        <v>86780</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2072</v>
+        <v>1985</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705513</v>
+        <v>705380</v>
       </c>
       <c r="R85" t="n">
-        <v>6396594</v>
+        <v>6396917</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,19 +9673,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,22 +9690,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884882</v>
+        <v>128884862</v>
       </c>
       <c r="B86" t="n">
-        <v>86777</v>
+        <v>87026</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705380</v>
+        <v>705398</v>
       </c>
       <c r="R86" t="n">
-        <v>6396917</v>
+        <v>6396569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9799,45 +9799,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128884878</v>
+        <v>128884300</v>
       </c>
       <c r="B87" t="n">
-        <v>86978</v>
+        <v>86828</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>705291</v>
+        <v>705540</v>
       </c>
       <c r="R87" t="n">
-        <v>6396809</v>
+        <v>6396625</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9867,40 +9867,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128884300</v>
+        <v>128884870</v>
       </c>
       <c r="B88" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9928,14 +9937,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>705540</v>
+        <v>705479</v>
       </c>
       <c r="R88" t="n">
-        <v>6396625</v>
+        <v>6396566</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9965,19 +9974,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9992,44 +9991,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128884870</v>
+        <v>128884878</v>
       </c>
       <c r="B89" t="n">
-        <v>86825</v>
+        <v>86981</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10039,10 +10038,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>705479</v>
+        <v>705291</v>
       </c>
       <c r="R89" t="n">
-        <v>6396566</v>
+        <v>6396809</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10083,6 +10082,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>128884907</v>
       </c>
       <c r="B90" t="n">
-        <v>90264</v>
+        <v>90267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>128884304</v>
       </c>
       <c r="B91" t="n">
-        <v>86965</v>
+        <v>86968</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>128884864</v>
       </c>
       <c r="B92" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>128884896</v>
       </c>
       <c r="B93" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10505,32 +10505,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884900</v>
+        <v>128884306</v>
       </c>
       <c r="B94" t="n">
-        <v>92852</v>
+        <v>86882</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10539,14 +10539,14 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705445</v>
+        <v>705439</v>
       </c>
       <c r="R94" t="n">
-        <v>6396819</v>
+        <v>6396582</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10576,9 +10576,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10594,12 +10604,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10609,7 +10619,7 @@
         <v>128884876</v>
       </c>
       <c r="B95" t="n">
-        <v>90321</v>
+        <v>90324</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10707,45 +10717,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884915</v>
+        <v>128884900</v>
       </c>
       <c r="B96" t="n">
-        <v>86732</v>
+        <v>92855</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705291</v>
+        <v>705445</v>
       </c>
       <c r="R96" t="n">
-        <v>6396949</v>
+        <v>6396819</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10786,6 +10799,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10804,10 +10818,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884306</v>
+        <v>128884915</v>
       </c>
       <c r="B97" t="n">
-        <v>86879</v>
+        <v>86735</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10815,37 +10829,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705439</v>
+        <v>705291</v>
       </c>
       <c r="R97" t="n">
-        <v>6396582</v>
+        <v>6396949</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10875,40 +10886,29 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10918,7 +10918,7 @@
         <v>128884303</v>
       </c>
       <c r="B98" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11022,48 +11022,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884899</v>
+        <v>128884913</v>
       </c>
       <c r="B99" t="n">
-        <v>92852</v>
+        <v>86735</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705436</v>
+        <v>705414</v>
       </c>
       <c r="R99" t="n">
-        <v>6396834</v>
+        <v>6396611</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11123,48 +11120,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884897</v>
+        <v>128884910</v>
       </c>
       <c r="B100" t="n">
-        <v>92852</v>
+        <v>86735</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705297</v>
+        <v>705273</v>
       </c>
       <c r="R100" t="n">
-        <v>6396949</v>
+        <v>6396934</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11224,45 +11218,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884913</v>
+        <v>128884899</v>
       </c>
       <c r="B101" t="n">
-        <v>86732</v>
+        <v>92855</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705414</v>
+        <v>705436</v>
       </c>
       <c r="R101" t="n">
-        <v>6396611</v>
+        <v>6396834</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11322,45 +11319,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884910</v>
+        <v>128884897</v>
       </c>
       <c r="B102" t="n">
-        <v>86732</v>
+        <v>92855</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705273</v>
+        <v>705297</v>
       </c>
       <c r="R102" t="n">
-        <v>6396934</v>
+        <v>6396949</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11423,7 +11423,7 @@
         <v>128884874</v>
       </c>
       <c r="B103" t="n">
-        <v>90321</v>
+        <v>90324</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>128884908</v>
       </c>
       <c r="B104" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>128884911</v>
       </c>
       <c r="B105" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>128884877</v>
       </c>
       <c r="B106" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>128906402</v>
       </c>
       <c r="B107" t="n">
-        <v>86979</v>
+        <v>86982</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>128884909</v>
       </c>
       <c r="B108" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912404</v>
+        <v>128912419</v>
       </c>
       <c r="B109" t="n">
-        <v>86777</v>
+        <v>86735</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705405</v>
+        <v>705420</v>
       </c>
       <c r="R109" t="n">
-        <v>6396928</v>
+        <v>6396917</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,10 +12132,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912419</v>
+        <v>128912424</v>
       </c>
       <c r="B110" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705420</v>
+        <v>705432</v>
       </c>
       <c r="R110" t="n">
-        <v>6396917</v>
+        <v>6396615</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,10 +12229,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912424</v>
+        <v>128912420</v>
       </c>
       <c r="B111" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705432</v>
+        <v>705443</v>
       </c>
       <c r="R111" t="n">
-        <v>6396615</v>
+        <v>6396921</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912420</v>
+        <v>128912417</v>
       </c>
       <c r="B112" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705443</v>
+        <v>705276</v>
       </c>
       <c r="R112" t="n">
-        <v>6396921</v>
+        <v>6396964</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,32 +12423,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912417</v>
+        <v>128912404</v>
       </c>
       <c r="B113" t="n">
-        <v>86732</v>
+        <v>86780</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705276</v>
+        <v>705405</v>
       </c>
       <c r="R113" t="n">
-        <v>6396964</v>
+        <v>6396928</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
         <v>128912385</v>
       </c>
       <c r="B114" t="n">
-        <v>90321</v>
+        <v>90324</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>128912405</v>
       </c>
       <c r="B115" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>128912408</v>
       </c>
       <c r="B116" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>128912388</v>
       </c>
       <c r="B117" t="n">
-        <v>90321</v>
+        <v>90324</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>128912380</v>
       </c>
       <c r="B118" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>128912422</v>
       </c>
       <c r="B119" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>128912402</v>
       </c>
       <c r="B120" t="n">
-        <v>86777</v>
+        <v>86780</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13209,32 +13209,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128912379</v>
+        <v>128912421</v>
       </c>
       <c r="B121" t="n">
-        <v>91032</v>
+        <v>86735</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5741</v>
+        <v>249278</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13244,10 +13244,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>705404</v>
+        <v>705425</v>
       </c>
       <c r="R121" t="n">
-        <v>6396616</v>
+        <v>6396872</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13306,10 +13306,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912384</v>
+        <v>128912379</v>
       </c>
       <c r="B122" t="n">
-        <v>90310</v>
+        <v>91035</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13317,37 +13317,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6268</v>
+        <v>5741</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705294</v>
+        <v>705404</v>
       </c>
       <c r="R122" t="n">
-        <v>6396977</v>
+        <v>6396616</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13382,18 +13379,12 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Utbrett mycel med minst 10 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13412,45 +13403,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128912421</v>
+        <v>128912384</v>
       </c>
       <c r="B123" t="n">
-        <v>86732</v>
+        <v>90313</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>249278</v>
+        <v>6268</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>705425</v>
+        <v>705294</v>
       </c>
       <c r="R123" t="n">
-        <v>6396872</v>
+        <v>6396977</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13485,12 +13479,18 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13512,7 +13512,7 @@
         <v>128912411</v>
       </c>
       <c r="B124" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>128912425</v>
       </c>
       <c r="B125" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>128912416</v>
       </c>
       <c r="B126" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13800,32 +13800,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128912394</v>
+        <v>128912398</v>
       </c>
       <c r="B127" t="n">
-        <v>86779</v>
+        <v>86981</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13835,10 +13835,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>705421</v>
+        <v>705492</v>
       </c>
       <c r="R127" t="n">
-        <v>6396928</v>
+        <v>6396758</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13879,6 +13879,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13897,32 +13898,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128912398</v>
+        <v>128912394</v>
       </c>
       <c r="B128" t="n">
-        <v>86978</v>
+        <v>86782</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13932,10 +13933,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>705492</v>
+        <v>705421</v>
       </c>
       <c r="R128" t="n">
-        <v>6396758</v>
+        <v>6396928</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13976,7 +13977,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13995,32 +13995,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912410</v>
+        <v>128912406</v>
       </c>
       <c r="B129" t="n">
-        <v>87000</v>
+        <v>86882</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>449</v>
+        <v>3611</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705430</v>
+        <v>705470</v>
       </c>
       <c r="R129" t="n">
-        <v>6396796</v>
+        <v>6396774</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,32 +14092,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912406</v>
+        <v>128912410</v>
       </c>
       <c r="B130" t="n">
-        <v>86879</v>
+        <v>87003</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3611</v>
+        <v>449</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705470</v>
+        <v>705430</v>
       </c>
       <c r="R130" t="n">
-        <v>6396774</v>
+        <v>6396796</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14192,7 +14192,7 @@
         <v>128912423</v>
       </c>
       <c r="B131" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>128912390</v>
       </c>
       <c r="B132" t="n">
-        <v>90321</v>
+        <v>90324</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>128912407</v>
       </c>
       <c r="B133" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14480,34 +14480,30 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128912412</v>
+        <v>128912382</v>
       </c>
       <c r="B134" t="n">
-        <v>90984</v>
+        <v>92833</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14515,10 +14511,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>705316</v>
+        <v>705322</v>
       </c>
       <c r="R134" t="n">
-        <v>6396862</v>
+        <v>6396888</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14577,30 +14573,34 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128912382</v>
+        <v>128912412</v>
       </c>
       <c r="B135" t="n">
-        <v>92830</v>
+        <v>90987</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6047725</v>
+        <v>3286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14608,10 +14608,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>705322</v>
+        <v>705316</v>
       </c>
       <c r="R135" t="n">
-        <v>6396888</v>
+        <v>6396862</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14670,10 +14670,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128912396</v>
+        <v>128912395</v>
       </c>
       <c r="B136" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14705,10 +14705,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>705284</v>
+        <v>705266</v>
       </c>
       <c r="R136" t="n">
-        <v>6396977</v>
+        <v>6396904</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14768,10 +14768,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128912395</v>
+        <v>128912396</v>
       </c>
       <c r="B137" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14803,10 +14803,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>705266</v>
+        <v>705284</v>
       </c>
       <c r="R137" t="n">
-        <v>6396904</v>
+        <v>6396977</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14869,7 +14869,7 @@
         <v>128912418</v>
       </c>
       <c r="B138" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>128912401</v>
       </c>
       <c r="B139" t="n">
-        <v>86777</v>
+        <v>86780</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>128912409</v>
       </c>
       <c r="B140" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>128912415</v>
       </c>
       <c r="B141" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15254,32 +15254,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128912399</v>
+        <v>128912403</v>
       </c>
       <c r="B142" t="n">
-        <v>86978</v>
+        <v>86780</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15289,10 +15289,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>705482</v>
+        <v>705401</v>
       </c>
       <c r="R142" t="n">
-        <v>6396750</v>
+        <v>6396966</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15333,7 +15333,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15352,32 +15351,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128912403</v>
+        <v>128912399</v>
       </c>
       <c r="B143" t="n">
-        <v>86777</v>
+        <v>86981</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15387,10 +15386,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>705401</v>
+        <v>705482</v>
       </c>
       <c r="R143" t="n">
-        <v>6396966</v>
+        <v>6396750</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15431,6 +15430,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY143"/>
+  <dimension ref="A1:AY144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6704,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884884</v>
+        <v>128884887</v>
       </c>
       <c r="B56" t="n">
-        <v>91035</v>
+        <v>86957</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6715,21 +6715,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5741</v>
+        <v>1988</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705475</v>
+        <v>705305</v>
       </c>
       <c r="R56" t="n">
-        <v>6396574</v>
+        <v>6396830</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6783,7 +6783,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6802,45 +6801,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884301</v>
+        <v>128884894</v>
       </c>
       <c r="B57" t="n">
-        <v>91061</v>
+        <v>90987</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705546</v>
+        <v>705317</v>
       </c>
       <c r="R57" t="n">
-        <v>6396613</v>
+        <v>6396863</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6870,19 +6869,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6897,22 +6886,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884887</v>
+        <v>128884863</v>
       </c>
       <c r="B58" t="n">
-        <v>86957</v>
+        <v>92226</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6920,21 +6909,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1988</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6944,10 +6933,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705305</v>
+        <v>705446</v>
       </c>
       <c r="R58" t="n">
-        <v>6396830</v>
+        <v>6396726</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7200,32 +7189,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884894</v>
+        <v>128884884</v>
       </c>
       <c r="B61" t="n">
-        <v>90987</v>
+        <v>91035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3286</v>
+        <v>5741</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7235,10 +7224,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705317</v>
+        <v>705475</v>
       </c>
       <c r="R61" t="n">
-        <v>6396863</v>
+        <v>6396574</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7279,6 +7268,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7297,45 +7287,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884863</v>
+        <v>128884301</v>
       </c>
       <c r="B62" t="n">
-        <v>92226</v>
+        <v>91061</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>5747</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705446</v>
+        <v>705546</v>
       </c>
       <c r="R62" t="n">
-        <v>6396726</v>
+        <v>6396613</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7365,9 +7355,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7382,12 +7382,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7501,45 +7501,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884875</v>
+        <v>128884294</v>
       </c>
       <c r="B64" t="n">
-        <v>90324</v>
+        <v>86735</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705428</v>
+        <v>705415</v>
       </c>
       <c r="R64" t="n">
-        <v>6396833</v>
+        <v>6396763</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,36 +7569,47 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884294</v>
+        <v>128884912</v>
       </c>
       <c r="B65" t="n">
         <v>86735</v>
@@ -7629,14 +7640,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705415</v>
+        <v>705461</v>
       </c>
       <c r="R65" t="n">
-        <v>6396763</v>
+        <v>6396579</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7666,19 +7677,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7694,22 +7695,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884912</v>
+        <v>128884879</v>
       </c>
       <c r="B66" t="n">
-        <v>86735</v>
+        <v>86981</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,21 +7718,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7741,10 +7742,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705461</v>
+        <v>705537</v>
       </c>
       <c r="R66" t="n">
-        <v>6396579</v>
+        <v>6396616</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7804,32 +7805,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884879</v>
+        <v>128884875</v>
       </c>
       <c r="B67" t="n">
-        <v>86981</v>
+        <v>90324</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>2072</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7839,10 +7840,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705537</v>
+        <v>705428</v>
       </c>
       <c r="R67" t="n">
-        <v>6396616</v>
+        <v>6396833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7883,7 +7884,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7902,32 +7902,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128884914</v>
+        <v>128884861</v>
       </c>
       <c r="B68" t="n">
-        <v>86735</v>
+        <v>87026</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>705401</v>
+        <v>705483</v>
       </c>
       <c r="R68" t="n">
-        <v>6396625</v>
+        <v>6396620</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7981,7 +7981,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8000,32 +7999,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128884861</v>
+        <v>128884914</v>
       </c>
       <c r="B69" t="n">
-        <v>87026</v>
+        <v>86735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8035,10 +8034,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>705483</v>
+        <v>705401</v>
       </c>
       <c r="R69" t="n">
-        <v>6396620</v>
+        <v>6396625</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8079,6 +8078,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884865</v>
+        <v>128884871</v>
       </c>
       <c r="B70" t="n">
-        <v>91035</v>
+        <v>87047</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,23 +8108,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5741</v>
+        <v>3624</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8132,10 +8128,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705416</v>
+        <v>705290</v>
       </c>
       <c r="R70" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8176,7 +8172,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8195,32 +8190,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884898</v>
+        <v>128884886</v>
       </c>
       <c r="B71" t="n">
-        <v>92855</v>
+        <v>86882</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8233,10 +8228,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705425</v>
+        <v>705473</v>
       </c>
       <c r="R71" t="n">
-        <v>6396809</v>
+        <v>6396572</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8296,10 +8291,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884871</v>
+        <v>128884865</v>
       </c>
       <c r="B72" t="n">
-        <v>87047</v>
+        <v>91035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8307,19 +8302,23 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3624</v>
+        <v>5741</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8327,10 +8326,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705290</v>
+        <v>705416</v>
       </c>
       <c r="R72" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8371,6 +8370,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884886</v>
+        <v>128884898</v>
       </c>
       <c r="B73" t="n">
-        <v>86882</v>
+        <v>92855</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705473</v>
+        <v>705425</v>
       </c>
       <c r="R73" t="n">
-        <v>6396572</v>
+        <v>6396809</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884867</v>
+        <v>128884869</v>
       </c>
       <c r="B75" t="n">
-        <v>91035</v>
+        <v>86828</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5741</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>705431</v>
+        <v>705297</v>
       </c>
       <c r="R75" t="n">
-        <v>6396688</v>
+        <v>6396817</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8684,32 +8684,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884869</v>
+        <v>128884867</v>
       </c>
       <c r="B76" t="n">
-        <v>86828</v>
+        <v>91035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>424</v>
+        <v>5741</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>705297</v>
+        <v>705431</v>
       </c>
       <c r="R76" t="n">
-        <v>6396817</v>
+        <v>6396688</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8878,48 +8878,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884873</v>
+        <v>128884296</v>
       </c>
       <c r="B78" t="n">
-        <v>90324</v>
+        <v>91035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>705314</v>
+        <v>705419</v>
       </c>
       <c r="R78" t="n">
-        <v>6396809</v>
+        <v>6396769</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8949,75 +8946,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884296</v>
+        <v>128884873</v>
       </c>
       <c r="B79" t="n">
-        <v>91035</v>
+        <v>90324</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>705419</v>
+        <v>705314</v>
       </c>
       <c r="R79" t="n">
-        <v>6396769</v>
+        <v>6396809</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9047,39 +9056,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9193,45 +9193,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884305</v>
+        <v>128884881</v>
       </c>
       <c r="B81" t="n">
-        <v>91035</v>
+        <v>86968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>705468</v>
+        <v>705474</v>
       </c>
       <c r="R81" t="n">
-        <v>6396595</v>
+        <v>6396574</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9261,46 +9264,37 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884866</v>
+        <v>128884305</v>
       </c>
       <c r="B82" t="n">
         <v>91035</v>
@@ -9331,14 +9325,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>705433</v>
+        <v>705468</v>
       </c>
       <c r="R82" t="n">
-        <v>6396684</v>
+        <v>6396595</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9368,9 +9362,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9385,60 +9389,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128884881</v>
+        <v>128884866</v>
       </c>
       <c r="B83" t="n">
-        <v>86968</v>
+        <v>91035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>705474</v>
+        <v>705433</v>
       </c>
       <c r="R83" t="n">
-        <v>6396574</v>
+        <v>6396684</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9479,7 +9480,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10101,45 +10101,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884907</v>
+        <v>128884304</v>
       </c>
       <c r="B90" t="n">
-        <v>90267</v>
+        <v>86968</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>970</v>
+        <v>3599</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705399</v>
+        <v>705475</v>
       </c>
       <c r="R90" t="n">
-        <v>6396889</v>
+        <v>6396577</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10169,75 +10169,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884304</v>
+        <v>128884907</v>
       </c>
       <c r="B91" t="n">
-        <v>86968</v>
+        <v>90267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3599</v>
+        <v>970</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705475</v>
+        <v>705399</v>
       </c>
       <c r="R91" t="n">
-        <v>6396577</v>
+        <v>6396889</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10267,39 +10276,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884306</v>
+        <v>128884915</v>
       </c>
       <c r="B94" t="n">
-        <v>86882</v>
+        <v>86735</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10516,37 +10516,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705439</v>
+        <v>705291</v>
       </c>
       <c r="R94" t="n">
-        <v>6396582</v>
+        <v>6396949</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10576,40 +10573,29 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10717,32 +10703,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884900</v>
+        <v>128884306</v>
       </c>
       <c r="B96" t="n">
-        <v>92855</v>
+        <v>86882</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10751,14 +10737,14 @@
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705445</v>
+        <v>705439</v>
       </c>
       <c r="R96" t="n">
-        <v>6396819</v>
+        <v>6396582</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10788,9 +10774,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10806,57 +10802,60 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884915</v>
+        <v>128884900</v>
       </c>
       <c r="B97" t="n">
-        <v>86735</v>
+        <v>92855</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705291</v>
+        <v>705445</v>
       </c>
       <c r="R97" t="n">
-        <v>6396949</v>
+        <v>6396819</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10897,6 +10896,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10915,10 +10915,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884303</v>
+        <v>128884913</v>
       </c>
       <c r="B98" t="n">
-        <v>86882</v>
+        <v>86735</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705477</v>
+        <v>705414</v>
       </c>
       <c r="R98" t="n">
-        <v>6396583</v>
+        <v>6396611</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10983,46 +10983,37 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884913</v>
+        <v>128884910</v>
       </c>
       <c r="B99" t="n">
         <v>86735</v>
@@ -11057,10 +11048,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705414</v>
+        <v>705273</v>
       </c>
       <c r="R99" t="n">
-        <v>6396611</v>
+        <v>6396934</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11120,10 +11111,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884910</v>
+        <v>128884303</v>
       </c>
       <c r="B100" t="n">
-        <v>86735</v>
+        <v>86882</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11131,34 +11122,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705273</v>
+        <v>705477</v>
       </c>
       <c r="R100" t="n">
-        <v>6396934</v>
+        <v>6396583</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11188,30 +11179,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11420,48 +11420,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128884874</v>
+        <v>128884908</v>
       </c>
       <c r="B103" t="n">
-        <v>90324</v>
+        <v>86735</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>705425</v>
+        <v>705320</v>
       </c>
       <c r="R103" t="n">
-        <v>6396850</v>
+        <v>6396829</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11521,7 +11518,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128884908</v>
+        <v>128884911</v>
       </c>
       <c r="B104" t="n">
         <v>86735</v>
@@ -11556,10 +11553,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>705320</v>
+        <v>705527</v>
       </c>
       <c r="R104" t="n">
-        <v>6396829</v>
+        <v>6396694</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11619,45 +11616,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884911</v>
+        <v>128884874</v>
       </c>
       <c r="B105" t="n">
-        <v>86735</v>
+        <v>90324</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705527</v>
+        <v>705425</v>
       </c>
       <c r="R105" t="n">
-        <v>6396694</v>
+        <v>6396850</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912419</v>
+        <v>128912404</v>
       </c>
       <c r="B109" t="n">
-        <v>86735</v>
+        <v>86780</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705420</v>
+        <v>705405</v>
       </c>
       <c r="R109" t="n">
-        <v>6396917</v>
+        <v>6396928</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912424</v>
+        <v>128912417</v>
       </c>
       <c r="B110" t="n">
         <v>86735</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705432</v>
+        <v>705276</v>
       </c>
       <c r="R110" t="n">
-        <v>6396615</v>
+        <v>6396964</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12326,7 +12326,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912417</v>
+        <v>128912424</v>
       </c>
       <c r="B112" t="n">
         <v>86735</v>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705276</v>
+        <v>705432</v>
       </c>
       <c r="R112" t="n">
-        <v>6396964</v>
+        <v>6396615</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,32 +12423,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912404</v>
+        <v>128912419</v>
       </c>
       <c r="B113" t="n">
-        <v>86780</v>
+        <v>86735</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705405</v>
+        <v>705420</v>
       </c>
       <c r="R113" t="n">
-        <v>6396928</v>
+        <v>6396917</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13209,32 +13209,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128912421</v>
+        <v>128912379</v>
       </c>
       <c r="B121" t="n">
-        <v>86735</v>
+        <v>91035</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>249278</v>
+        <v>5741</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13244,10 +13244,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>705425</v>
+        <v>705404</v>
       </c>
       <c r="R121" t="n">
-        <v>6396872</v>
+        <v>6396616</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13306,10 +13306,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912379</v>
+        <v>128912384</v>
       </c>
       <c r="B122" t="n">
-        <v>91035</v>
+        <v>90313</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13317,34 +13317,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5741</v>
+        <v>6268</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705404</v>
+        <v>705294</v>
       </c>
       <c r="R122" t="n">
-        <v>6396616</v>
+        <v>6396977</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13379,12 +13382,18 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13403,48 +13412,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128912384</v>
+        <v>128912421</v>
       </c>
       <c r="B123" t="n">
-        <v>90313</v>
+        <v>86735</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6268</v>
+        <v>249278</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>705294</v>
+        <v>705425</v>
       </c>
       <c r="R123" t="n">
-        <v>6396977</v>
+        <v>6396872</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13479,18 +13485,12 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Utbrett mycel med minst 10 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13606,7 +13606,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128912425</v>
+        <v>128912416</v>
       </c>
       <c r="B125" t="n">
         <v>86735</v>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>705415</v>
+        <v>705273</v>
       </c>
       <c r="R125" t="n">
-        <v>6396600</v>
+        <v>6396936</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13703,7 +13703,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128912416</v>
+        <v>128912425</v>
       </c>
       <c r="B126" t="n">
         <v>86735</v>
@@ -13738,10 +13738,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>705273</v>
+        <v>705415</v>
       </c>
       <c r="R126" t="n">
-        <v>6396936</v>
+        <v>6396600</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13995,10 +13995,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912406</v>
+        <v>128912423</v>
       </c>
       <c r="B129" t="n">
-        <v>86882</v>
+        <v>86735</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14006,21 +14006,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705470</v>
+        <v>705462</v>
       </c>
       <c r="R129" t="n">
-        <v>6396774</v>
+        <v>6396694</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,32 +14092,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912410</v>
+        <v>128912406</v>
       </c>
       <c r="B130" t="n">
-        <v>87003</v>
+        <v>86882</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>449</v>
+        <v>3611</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705430</v>
+        <v>705470</v>
       </c>
       <c r="R130" t="n">
-        <v>6396796</v>
+        <v>6396774</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14189,32 +14189,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128912423</v>
+        <v>128912410</v>
       </c>
       <c r="B131" t="n">
-        <v>86735</v>
+        <v>87003</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>249278</v>
+        <v>449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14224,10 +14224,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>705462</v>
+        <v>705430</v>
       </c>
       <c r="R131" t="n">
-        <v>6396694</v>
+        <v>6396796</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14670,7 +14670,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128912395</v>
+        <v>128912396</v>
       </c>
       <c r="B136" t="n">
         <v>86981</v>
@@ -14705,10 +14705,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>705266</v>
+        <v>705284</v>
       </c>
       <c r="R136" t="n">
-        <v>6396904</v>
+        <v>6396977</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14768,7 +14768,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128912396</v>
+        <v>128912395</v>
       </c>
       <c r="B137" t="n">
         <v>86981</v>
@@ -14803,10 +14803,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>705284</v>
+        <v>705266</v>
       </c>
       <c r="R137" t="n">
-        <v>6396977</v>
+        <v>6396904</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14866,32 +14866,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128912418</v>
+        <v>128912401</v>
       </c>
       <c r="B138" t="n">
-        <v>86735</v>
+        <v>86780</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>705286</v>
+        <v>705317</v>
       </c>
       <c r="R138" t="n">
-        <v>6396970</v>
+        <v>6396871</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14963,32 +14963,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128912401</v>
+        <v>128912418</v>
       </c>
       <c r="B139" t="n">
-        <v>86780</v>
+        <v>86735</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14998,10 +14998,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>705317</v>
+        <v>705286</v>
       </c>
       <c r="R139" t="n">
-        <v>6396871</v>
+        <v>6396970</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15060,32 +15060,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128912409</v>
+        <v>128912415</v>
       </c>
       <c r="B140" t="n">
-        <v>86957</v>
+        <v>86735</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>705284</v>
+        <v>705249</v>
       </c>
       <c r="R140" t="n">
-        <v>6396861</v>
+        <v>6396927</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15157,32 +15157,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128912415</v>
+        <v>128912409</v>
       </c>
       <c r="B141" t="n">
-        <v>86735</v>
+        <v>86957</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15192,10 +15192,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>705249</v>
+        <v>705284</v>
       </c>
       <c r="R141" t="n">
-        <v>6396927</v>
+        <v>6396861</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15447,6 +15447,125 @@
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>129214805</v>
+      </c>
+      <c r="B144" t="n">
+        <v>90313</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6268</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Rökmusseron</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Tricholoma fucatum</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Bro, Ojkare, Gtl</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>705294</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6396976</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6704,32 +6704,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884887</v>
+        <v>128884894</v>
       </c>
       <c r="B56" t="n">
-        <v>86957</v>
+        <v>90987</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1988</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705305</v>
+        <v>705317</v>
       </c>
       <c r="R56" t="n">
-        <v>6396830</v>
+        <v>6396863</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,32 +6801,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884894</v>
+        <v>128884863</v>
       </c>
       <c r="B57" t="n">
-        <v>90987</v>
+        <v>92226</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705317</v>
+        <v>705446</v>
       </c>
       <c r="R57" t="n">
-        <v>6396863</v>
+        <v>6396726</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884863</v>
+        <v>128884872</v>
       </c>
       <c r="B58" t="n">
-        <v>92226</v>
+        <v>92831</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705446</v>
+        <v>705338</v>
       </c>
       <c r="R58" t="n">
-        <v>6396726</v>
+        <v>6396936</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6995,10 +6995,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884872</v>
+        <v>128884887</v>
       </c>
       <c r="B59" t="n">
-        <v>92831</v>
+        <v>86957</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7006,21 +7006,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4366</v>
+        <v>1988</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705338</v>
+        <v>705305</v>
       </c>
       <c r="R59" t="n">
-        <v>6396936</v>
+        <v>6396830</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7501,45 +7501,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884294</v>
+        <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>86735</v>
+        <v>90324</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705415</v>
+        <v>705428</v>
       </c>
       <c r="R64" t="n">
-        <v>6396763</v>
+        <v>6396833</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,47 +7569,36 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884912</v>
+        <v>128884294</v>
       </c>
       <c r="B65" t="n">
         <v>86735</v>
@@ -7640,14 +7629,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705461</v>
+        <v>705415</v>
       </c>
       <c r="R65" t="n">
-        <v>6396579</v>
+        <v>6396763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7677,9 +7666,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7695,22 +7694,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884879</v>
+        <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>86981</v>
+        <v>86735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7718,21 +7717,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7742,10 +7741,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705537</v>
+        <v>705461</v>
       </c>
       <c r="R66" t="n">
-        <v>6396616</v>
+        <v>6396579</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7805,32 +7804,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884875</v>
+        <v>128884879</v>
       </c>
       <c r="B67" t="n">
-        <v>90324</v>
+        <v>86981</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2072</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7840,10 +7839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705428</v>
+        <v>705537</v>
       </c>
       <c r="R67" t="n">
-        <v>6396833</v>
+        <v>6396616</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7884,6 +7883,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -10101,45 +10101,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884304</v>
+        <v>128884907</v>
       </c>
       <c r="B90" t="n">
-        <v>86968</v>
+        <v>90267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3599</v>
+        <v>970</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705475</v>
+        <v>705399</v>
       </c>
       <c r="R90" t="n">
-        <v>6396577</v>
+        <v>6396889</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10169,71 +10169,62 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884907</v>
+        <v>128884864</v>
       </c>
       <c r="B91" t="n">
-        <v>90267</v>
+        <v>91035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>970</v>
+        <v>5741</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10243,10 +10234,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705399</v>
+        <v>705252</v>
       </c>
       <c r="R91" t="n">
-        <v>6396889</v>
+        <v>6396894</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10306,10 +10297,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884864</v>
+        <v>128884896</v>
       </c>
       <c r="B92" t="n">
-        <v>91035</v>
+        <v>92855</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10317,34 +10308,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705252</v>
+        <v>705227</v>
       </c>
       <c r="R92" t="n">
-        <v>6396894</v>
+        <v>6396932</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10404,48 +10398,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884896</v>
+        <v>128884304</v>
       </c>
       <c r="B93" t="n">
-        <v>92855</v>
+        <v>86968</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705227</v>
+        <v>705475</v>
       </c>
       <c r="R93" t="n">
-        <v>6396932</v>
+        <v>6396577</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10475,30 +10466,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10915,10 +10915,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884913</v>
+        <v>128884303</v>
       </c>
       <c r="B98" t="n">
-        <v>86735</v>
+        <v>86882</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705414</v>
+        <v>705477</v>
       </c>
       <c r="R98" t="n">
-        <v>6396611</v>
+        <v>6396583</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10983,37 +10983,46 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884910</v>
+        <v>128884913</v>
       </c>
       <c r="B99" t="n">
         <v>86735</v>
@@ -11048,10 +11057,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705273</v>
+        <v>705414</v>
       </c>
       <c r="R99" t="n">
-        <v>6396934</v>
+        <v>6396611</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11111,10 +11120,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884303</v>
+        <v>128884910</v>
       </c>
       <c r="B100" t="n">
-        <v>86882</v>
+        <v>86735</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11122,34 +11131,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705477</v>
+        <v>705273</v>
       </c>
       <c r="R100" t="n">
-        <v>6396583</v>
+        <v>6396934</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11179,39 +11188,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11420,45 +11420,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128884908</v>
+        <v>128884874</v>
       </c>
       <c r="B103" t="n">
-        <v>86735</v>
+        <v>90324</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>705320</v>
+        <v>705425</v>
       </c>
       <c r="R103" t="n">
-        <v>6396829</v>
+        <v>6396850</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11518,7 +11521,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128884911</v>
+        <v>128884908</v>
       </c>
       <c r="B104" t="n">
         <v>86735</v>
@@ -11553,10 +11556,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>705527</v>
+        <v>705320</v>
       </c>
       <c r="R104" t="n">
-        <v>6396694</v>
+        <v>6396829</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11616,48 +11619,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884874</v>
+        <v>128884911</v>
       </c>
       <c r="B105" t="n">
-        <v>90324</v>
+        <v>86735</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705425</v>
+        <v>705527</v>
       </c>
       <c r="R105" t="n">
-        <v>6396850</v>
+        <v>6396694</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912404</v>
+        <v>128912417</v>
       </c>
       <c r="B109" t="n">
-        <v>86780</v>
+        <v>86735</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705405</v>
+        <v>705276</v>
       </c>
       <c r="R109" t="n">
-        <v>6396928</v>
+        <v>6396964</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912417</v>
+        <v>128912420</v>
       </c>
       <c r="B110" t="n">
         <v>86735</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705276</v>
+        <v>705443</v>
       </c>
       <c r="R110" t="n">
-        <v>6396964</v>
+        <v>6396921</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,7 +12229,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912420</v>
+        <v>128912424</v>
       </c>
       <c r="B111" t="n">
         <v>86735</v>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705443</v>
+        <v>705432</v>
       </c>
       <c r="R111" t="n">
-        <v>6396921</v>
+        <v>6396615</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,7 +12326,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912424</v>
+        <v>128912419</v>
       </c>
       <c r="B112" t="n">
         <v>86735</v>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705432</v>
+        <v>705420</v>
       </c>
       <c r="R112" t="n">
-        <v>6396615</v>
+        <v>6396917</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,32 +12423,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912419</v>
+        <v>128912404</v>
       </c>
       <c r="B113" t="n">
-        <v>86735</v>
+        <v>86780</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705420</v>
+        <v>705405</v>
       </c>
       <c r="R113" t="n">
-        <v>6396917</v>
+        <v>6396928</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12816,32 +12816,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128912388</v>
+        <v>128912422</v>
       </c>
       <c r="B117" t="n">
-        <v>90324</v>
+        <v>86735</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12851,10 +12851,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>705434</v>
+        <v>705469</v>
       </c>
       <c r="R117" t="n">
-        <v>6396836</v>
+        <v>6396714</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12887,11 +12887,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>4 st</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12918,32 +12913,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128912380</v>
+        <v>128912388</v>
       </c>
       <c r="B118" t="n">
-        <v>91035</v>
+        <v>90324</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12953,10 +12948,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>705428</v>
+        <v>705434</v>
       </c>
       <c r="R118" t="n">
-        <v>6396581</v>
+        <v>6396836</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12989,6 +12984,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13015,32 +13015,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128912422</v>
+        <v>128912380</v>
       </c>
       <c r="B119" t="n">
-        <v>86735</v>
+        <v>91035</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>249278</v>
+        <v>5741</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13050,10 +13050,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>705469</v>
+        <v>705428</v>
       </c>
       <c r="R119" t="n">
-        <v>6396714</v>
+        <v>6396581</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14480,30 +14480,34 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128912382</v>
+        <v>128912412</v>
       </c>
       <c r="B134" t="n">
-        <v>92833</v>
+        <v>90987</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6047725</v>
+        <v>3286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14511,10 +14515,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>705322</v>
+        <v>705316</v>
       </c>
       <c r="R134" t="n">
-        <v>6396888</v>
+        <v>6396862</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14573,34 +14577,30 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128912412</v>
+        <v>128912382</v>
       </c>
       <c r="B135" t="n">
-        <v>90987</v>
+        <v>92833</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3286</v>
+        <v>6047725</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14608,10 +14608,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>705316</v>
+        <v>705322</v>
       </c>
       <c r="R135" t="n">
-        <v>6396862</v>
+        <v>6396888</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6704,32 +6704,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884894</v>
+        <v>128884887</v>
       </c>
       <c r="B56" t="n">
-        <v>90987</v>
+        <v>86957</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>1988</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705317</v>
+        <v>705305</v>
       </c>
       <c r="R56" t="n">
-        <v>6396863</v>
+        <v>6396830</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,32 +6801,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884863</v>
+        <v>128884894</v>
       </c>
       <c r="B57" t="n">
-        <v>92226</v>
+        <v>90987</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705446</v>
+        <v>705317</v>
       </c>
       <c r="R57" t="n">
-        <v>6396726</v>
+        <v>6396863</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884872</v>
+        <v>128884863</v>
       </c>
       <c r="B58" t="n">
-        <v>92831</v>
+        <v>92226</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705338</v>
+        <v>705446</v>
       </c>
       <c r="R58" t="n">
-        <v>6396936</v>
+        <v>6396726</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6995,10 +6995,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884887</v>
+        <v>128884872</v>
       </c>
       <c r="B59" t="n">
-        <v>86957</v>
+        <v>92831</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7006,21 +7006,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1988</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705305</v>
+        <v>705338</v>
       </c>
       <c r="R59" t="n">
-        <v>6396830</v>
+        <v>6396936</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7092,45 +7092,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884906</v>
+        <v>128884301</v>
       </c>
       <c r="B60" t="n">
-        <v>92161</v>
+        <v>91061</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6031</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705291</v>
+        <v>705546</v>
       </c>
       <c r="R60" t="n">
-        <v>6396952</v>
+        <v>6396613</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7160,9 +7160,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7177,12 +7187,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7287,45 +7297,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884301</v>
+        <v>128884906</v>
       </c>
       <c r="B62" t="n">
-        <v>91061</v>
+        <v>92161</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5747</v>
+        <v>6031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705546</v>
+        <v>705291</v>
       </c>
       <c r="R62" t="n">
-        <v>6396613</v>
+        <v>6396952</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7355,19 +7365,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7382,12 +7382,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7501,45 +7501,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884875</v>
+        <v>128884294</v>
       </c>
       <c r="B64" t="n">
-        <v>90324</v>
+        <v>86735</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705428</v>
+        <v>705415</v>
       </c>
       <c r="R64" t="n">
-        <v>6396833</v>
+        <v>6396763</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,36 +7569,47 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884294</v>
+        <v>128884912</v>
       </c>
       <c r="B65" t="n">
         <v>86735</v>
@@ -7629,14 +7640,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705415</v>
+        <v>705461</v>
       </c>
       <c r="R65" t="n">
-        <v>6396763</v>
+        <v>6396579</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7666,19 +7677,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7694,22 +7695,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884912</v>
+        <v>128884879</v>
       </c>
       <c r="B66" t="n">
-        <v>86735</v>
+        <v>86981</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,21 +7718,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7741,10 +7742,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705461</v>
+        <v>705537</v>
       </c>
       <c r="R66" t="n">
-        <v>6396579</v>
+        <v>6396616</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7804,32 +7805,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884879</v>
+        <v>128884875</v>
       </c>
       <c r="B67" t="n">
-        <v>86981</v>
+        <v>90324</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>2072</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7839,10 +7840,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705537</v>
+        <v>705428</v>
       </c>
       <c r="R67" t="n">
-        <v>6396616</v>
+        <v>6396833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7883,7 +7884,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7902,32 +7902,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128884861</v>
+        <v>128884914</v>
       </c>
       <c r="B68" t="n">
-        <v>87026</v>
+        <v>86735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>705483</v>
+        <v>705401</v>
       </c>
       <c r="R68" t="n">
-        <v>6396620</v>
+        <v>6396625</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7981,6 +7981,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7999,32 +8000,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128884914</v>
+        <v>128884861</v>
       </c>
       <c r="B69" t="n">
-        <v>86735</v>
+        <v>87026</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8034,10 +8035,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>705401</v>
+        <v>705483</v>
       </c>
       <c r="R69" t="n">
-        <v>6396625</v>
+        <v>6396620</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8078,7 +8079,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -10199,10 +10199,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884864</v>
+        <v>128884896</v>
       </c>
       <c r="B91" t="n">
-        <v>91035</v>
+        <v>92855</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10210,34 +10210,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705252</v>
+        <v>705227</v>
       </c>
       <c r="R91" t="n">
-        <v>6396894</v>
+        <v>6396932</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10297,48 +10300,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884896</v>
+        <v>128884304</v>
       </c>
       <c r="B92" t="n">
-        <v>92855</v>
+        <v>86968</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5964</v>
+        <v>3599</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705227</v>
+        <v>705475</v>
       </c>
       <c r="R92" t="n">
-        <v>6396932</v>
+        <v>6396577</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10368,75 +10368,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884304</v>
+        <v>128884864</v>
       </c>
       <c r="B93" t="n">
-        <v>86968</v>
+        <v>91035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705475</v>
+        <v>705252</v>
       </c>
       <c r="R93" t="n">
-        <v>6396577</v>
+        <v>6396894</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10466,84 +10475,78 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884915</v>
+        <v>128884876</v>
       </c>
       <c r="B94" t="n">
-        <v>86735</v>
+        <v>90324</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705291</v>
+        <v>705430</v>
       </c>
       <c r="R94" t="n">
-        <v>6396949</v>
+        <v>6396834</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10584,6 +10587,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10602,32 +10606,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884876</v>
+        <v>128884306</v>
       </c>
       <c r="B95" t="n">
-        <v>90324</v>
+        <v>86882</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2072</v>
+        <v>3611</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10636,14 +10640,14 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705430</v>
+        <v>705439</v>
       </c>
       <c r="R95" t="n">
-        <v>6396834</v>
+        <v>6396582</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10673,9 +10677,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10691,44 +10705,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884306</v>
+        <v>128884900</v>
       </c>
       <c r="B96" t="n">
-        <v>86882</v>
+        <v>92855</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10737,14 +10751,14 @@
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705439</v>
+        <v>705445</v>
       </c>
       <c r="R96" t="n">
-        <v>6396582</v>
+        <v>6396819</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10774,19 +10788,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10802,60 +10806,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884900</v>
+        <v>128884915</v>
       </c>
       <c r="B97" t="n">
-        <v>92855</v>
+        <v>86735</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705445</v>
+        <v>705291</v>
       </c>
       <c r="R97" t="n">
-        <v>6396819</v>
+        <v>6396949</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10896,7 +10897,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11022,45 +11022,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884913</v>
+        <v>128884899</v>
       </c>
       <c r="B99" t="n">
-        <v>86735</v>
+        <v>92855</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705414</v>
+        <v>705436</v>
       </c>
       <c r="R99" t="n">
-        <v>6396611</v>
+        <v>6396834</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11120,45 +11123,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884910</v>
+        <v>128884897</v>
       </c>
       <c r="B100" t="n">
-        <v>86735</v>
+        <v>92855</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705273</v>
+        <v>705297</v>
       </c>
       <c r="R100" t="n">
-        <v>6396934</v>
+        <v>6396949</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11218,48 +11224,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884899</v>
+        <v>128884913</v>
       </c>
       <c r="B101" t="n">
-        <v>92855</v>
+        <v>86735</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705436</v>
+        <v>705414</v>
       </c>
       <c r="R101" t="n">
-        <v>6396834</v>
+        <v>6396611</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11319,48 +11322,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884897</v>
+        <v>128884910</v>
       </c>
       <c r="B102" t="n">
-        <v>92855</v>
+        <v>86735</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705297</v>
+        <v>705273</v>
       </c>
       <c r="R102" t="n">
-        <v>6396949</v>
+        <v>6396934</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12816,32 +12816,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128912422</v>
+        <v>128912380</v>
       </c>
       <c r="B117" t="n">
-        <v>86735</v>
+        <v>91035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>249278</v>
+        <v>5741</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12851,10 +12851,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>705469</v>
+        <v>705428</v>
       </c>
       <c r="R117" t="n">
-        <v>6396714</v>
+        <v>6396581</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12913,32 +12913,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128912388</v>
+        <v>128912422</v>
       </c>
       <c r="B118" t="n">
-        <v>90324</v>
+        <v>86735</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12948,10 +12948,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>705434</v>
+        <v>705469</v>
       </c>
       <c r="R118" t="n">
-        <v>6396836</v>
+        <v>6396714</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12984,11 +12984,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>4 st</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13015,32 +13010,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128912380</v>
+        <v>128912388</v>
       </c>
       <c r="B119" t="n">
-        <v>91035</v>
+        <v>90324</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13050,10 +13045,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>705428</v>
+        <v>705434</v>
       </c>
       <c r="R119" t="n">
-        <v>6396581</v>
+        <v>6396836</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13086,6 +13081,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13209,10 +13209,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128912379</v>
+        <v>128912384</v>
       </c>
       <c r="B121" t="n">
-        <v>91035</v>
+        <v>90313</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13220,34 +13220,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5741</v>
+        <v>6268</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>705404</v>
+        <v>705294</v>
       </c>
       <c r="R121" t="n">
-        <v>6396616</v>
+        <v>6396977</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13282,12 +13285,18 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13306,10 +13315,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912384</v>
+        <v>128912379</v>
       </c>
       <c r="B122" t="n">
-        <v>90313</v>
+        <v>91035</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13317,37 +13326,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6268</v>
+        <v>5741</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705294</v>
+        <v>705404</v>
       </c>
       <c r="R122" t="n">
-        <v>6396977</v>
+        <v>6396616</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13382,18 +13388,12 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Utbrett mycel med minst 10 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13800,32 +13800,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128912398</v>
+        <v>128912394</v>
       </c>
       <c r="B127" t="n">
-        <v>86981</v>
+        <v>86782</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13835,10 +13835,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>705492</v>
+        <v>705421</v>
       </c>
       <c r="R127" t="n">
-        <v>6396758</v>
+        <v>6396928</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13879,7 +13879,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13898,32 +13897,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128912394</v>
+        <v>128912398</v>
       </c>
       <c r="B128" t="n">
-        <v>86782</v>
+        <v>86981</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13933,10 +13932,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>705421</v>
+        <v>705492</v>
       </c>
       <c r="R128" t="n">
-        <v>6396928</v>
+        <v>6396758</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13977,6 +13976,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13995,32 +13995,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912423</v>
+        <v>128912410</v>
       </c>
       <c r="B129" t="n">
-        <v>86735</v>
+        <v>87003</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>249278</v>
+        <v>449</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705462</v>
+        <v>705430</v>
       </c>
       <c r="R129" t="n">
-        <v>6396694</v>
+        <v>6396796</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,10 +14092,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912406</v>
+        <v>128912423</v>
       </c>
       <c r="B130" t="n">
-        <v>86882</v>
+        <v>86735</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14103,21 +14103,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705470</v>
+        <v>705462</v>
       </c>
       <c r="R130" t="n">
-        <v>6396774</v>
+        <v>6396694</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14189,32 +14189,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128912410</v>
+        <v>128912406</v>
       </c>
       <c r="B131" t="n">
-        <v>87003</v>
+        <v>86882</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>449</v>
+        <v>3611</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14224,10 +14224,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>705430</v>
+        <v>705470</v>
       </c>
       <c r="R131" t="n">
-        <v>6396796</v>
+        <v>6396774</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14670,7 +14670,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128912396</v>
+        <v>128912395</v>
       </c>
       <c r="B136" t="n">
         <v>86981</v>
@@ -14705,10 +14705,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>705284</v>
+        <v>705266</v>
       </c>
       <c r="R136" t="n">
-        <v>6396977</v>
+        <v>6396904</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14768,7 +14768,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128912395</v>
+        <v>128912396</v>
       </c>
       <c r="B137" t="n">
         <v>86981</v>
@@ -14803,10 +14803,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>705266</v>
+        <v>705284</v>
       </c>
       <c r="R137" t="n">
-        <v>6396904</v>
+        <v>6396977</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15060,32 +15060,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128912415</v>
+        <v>128912409</v>
       </c>
       <c r="B140" t="n">
-        <v>86735</v>
+        <v>86957</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>705249</v>
+        <v>705284</v>
       </c>
       <c r="R140" t="n">
-        <v>6396927</v>
+        <v>6396861</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15157,32 +15157,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128912409</v>
+        <v>128912415</v>
       </c>
       <c r="B141" t="n">
-        <v>86957</v>
+        <v>86735</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15192,10 +15192,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>705284</v>
+        <v>705249</v>
       </c>
       <c r="R141" t="n">
-        <v>6396861</v>
+        <v>6396927</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15254,32 +15254,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128912403</v>
+        <v>128912399</v>
       </c>
       <c r="B142" t="n">
-        <v>86780</v>
+        <v>86981</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15289,10 +15289,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>705401</v>
+        <v>705482</v>
       </c>
       <c r="R142" t="n">
-        <v>6396966</v>
+        <v>6396750</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15333,6 +15333,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15351,32 +15352,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128912399</v>
+        <v>128912403</v>
       </c>
       <c r="B143" t="n">
-        <v>86981</v>
+        <v>86780</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15386,10 +15387,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>705482</v>
+        <v>705401</v>
       </c>
       <c r="R143" t="n">
-        <v>6396750</v>
+        <v>6396966</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15430,7 +15431,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6294,7 +6294,7 @@
         <v>128884883</v>
       </c>
       <c r="B52" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>128884302</v>
       </c>
       <c r="B53" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>128884885</v>
       </c>
       <c r="B54" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>128889600</v>
       </c>
       <c r="B55" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884887</v>
+        <v>128884863</v>
       </c>
       <c r="B56" t="n">
-        <v>86957</v>
+        <v>92233</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6715,21 +6715,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1988</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705305</v>
+        <v>705446</v>
       </c>
       <c r="R56" t="n">
-        <v>6396830</v>
+        <v>6396726</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,32 +6801,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884894</v>
+        <v>128884872</v>
       </c>
       <c r="B57" t="n">
-        <v>90987</v>
+        <v>92838</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705317</v>
+        <v>705338</v>
       </c>
       <c r="R57" t="n">
-        <v>6396863</v>
+        <v>6396936</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6898,45 +6898,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884863</v>
+        <v>128884301</v>
       </c>
       <c r="B58" t="n">
-        <v>92226</v>
+        <v>91065</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705446</v>
+        <v>705546</v>
       </c>
       <c r="R58" t="n">
-        <v>6396726</v>
+        <v>6396613</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6966,9 +6966,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6983,22 +6993,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884872</v>
+        <v>128884884</v>
       </c>
       <c r="B59" t="n">
-        <v>92831</v>
+        <v>91039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7006,21 +7016,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7030,10 +7040,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705338</v>
+        <v>705475</v>
       </c>
       <c r="R59" t="n">
-        <v>6396936</v>
+        <v>6396574</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7074,6 +7084,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7092,45 +7103,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884301</v>
+        <v>128884894</v>
       </c>
       <c r="B60" t="n">
-        <v>91061</v>
+        <v>90991</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705546</v>
+        <v>705317</v>
       </c>
       <c r="R60" t="n">
-        <v>6396613</v>
+        <v>6396863</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7160,19 +7171,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7187,22 +7188,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884884</v>
+        <v>128884887</v>
       </c>
       <c r="B61" t="n">
-        <v>91035</v>
+        <v>86961</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7210,21 +7211,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5741</v>
+        <v>1988</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7234,10 +7235,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705475</v>
+        <v>705305</v>
       </c>
       <c r="R61" t="n">
-        <v>6396574</v>
+        <v>6396830</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7278,7 +7279,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7300,7 +7300,7 @@
         <v>128884906</v>
       </c>
       <c r="B62" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>128890120</v>
       </c>
       <c r="B63" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7501,45 +7501,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884294</v>
+        <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>86735</v>
+        <v>90328</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705415</v>
+        <v>705428</v>
       </c>
       <c r="R64" t="n">
-        <v>6396763</v>
+        <v>6396833</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7569,50 +7569,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884912</v>
+        <v>128884294</v>
       </c>
       <c r="B65" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7640,14 +7629,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705461</v>
+        <v>705415</v>
       </c>
       <c r="R65" t="n">
-        <v>6396579</v>
+        <v>6396763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7677,9 +7666,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7695,22 +7694,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884879</v>
+        <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>86981</v>
+        <v>86739</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7718,21 +7717,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7742,10 +7741,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705537</v>
+        <v>705461</v>
       </c>
       <c r="R66" t="n">
-        <v>6396616</v>
+        <v>6396579</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7805,32 +7804,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884875</v>
+        <v>128884879</v>
       </c>
       <c r="B67" t="n">
-        <v>90324</v>
+        <v>86985</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2072</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7840,10 +7839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705428</v>
+        <v>705537</v>
       </c>
       <c r="R67" t="n">
-        <v>6396833</v>
+        <v>6396616</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7884,6 +7883,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7902,32 +7902,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128884914</v>
+        <v>128884861</v>
       </c>
       <c r="B68" t="n">
-        <v>86735</v>
+        <v>87030</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>705401</v>
+        <v>705483</v>
       </c>
       <c r="R68" t="n">
-        <v>6396625</v>
+        <v>6396620</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7981,7 +7981,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8000,32 +7999,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128884861</v>
+        <v>128884914</v>
       </c>
       <c r="B69" t="n">
-        <v>87026</v>
+        <v>86739</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8035,10 +8034,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>705483</v>
+        <v>705401</v>
       </c>
       <c r="R69" t="n">
-        <v>6396620</v>
+        <v>6396625</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8079,6 +8078,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884871</v>
+        <v>128884865</v>
       </c>
       <c r="B70" t="n">
-        <v>87047</v>
+        <v>91039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,19 +8108,23 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3624</v>
+        <v>5741</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8128,10 +8132,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705290</v>
+        <v>705416</v>
       </c>
       <c r="R70" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8172,6 +8176,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8190,32 +8195,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884886</v>
+        <v>128884898</v>
       </c>
       <c r="B71" t="n">
-        <v>86882</v>
+        <v>92862</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705473</v>
+        <v>705425</v>
       </c>
       <c r="R71" t="n">
-        <v>6396572</v>
+        <v>6396809</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8291,10 +8296,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884865</v>
+        <v>128884871</v>
       </c>
       <c r="B72" t="n">
-        <v>91035</v>
+        <v>87051</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8302,23 +8307,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5741</v>
+        <v>3624</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8326,10 +8327,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705416</v>
+        <v>705290</v>
       </c>
       <c r="R72" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8370,7 +8371,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884898</v>
+        <v>128884886</v>
       </c>
       <c r="B73" t="n">
-        <v>92855</v>
+        <v>86886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705425</v>
+        <v>705473</v>
       </c>
       <c r="R73" t="n">
-        <v>6396809</v>
+        <v>6396572</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8493,7 +8493,7 @@
         <v>128884868</v>
       </c>
       <c r="B74" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>128884869</v>
       </c>
       <c r="B75" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>128884867</v>
       </c>
       <c r="B76" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>128884890</v>
       </c>
       <c r="B77" t="n">
-        <v>105709</v>
+        <v>105719</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,45 +8878,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884296</v>
+        <v>128884873</v>
       </c>
       <c r="B78" t="n">
-        <v>91035</v>
+        <v>90328</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>705419</v>
+        <v>705314</v>
       </c>
       <c r="R78" t="n">
-        <v>6396769</v>
+        <v>6396809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8946,87 +8949,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884873</v>
+        <v>128884296</v>
       </c>
       <c r="B79" t="n">
-        <v>90324</v>
+        <v>91039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>705314</v>
+        <v>705419</v>
       </c>
       <c r="R79" t="n">
-        <v>6396809</v>
+        <v>6396769</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9056,30 +9047,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
         <v>128884299</v>
       </c>
       <c r="B80" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>128884881</v>
       </c>
       <c r="B81" t="n">
-        <v>86968</v>
+        <v>86972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>128884305</v>
       </c>
       <c r="B82" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>128884866</v>
       </c>
       <c r="B83" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>128889624</v>
       </c>
       <c r="B84" t="n">
-        <v>90324</v>
+        <v>90328</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>128884882</v>
       </c>
       <c r="B85" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>128884862</v>
       </c>
       <c r="B86" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9799,45 +9799,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128884300</v>
+        <v>128884878</v>
       </c>
       <c r="B87" t="n">
-        <v>86828</v>
+        <v>86985</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>705540</v>
+        <v>705291</v>
       </c>
       <c r="R87" t="n">
-        <v>6396625</v>
+        <v>6396809</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9867,49 +9867,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128884870</v>
+        <v>128884300</v>
       </c>
       <c r="B88" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9937,14 +9928,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>705479</v>
+        <v>705540</v>
       </c>
       <c r="R88" t="n">
-        <v>6396566</v>
+        <v>6396625</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9974,9 +9965,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9991,44 +9992,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128884878</v>
+        <v>128884870</v>
       </c>
       <c r="B89" t="n">
-        <v>86981</v>
+        <v>86832</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10038,10 +10039,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>705291</v>
+        <v>705479</v>
       </c>
       <c r="R89" t="n">
-        <v>6396809</v>
+        <v>6396566</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10082,7 +10083,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>128884907</v>
       </c>
       <c r="B90" t="n">
-        <v>90267</v>
+        <v>90271</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10199,10 +10199,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884896</v>
+        <v>128884864</v>
       </c>
       <c r="B91" t="n">
-        <v>92855</v>
+        <v>91039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10210,37 +10210,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705227</v>
+        <v>705252</v>
       </c>
       <c r="R91" t="n">
-        <v>6396932</v>
+        <v>6396894</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10300,45 +10297,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884304</v>
+        <v>128884896</v>
       </c>
       <c r="B92" t="n">
-        <v>86968</v>
+        <v>92862</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705475</v>
+        <v>705227</v>
       </c>
       <c r="R92" t="n">
-        <v>6396577</v>
+        <v>6396932</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10368,84 +10368,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884864</v>
+        <v>128884304</v>
       </c>
       <c r="B93" t="n">
-        <v>91035</v>
+        <v>86972</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705252</v>
+        <v>705475</v>
       </c>
       <c r="R93" t="n">
-        <v>6396894</v>
+        <v>6396577</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10475,62 +10466,71 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884876</v>
+        <v>128884306</v>
       </c>
       <c r="B94" t="n">
-        <v>90324</v>
+        <v>86886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2072</v>
+        <v>3611</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10539,14 +10539,14 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705430</v>
+        <v>705439</v>
       </c>
       <c r="R94" t="n">
-        <v>6396834</v>
+        <v>6396582</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10576,9 +10576,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10594,44 +10604,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884306</v>
+        <v>128884900</v>
       </c>
       <c r="B95" t="n">
-        <v>86882</v>
+        <v>92862</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10640,14 +10650,14 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705439</v>
+        <v>705445</v>
       </c>
       <c r="R95" t="n">
-        <v>6396582</v>
+        <v>6396819</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10677,19 +10687,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10705,60 +10705,57 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884900</v>
+        <v>128884915</v>
       </c>
       <c r="B96" t="n">
-        <v>92855</v>
+        <v>86739</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705445</v>
+        <v>705291</v>
       </c>
       <c r="R96" t="n">
-        <v>6396819</v>
+        <v>6396949</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10799,7 +10796,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10818,45 +10814,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884915</v>
+        <v>128884876</v>
       </c>
       <c r="B97" t="n">
-        <v>86735</v>
+        <v>90328</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705291</v>
+        <v>705430</v>
       </c>
       <c r="R97" t="n">
-        <v>6396949</v>
+        <v>6396834</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10897,6 +10896,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>128884303</v>
       </c>
       <c r="B98" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>128884899</v>
       </c>
       <c r="B99" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>128884897</v>
       </c>
       <c r="B100" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>128884913</v>
       </c>
       <c r="B101" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128884910</v>
       </c>
       <c r="B102" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>128884874</v>
       </c>
       <c r="B103" t="n">
-        <v>90324</v>
+        <v>90328</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>128884908</v>
       </c>
       <c r="B104" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>128884911</v>
       </c>
       <c r="B105" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>128884877</v>
       </c>
       <c r="B106" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>128906402</v>
       </c>
       <c r="B107" t="n">
-        <v>86982</v>
+        <v>86986</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>128884909</v>
       </c>
       <c r="B108" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912417</v>
+        <v>128912404</v>
       </c>
       <c r="B109" t="n">
-        <v>86735</v>
+        <v>86784</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705276</v>
+        <v>705405</v>
       </c>
       <c r="R109" t="n">
-        <v>6396964</v>
+        <v>6396928</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,10 +12132,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912420</v>
+        <v>128912419</v>
       </c>
       <c r="B110" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705443</v>
+        <v>705420</v>
       </c>
       <c r="R110" t="n">
-        <v>6396921</v>
+        <v>6396917</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12232,7 +12232,7 @@
         <v>128912424</v>
       </c>
       <c r="B111" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912419</v>
+        <v>128912420</v>
       </c>
       <c r="B112" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705420</v>
+        <v>705443</v>
       </c>
       <c r="R112" t="n">
-        <v>6396917</v>
+        <v>6396921</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,32 +12423,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912404</v>
+        <v>128912417</v>
       </c>
       <c r="B113" t="n">
-        <v>86780</v>
+        <v>86739</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705405</v>
+        <v>705276</v>
       </c>
       <c r="R113" t="n">
-        <v>6396928</v>
+        <v>6396964</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
         <v>128912385</v>
       </c>
       <c r="B114" t="n">
-        <v>90324</v>
+        <v>90328</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>128912405</v>
       </c>
       <c r="B115" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>128912408</v>
       </c>
       <c r="B116" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12816,32 +12816,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128912380</v>
+        <v>128912422</v>
       </c>
       <c r="B117" t="n">
-        <v>91035</v>
+        <v>86739</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5741</v>
+        <v>249278</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12851,10 +12851,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>705428</v>
+        <v>705469</v>
       </c>
       <c r="R117" t="n">
-        <v>6396581</v>
+        <v>6396714</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12913,32 +12913,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128912422</v>
+        <v>128912388</v>
       </c>
       <c r="B118" t="n">
-        <v>86735</v>
+        <v>90328</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12948,10 +12948,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>705469</v>
+        <v>705434</v>
       </c>
       <c r="R118" t="n">
-        <v>6396714</v>
+        <v>6396836</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12984,6 +12984,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13010,32 +13015,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128912388</v>
+        <v>128912380</v>
       </c>
       <c r="B119" t="n">
-        <v>90324</v>
+        <v>91039</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13045,10 +13050,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>705434</v>
+        <v>705428</v>
       </c>
       <c r="R119" t="n">
-        <v>6396836</v>
+        <v>6396581</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13081,11 +13086,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>4 st</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13115,7 +13115,7 @@
         <v>128912402</v>
       </c>
       <c r="B120" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13209,10 +13209,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128912384</v>
+        <v>128912379</v>
       </c>
       <c r="B121" t="n">
-        <v>90313</v>
+        <v>91039</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13220,37 +13220,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6268</v>
+        <v>5741</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>705294</v>
+        <v>705404</v>
       </c>
       <c r="R121" t="n">
-        <v>6396977</v>
+        <v>6396616</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13285,18 +13282,12 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Utbrett mycel med minst 10 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13315,10 +13306,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912379</v>
+        <v>128912384</v>
       </c>
       <c r="B122" t="n">
-        <v>91035</v>
+        <v>90317</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13326,34 +13317,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5741</v>
+        <v>6268</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705404</v>
+        <v>705294</v>
       </c>
       <c r="R122" t="n">
-        <v>6396616</v>
+        <v>6396977</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13388,12 +13382,18 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>128912421</v>
       </c>
       <c r="B123" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>128912411</v>
       </c>
       <c r="B124" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13606,10 +13606,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128912416</v>
+        <v>128912425</v>
       </c>
       <c r="B125" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>705273</v>
+        <v>705415</v>
       </c>
       <c r="R125" t="n">
-        <v>6396936</v>
+        <v>6396600</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13703,10 +13703,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128912425</v>
+        <v>128912416</v>
       </c>
       <c r="B126" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13738,10 +13738,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>705415</v>
+        <v>705273</v>
       </c>
       <c r="R126" t="n">
-        <v>6396600</v>
+        <v>6396936</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13803,7 +13803,7 @@
         <v>128912394</v>
       </c>
       <c r="B127" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>128912398</v>
       </c>
       <c r="B128" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>128912410</v>
       </c>
       <c r="B129" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14092,10 +14092,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912423</v>
+        <v>128912406</v>
       </c>
       <c r="B130" t="n">
-        <v>86735</v>
+        <v>86886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14103,21 +14103,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705462</v>
+        <v>705470</v>
       </c>
       <c r="R130" t="n">
-        <v>6396694</v>
+        <v>6396774</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14189,10 +14189,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128912406</v>
+        <v>128912423</v>
       </c>
       <c r="B131" t="n">
-        <v>86882</v>
+        <v>86739</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14200,21 +14200,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14224,10 +14224,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>705470</v>
+        <v>705462</v>
       </c>
       <c r="R131" t="n">
-        <v>6396774</v>
+        <v>6396694</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14289,7 +14289,7 @@
         <v>128912390</v>
       </c>
       <c r="B132" t="n">
-        <v>90324</v>
+        <v>90328</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>128912407</v>
       </c>
       <c r="B133" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>128912412</v>
       </c>
       <c r="B134" t="n">
-        <v>90987</v>
+        <v>90991</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>128912382</v>
       </c>
       <c r="B135" t="n">
-        <v>92833</v>
+        <v>92840</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>128912395</v>
       </c>
       <c r="B136" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>128912396</v>
       </c>
       <c r="B137" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>128912401</v>
       </c>
       <c r="B138" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>128912418</v>
       </c>
       <c r="B139" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>128912409</v>
       </c>
       <c r="B140" t="n">
-        <v>86957</v>
+        <v>86961</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>128912415</v>
       </c>
       <c r="B141" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15254,32 +15254,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128912399</v>
+        <v>128912403</v>
       </c>
       <c r="B142" t="n">
-        <v>86981</v>
+        <v>86784</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15289,10 +15289,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>705482</v>
+        <v>705401</v>
       </c>
       <c r="R142" t="n">
-        <v>6396750</v>
+        <v>6396966</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15333,7 +15333,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15352,32 +15351,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128912403</v>
+        <v>128912399</v>
       </c>
       <c r="B143" t="n">
-        <v>86780</v>
+        <v>86985</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15387,10 +15386,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>705401</v>
+        <v>705482</v>
       </c>
       <c r="R143" t="n">
-        <v>6396966</v>
+        <v>6396750</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15431,6 +15430,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15452,7 +15452,7 @@
         <v>129214805</v>
       </c>
       <c r="B144" t="n">
-        <v>90313</v>
+        <v>90317</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -7501,32 +7501,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884875</v>
+        <v>128884879</v>
       </c>
       <c r="B64" t="n">
-        <v>90328</v>
+        <v>86985</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2072</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705428</v>
+        <v>705537</v>
       </c>
       <c r="R64" t="n">
-        <v>6396833</v>
+        <v>6396616</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7580,6 +7580,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7598,45 +7599,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884294</v>
+        <v>128884875</v>
       </c>
       <c r="B65" t="n">
-        <v>86739</v>
+        <v>90328</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705415</v>
+        <v>705428</v>
       </c>
       <c r="R65" t="n">
-        <v>6396763</v>
+        <v>6396833</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7666,47 +7667,36 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884912</v>
+        <v>128884294</v>
       </c>
       <c r="B66" t="n">
         <v>86739</v>
@@ -7737,14 +7727,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705461</v>
+        <v>705415</v>
       </c>
       <c r="R66" t="n">
-        <v>6396579</v>
+        <v>6396763</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7774,9 +7764,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7792,22 +7792,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884879</v>
+        <v>128884912</v>
       </c>
       <c r="B67" t="n">
-        <v>86985</v>
+        <v>86739</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705537</v>
+        <v>705461</v>
       </c>
       <c r="R67" t="n">
-        <v>6396616</v>
+        <v>6396579</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9799,45 +9799,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128884878</v>
+        <v>128884300</v>
       </c>
       <c r="B87" t="n">
-        <v>86985</v>
+        <v>86832</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>705291</v>
+        <v>705540</v>
       </c>
       <c r="R87" t="n">
-        <v>6396809</v>
+        <v>6396625</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9867,37 +9867,46 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128884300</v>
+        <v>128884870</v>
       </c>
       <c r="B88" t="n">
         <v>86832</v>
@@ -9928,14 +9937,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>705540</v>
+        <v>705479</v>
       </c>
       <c r="R88" t="n">
-        <v>6396625</v>
+        <v>6396566</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9965,19 +9974,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9992,44 +9991,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128884870</v>
+        <v>128884878</v>
       </c>
       <c r="B89" t="n">
-        <v>86832</v>
+        <v>86985</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10039,10 +10038,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>705479</v>
+        <v>705291</v>
       </c>
       <c r="R89" t="n">
-        <v>6396566</v>
+        <v>6396809</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10083,6 +10082,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10101,45 +10101,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884907</v>
+        <v>128884304</v>
       </c>
       <c r="B90" t="n">
-        <v>90271</v>
+        <v>86972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>970</v>
+        <v>3599</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705399</v>
+        <v>705475</v>
       </c>
       <c r="R90" t="n">
-        <v>6396889</v>
+        <v>6396577</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10169,40 +10169,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884864</v>
+        <v>128884896</v>
       </c>
       <c r="B91" t="n">
-        <v>91039</v>
+        <v>92862</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10210,34 +10219,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705252</v>
+        <v>705227</v>
       </c>
       <c r="R91" t="n">
-        <v>6396894</v>
+        <v>6396932</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10297,48 +10309,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884896</v>
+        <v>128884907</v>
       </c>
       <c r="B92" t="n">
-        <v>92862</v>
+        <v>90271</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5964</v>
+        <v>970</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705227</v>
+        <v>705399</v>
       </c>
       <c r="R92" t="n">
-        <v>6396932</v>
+        <v>6396889</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10398,45 +10407,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884304</v>
+        <v>128884864</v>
       </c>
       <c r="B93" t="n">
-        <v>86972</v>
+        <v>91039</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705475</v>
+        <v>705252</v>
       </c>
       <c r="R93" t="n">
-        <v>6396577</v>
+        <v>6396894</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10466,39 +10475,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -12816,32 +12816,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128912422</v>
+        <v>128912380</v>
       </c>
       <c r="B117" t="n">
-        <v>86739</v>
+        <v>91039</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>249278</v>
+        <v>5741</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12851,10 +12851,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>705469</v>
+        <v>705428</v>
       </c>
       <c r="R117" t="n">
-        <v>6396714</v>
+        <v>6396581</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13015,32 +13015,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128912380</v>
+        <v>128912422</v>
       </c>
       <c r="B119" t="n">
-        <v>91039</v>
+        <v>86739</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5741</v>
+        <v>249278</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13050,10 +13050,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>705428</v>
+        <v>705469</v>
       </c>
       <c r="R119" t="n">
-        <v>6396581</v>
+        <v>6396714</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13995,32 +13995,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912410</v>
+        <v>128912406</v>
       </c>
       <c r="B129" t="n">
-        <v>87007</v>
+        <v>86886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>449</v>
+        <v>3611</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705430</v>
+        <v>705470</v>
       </c>
       <c r="R129" t="n">
-        <v>6396796</v>
+        <v>6396774</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,32 +14092,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912406</v>
+        <v>128912410</v>
       </c>
       <c r="B130" t="n">
-        <v>86886</v>
+        <v>87007</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3611</v>
+        <v>449</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705470</v>
+        <v>705430</v>
       </c>
       <c r="R130" t="n">
-        <v>6396774</v>
+        <v>6396796</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6291,45 +6291,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884883</v>
+        <v>128884885</v>
       </c>
       <c r="B52" t="n">
-        <v>86784</v>
+        <v>86893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1985</v>
+        <v>3611</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705450</v>
+        <v>705360</v>
       </c>
       <c r="R52" t="n">
-        <v>6396748</v>
+        <v>6396790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6389,10 +6392,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884302</v>
+        <v>128884883</v>
       </c>
       <c r="B53" t="n">
-        <v>86784</v>
+        <v>86791</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6420,14 +6423,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705513</v>
+        <v>705450</v>
       </c>
       <c r="R53" t="n">
-        <v>6396594</v>
+        <v>6396748</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6457,87 +6460,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884885</v>
+        <v>128884302</v>
       </c>
       <c r="B54" t="n">
-        <v>86886</v>
+        <v>86791</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3611</v>
+        <v>1985</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>705360</v>
+        <v>705513</v>
       </c>
       <c r="R54" t="n">
-        <v>6396790</v>
+        <v>6396594</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,30 +6558,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6600,7 +6600,7 @@
         <v>128889600</v>
       </c>
       <c r="B55" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,32 +6704,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884863</v>
+        <v>128884894</v>
       </c>
       <c r="B56" t="n">
-        <v>92233</v>
+        <v>90998</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705446</v>
+        <v>705317</v>
       </c>
       <c r="R56" t="n">
-        <v>6396726</v>
+        <v>6396863</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,10 +6801,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884872</v>
+        <v>128884863</v>
       </c>
       <c r="B57" t="n">
-        <v>92838</v>
+        <v>92240</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6812,21 +6812,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4366</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705338</v>
+        <v>705446</v>
       </c>
       <c r="R57" t="n">
-        <v>6396936</v>
+        <v>6396726</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6898,45 +6898,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884301</v>
+        <v>128884887</v>
       </c>
       <c r="B58" t="n">
-        <v>91065</v>
+        <v>86968</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>1988</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705546</v>
+        <v>705305</v>
       </c>
       <c r="R58" t="n">
-        <v>6396613</v>
+        <v>6396830</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6966,19 +6966,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6993,22 +6983,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884884</v>
+        <v>128884872</v>
       </c>
       <c r="B59" t="n">
-        <v>91039</v>
+        <v>92845</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7016,21 +7006,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7040,10 +7030,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705475</v>
+        <v>705338</v>
       </c>
       <c r="R59" t="n">
-        <v>6396574</v>
+        <v>6396936</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7084,7 +7074,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7103,32 +7092,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884894</v>
+        <v>128884906</v>
       </c>
       <c r="B60" t="n">
-        <v>90991</v>
+        <v>92175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3286</v>
+        <v>6031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7138,10 +7127,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705317</v>
+        <v>705291</v>
       </c>
       <c r="R60" t="n">
-        <v>6396863</v>
+        <v>6396952</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7200,10 +7189,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884887</v>
+        <v>128884884</v>
       </c>
       <c r="B61" t="n">
-        <v>86961</v>
+        <v>91046</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7211,21 +7200,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1988</v>
+        <v>5741</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7235,10 +7224,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705305</v>
+        <v>705475</v>
       </c>
       <c r="R61" t="n">
-        <v>6396830</v>
+        <v>6396574</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7279,6 +7268,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7297,45 +7287,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884906</v>
+        <v>128884301</v>
       </c>
       <c r="B62" t="n">
-        <v>92168</v>
+        <v>91072</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6031</v>
+        <v>5747</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705291</v>
+        <v>705546</v>
       </c>
       <c r="R62" t="n">
-        <v>6396952</v>
+        <v>6396613</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7365,9 +7355,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7382,12 +7382,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7397,7 +7397,7 @@
         <v>128890120</v>
       </c>
       <c r="B63" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7501,32 +7501,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884879</v>
+        <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>86985</v>
+        <v>90335</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>2072</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>705537</v>
+        <v>705428</v>
       </c>
       <c r="R64" t="n">
-        <v>6396616</v>
+        <v>6396833</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7580,7 +7580,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7599,45 +7598,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884875</v>
+        <v>128884294</v>
       </c>
       <c r="B65" t="n">
-        <v>90328</v>
+        <v>86746</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>705428</v>
+        <v>705415</v>
       </c>
       <c r="R65" t="n">
-        <v>6396833</v>
+        <v>6396763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7667,39 +7666,50 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884294</v>
+        <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7727,14 +7737,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>705415</v>
+        <v>705461</v>
       </c>
       <c r="R66" t="n">
-        <v>6396763</v>
+        <v>6396579</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7764,19 +7774,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7792,22 +7792,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884912</v>
+        <v>128884879</v>
       </c>
       <c r="B67" t="n">
-        <v>86739</v>
+        <v>86992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>705461</v>
+        <v>705537</v>
       </c>
       <c r="R67" t="n">
-        <v>6396579</v>
+        <v>6396616</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7902,32 +7902,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128884861</v>
+        <v>128884914</v>
       </c>
       <c r="B68" t="n">
-        <v>87030</v>
+        <v>86746</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>705483</v>
+        <v>705401</v>
       </c>
       <c r="R68" t="n">
-        <v>6396620</v>
+        <v>6396625</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7981,6 +7981,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7999,32 +8000,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128884914</v>
+        <v>128884861</v>
       </c>
       <c r="B69" t="n">
-        <v>86739</v>
+        <v>87037</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8034,10 +8035,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>705401</v>
+        <v>705483</v>
       </c>
       <c r="R69" t="n">
-        <v>6396625</v>
+        <v>6396620</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8078,7 +8079,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>128884865</v>
       </c>
       <c r="B70" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>128884898</v>
       </c>
       <c r="B71" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>128884871</v>
       </c>
       <c r="B72" t="n">
-        <v>87051</v>
+        <v>87058</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>128884886</v>
       </c>
       <c r="B73" t="n">
-        <v>86886</v>
+        <v>86893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>128884868</v>
       </c>
       <c r="B74" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>128884869</v>
       </c>
       <c r="B75" t="n">
-        <v>86832</v>
+        <v>86839</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>128884867</v>
       </c>
       <c r="B76" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>128884890</v>
       </c>
       <c r="B77" t="n">
-        <v>105719</v>
+        <v>105726</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>128884873</v>
       </c>
       <c r="B78" t="n">
-        <v>90328</v>
+        <v>90335</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>128884296</v>
       </c>
       <c r="B79" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>128884299</v>
       </c>
       <c r="B80" t="n">
-        <v>86886</v>
+        <v>86893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9193,48 +9193,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884881</v>
+        <v>128884305</v>
       </c>
       <c r="B81" t="n">
-        <v>86972</v>
+        <v>91046</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>705474</v>
+        <v>705468</v>
       </c>
       <c r="R81" t="n">
-        <v>6396574</v>
+        <v>6396595</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9264,40 +9261,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884305</v>
+        <v>128884866</v>
       </c>
       <c r="B82" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9325,14 +9331,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>705468</v>
+        <v>705433</v>
       </c>
       <c r="R82" t="n">
-        <v>6396595</v>
+        <v>6396684</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9362,19 +9368,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9389,57 +9385,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128884866</v>
+        <v>128884881</v>
       </c>
       <c r="B83" t="n">
-        <v>91039</v>
+        <v>86979</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>705433</v>
+        <v>705474</v>
       </c>
       <c r="R83" t="n">
-        <v>6396684</v>
+        <v>6396574</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9480,6 +9479,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128889624</v>
+        <v>128884862</v>
       </c>
       <c r="B84" t="n">
-        <v>90328</v>
+        <v>87037</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2072</v>
+        <v>3767</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705513</v>
+        <v>705398</v>
       </c>
       <c r="R84" t="n">
-        <v>6396594</v>
+        <v>6396569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,19 +9566,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9593,57 +9583,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884882</v>
+        <v>128889624</v>
       </c>
       <c r="B85" t="n">
-        <v>86784</v>
+        <v>90335</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1985</v>
+        <v>2072</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705380</v>
+        <v>705513</v>
       </c>
       <c r="R85" t="n">
-        <v>6396917</v>
+        <v>6396594</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9673,9 +9663,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,22 +9690,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884862</v>
+        <v>128884882</v>
       </c>
       <c r="B86" t="n">
-        <v>87030</v>
+        <v>86791</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705398</v>
+        <v>705380</v>
       </c>
       <c r="R86" t="n">
-        <v>6396569</v>
+        <v>6396917</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9802,7 +9802,7 @@
         <v>128884300</v>
       </c>
       <c r="B87" t="n">
-        <v>86832</v>
+        <v>86839</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>128884870</v>
       </c>
       <c r="B88" t="n">
-        <v>86832</v>
+        <v>86839</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>128884878</v>
       </c>
       <c r="B89" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>128884304</v>
       </c>
       <c r="B90" t="n">
-        <v>86972</v>
+        <v>86979</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10208,48 +10208,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884896</v>
+        <v>128884907</v>
       </c>
       <c r="B91" t="n">
-        <v>92862</v>
+        <v>90278</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5964</v>
+        <v>970</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705227</v>
+        <v>705399</v>
       </c>
       <c r="R91" t="n">
-        <v>6396932</v>
+        <v>6396889</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10309,32 +10306,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884907</v>
+        <v>128884864</v>
       </c>
       <c r="B92" t="n">
-        <v>90271</v>
+        <v>91046</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>970</v>
+        <v>5741</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10344,10 +10341,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705399</v>
+        <v>705252</v>
       </c>
       <c r="R92" t="n">
-        <v>6396889</v>
+        <v>6396894</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10407,10 +10404,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884864</v>
+        <v>128884896</v>
       </c>
       <c r="B93" t="n">
-        <v>91039</v>
+        <v>92869</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10418,34 +10415,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705252</v>
+        <v>705227</v>
       </c>
       <c r="R93" t="n">
-        <v>6396894</v>
+        <v>6396932</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10505,32 +10505,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884306</v>
+        <v>128884900</v>
       </c>
       <c r="B94" t="n">
-        <v>86886</v>
+        <v>92869</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10539,14 +10539,14 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705439</v>
+        <v>705445</v>
       </c>
       <c r="R94" t="n">
-        <v>6396582</v>
+        <v>6396819</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10576,19 +10576,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10604,44 +10594,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884900</v>
+        <v>128884876</v>
       </c>
       <c r="B95" t="n">
-        <v>92862</v>
+        <v>90335</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5964</v>
+        <v>2072</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10654,10 +10644,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705445</v>
+        <v>705430</v>
       </c>
       <c r="R95" t="n">
-        <v>6396819</v>
+        <v>6396834</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10717,10 +10707,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884915</v>
+        <v>128884306</v>
       </c>
       <c r="B96" t="n">
-        <v>86739</v>
+        <v>86893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10728,34 +10718,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705291</v>
+        <v>705439</v>
       </c>
       <c r="R96" t="n">
-        <v>6396949</v>
+        <v>6396582</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10785,77 +10778,85 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884876</v>
+        <v>128884915</v>
       </c>
       <c r="B97" t="n">
-        <v>90328</v>
+        <v>86746</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705430</v>
+        <v>705291</v>
       </c>
       <c r="R97" t="n">
-        <v>6396834</v>
+        <v>6396949</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10896,7 +10897,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10915,45 +10915,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884303</v>
+        <v>128884899</v>
       </c>
       <c r="B98" t="n">
-        <v>86886</v>
+        <v>92869</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705477</v>
+        <v>705436</v>
       </c>
       <c r="R98" t="n">
-        <v>6396583</v>
+        <v>6396834</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10983,49 +10986,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884899</v>
+        <v>128884897</v>
       </c>
       <c r="B99" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11060,10 +11054,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705436</v>
+        <v>705297</v>
       </c>
       <c r="R99" t="n">
-        <v>6396834</v>
+        <v>6396949</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11123,48 +11117,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884897</v>
+        <v>128884303</v>
       </c>
       <c r="B100" t="n">
-        <v>92862</v>
+        <v>86893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705297</v>
+        <v>705477</v>
       </c>
       <c r="R100" t="n">
-        <v>6396949</v>
+        <v>6396583</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11194,30 +11185,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
         <v>128884913</v>
       </c>
       <c r="B101" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128884910</v>
       </c>
       <c r="B102" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>128884874</v>
       </c>
       <c r="B103" t="n">
-        <v>90328</v>
+        <v>90335</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11521,10 +11521,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128884908</v>
+        <v>128884911</v>
       </c>
       <c r="B104" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>705320</v>
+        <v>705527</v>
       </c>
       <c r="R104" t="n">
-        <v>6396829</v>
+        <v>6396694</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11619,10 +11619,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884911</v>
+        <v>128884908</v>
       </c>
       <c r="B105" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11654,10 +11654,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705527</v>
+        <v>705320</v>
       </c>
       <c r="R105" t="n">
-        <v>6396694</v>
+        <v>6396829</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
         <v>128884877</v>
       </c>
       <c r="B106" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>128906402</v>
       </c>
       <c r="B107" t="n">
-        <v>86986</v>
+        <v>86993</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>128884909</v>
       </c>
       <c r="B108" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>128912404</v>
       </c>
       <c r="B109" t="n">
-        <v>86784</v>
+        <v>86791</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>128912419</v>
       </c>
       <c r="B110" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>128912424</v>
       </c>
       <c r="B111" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>128912420</v>
       </c>
       <c r="B112" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>128912417</v>
       </c>
       <c r="B113" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>128912385</v>
       </c>
       <c r="B114" t="n">
-        <v>90328</v>
+        <v>90335</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>128912405</v>
       </c>
       <c r="B115" t="n">
-        <v>86886</v>
+        <v>86893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>128912408</v>
       </c>
       <c r="B116" t="n">
-        <v>86886</v>
+        <v>86893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>128912380</v>
       </c>
       <c r="B117" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>128912388</v>
       </c>
       <c r="B118" t="n">
-        <v>90328</v>
+        <v>90335</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>128912422</v>
       </c>
       <c r="B119" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>128912402</v>
       </c>
       <c r="B120" t="n">
-        <v>86784</v>
+        <v>86791</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>128912379</v>
       </c>
       <c r="B121" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>128912384</v>
       </c>
       <c r="B122" t="n">
-        <v>90317</v>
+        <v>90324</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>128912421</v>
       </c>
       <c r="B123" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>128912411</v>
       </c>
       <c r="B124" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>128912425</v>
       </c>
       <c r="B125" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>128912416</v>
       </c>
       <c r="B126" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>128912394</v>
       </c>
       <c r="B127" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>128912398</v>
       </c>
       <c r="B128" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13995,32 +13995,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912406</v>
+        <v>128912410</v>
       </c>
       <c r="B129" t="n">
-        <v>86886</v>
+        <v>87014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3611</v>
+        <v>449</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705470</v>
+        <v>705430</v>
       </c>
       <c r="R129" t="n">
-        <v>6396774</v>
+        <v>6396796</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,32 +14092,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912410</v>
+        <v>128912406</v>
       </c>
       <c r="B130" t="n">
-        <v>87007</v>
+        <v>86893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>449</v>
+        <v>3611</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705430</v>
+        <v>705470</v>
       </c>
       <c r="R130" t="n">
-        <v>6396796</v>
+        <v>6396774</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14192,7 +14192,7 @@
         <v>128912423</v>
       </c>
       <c r="B131" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>128912390</v>
       </c>
       <c r="B132" t="n">
-        <v>90328</v>
+        <v>90335</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>128912407</v>
       </c>
       <c r="B133" t="n">
-        <v>86886</v>
+        <v>86893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>128912412</v>
       </c>
       <c r="B134" t="n">
-        <v>90991</v>
+        <v>90998</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>128912382</v>
       </c>
       <c r="B135" t="n">
-        <v>92840</v>
+        <v>92847</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>128912395</v>
       </c>
       <c r="B136" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>128912396</v>
       </c>
       <c r="B137" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14866,32 +14866,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128912401</v>
+        <v>128912418</v>
       </c>
       <c r="B138" t="n">
-        <v>86784</v>
+        <v>86746</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>705317</v>
+        <v>705286</v>
       </c>
       <c r="R138" t="n">
-        <v>6396871</v>
+        <v>6396970</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14963,32 +14963,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128912418</v>
+        <v>128912401</v>
       </c>
       <c r="B139" t="n">
-        <v>86739</v>
+        <v>86791</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14998,10 +14998,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>705286</v>
+        <v>705317</v>
       </c>
       <c r="R139" t="n">
-        <v>6396970</v>
+        <v>6396871</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15063,7 +15063,7 @@
         <v>128912409</v>
       </c>
       <c r="B140" t="n">
-        <v>86961</v>
+        <v>86968</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>128912415</v>
       </c>
       <c r="B141" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>128912403</v>
       </c>
       <c r="B142" t="n">
-        <v>86784</v>
+        <v>86791</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>128912399</v>
       </c>
       <c r="B143" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>129214805</v>
       </c>
       <c r="B144" t="n">
-        <v>90317</v>
+        <v>90324</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6294,7 +6294,7 @@
         <v>128884885</v>
       </c>
       <c r="B52" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>128884883</v>
       </c>
       <c r="B53" t="n">
-        <v>86791</v>
+        <v>86793</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>128884302</v>
       </c>
       <c r="B54" t="n">
-        <v>86791</v>
+        <v>86793</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>128889600</v>
       </c>
       <c r="B55" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,32 +6704,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884894</v>
+        <v>128884887</v>
       </c>
       <c r="B56" t="n">
-        <v>90998</v>
+        <v>86970</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>1988</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705317</v>
+        <v>705305</v>
       </c>
       <c r="R56" t="n">
-        <v>6396863</v>
+        <v>6396830</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6804,7 +6804,7 @@
         <v>128884863</v>
       </c>
       <c r="B57" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6898,45 +6898,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884887</v>
+        <v>128884301</v>
       </c>
       <c r="B58" t="n">
-        <v>86968</v>
+        <v>91074</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1988</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705305</v>
+        <v>705546</v>
       </c>
       <c r="R58" t="n">
-        <v>6396830</v>
+        <v>6396613</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6966,9 +6966,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6983,22 +6993,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884872</v>
+        <v>128884884</v>
       </c>
       <c r="B59" t="n">
-        <v>92845</v>
+        <v>91048</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7006,21 +7016,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7030,10 +7040,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705338</v>
+        <v>705475</v>
       </c>
       <c r="R59" t="n">
-        <v>6396936</v>
+        <v>6396574</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7074,6 +7084,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7092,10 +7103,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884906</v>
+        <v>128884872</v>
       </c>
       <c r="B60" t="n">
-        <v>92175</v>
+        <v>92847</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,21 +7114,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6031</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7127,10 +7138,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705291</v>
+        <v>705338</v>
       </c>
       <c r="R60" t="n">
-        <v>6396952</v>
+        <v>6396936</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7189,32 +7200,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884884</v>
+        <v>128884894</v>
       </c>
       <c r="B61" t="n">
-        <v>91046</v>
+        <v>91000</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5741</v>
+        <v>3286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7224,10 +7235,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>705475</v>
+        <v>705317</v>
       </c>
       <c r="R61" t="n">
-        <v>6396574</v>
+        <v>6396863</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7268,7 +7279,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7287,45 +7297,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884301</v>
+        <v>128884906</v>
       </c>
       <c r="B62" t="n">
-        <v>91072</v>
+        <v>92177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5747</v>
+        <v>6031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705546</v>
+        <v>705291</v>
       </c>
       <c r="R62" t="n">
-        <v>6396613</v>
+        <v>6396952</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7355,19 +7365,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7382,12 +7382,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7397,7 +7397,7 @@
         <v>128890120</v>
       </c>
       <c r="B63" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>90335</v>
+        <v>90337</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>128884294</v>
       </c>
       <c r="B65" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>128884879</v>
       </c>
       <c r="B67" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>128884914</v>
       </c>
       <c r="B68" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>128884861</v>
       </c>
       <c r="B69" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884865</v>
+        <v>128884898</v>
       </c>
       <c r="B70" t="n">
-        <v>91046</v>
+        <v>92871</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,34 +8108,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705416</v>
+        <v>705425</v>
       </c>
       <c r="R70" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8195,10 +8198,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884898</v>
+        <v>128884871</v>
       </c>
       <c r="B71" t="n">
-        <v>92869</v>
+        <v>87060</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8206,34 +8209,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>3624</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705425</v>
+        <v>705290</v>
       </c>
       <c r="R71" t="n">
         <v>6396809</v>
@@ -8277,7 +8273,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8296,41 +8291,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884871</v>
+        <v>128884886</v>
       </c>
       <c r="B72" t="n">
-        <v>87058</v>
+        <v>86895</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3624</v>
+        <v>3611</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705290</v>
+        <v>705473</v>
       </c>
       <c r="R72" t="n">
-        <v>6396809</v>
+        <v>6396572</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8371,6 +8373,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8389,48 +8392,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884886</v>
+        <v>128884865</v>
       </c>
       <c r="B73" t="n">
-        <v>86893</v>
+        <v>91048</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3611</v>
+        <v>5741</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705473</v>
+        <v>705416</v>
       </c>
       <c r="R73" t="n">
-        <v>6396572</v>
+        <v>6396601</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8493,7 +8493,7 @@
         <v>128884868</v>
       </c>
       <c r="B74" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>128884869</v>
       </c>
       <c r="B75" t="n">
-        <v>86839</v>
+        <v>86841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>128884867</v>
       </c>
       <c r="B76" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>128884890</v>
       </c>
       <c r="B77" t="n">
-        <v>105726</v>
+        <v>105728</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>128884873</v>
       </c>
       <c r="B78" t="n">
-        <v>90335</v>
+        <v>90337</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>128884296</v>
       </c>
       <c r="B79" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>128884299</v>
       </c>
       <c r="B80" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9193,45 +9193,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884305</v>
+        <v>128884881</v>
       </c>
       <c r="B81" t="n">
-        <v>91046</v>
+        <v>86981</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>705468</v>
+        <v>705474</v>
       </c>
       <c r="R81" t="n">
-        <v>6396595</v>
+        <v>6396574</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9261,49 +9264,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884866</v>
+        <v>128884305</v>
       </c>
       <c r="B82" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9331,14 +9325,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>705433</v>
+        <v>705468</v>
       </c>
       <c r="R82" t="n">
-        <v>6396684</v>
+        <v>6396595</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9368,9 +9362,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9385,60 +9389,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128884881</v>
+        <v>128884866</v>
       </c>
       <c r="B83" t="n">
-        <v>86979</v>
+        <v>91048</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>705474</v>
+        <v>705433</v>
       </c>
       <c r="R83" t="n">
-        <v>6396574</v>
+        <v>6396684</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9479,7 +9480,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884862</v>
+        <v>128889624</v>
       </c>
       <c r="B84" t="n">
-        <v>87037</v>
+        <v>90337</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3767</v>
+        <v>2072</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705398</v>
+        <v>705513</v>
       </c>
       <c r="R84" t="n">
-        <v>6396569</v>
+        <v>6396594</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,9 +9566,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9583,57 +9593,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128889624</v>
+        <v>128884882</v>
       </c>
       <c r="B85" t="n">
-        <v>90335</v>
+        <v>86793</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2072</v>
+        <v>1985</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705513</v>
+        <v>705380</v>
       </c>
       <c r="R85" t="n">
-        <v>6396594</v>
+        <v>6396917</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,19 +9673,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,22 +9690,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884882</v>
+        <v>128884862</v>
       </c>
       <c r="B86" t="n">
-        <v>86791</v>
+        <v>87039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705380</v>
+        <v>705398</v>
       </c>
       <c r="R86" t="n">
-        <v>6396917</v>
+        <v>6396569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9802,7 +9802,7 @@
         <v>128884300</v>
       </c>
       <c r="B87" t="n">
-        <v>86839</v>
+        <v>86841</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>128884870</v>
       </c>
       <c r="B88" t="n">
-        <v>86839</v>
+        <v>86841</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>128884878</v>
       </c>
       <c r="B89" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10101,45 +10101,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884304</v>
+        <v>128884896</v>
       </c>
       <c r="B90" t="n">
-        <v>86979</v>
+        <v>92871</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3599</v>
+        <v>5964</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705475</v>
+        <v>705227</v>
       </c>
       <c r="R90" t="n">
-        <v>6396577</v>
+        <v>6396932</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10169,71 +10172,62 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884907</v>
+        <v>128884864</v>
       </c>
       <c r="B91" t="n">
-        <v>90278</v>
+        <v>91048</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>970</v>
+        <v>5741</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10243,10 +10237,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705399</v>
+        <v>705252</v>
       </c>
       <c r="R91" t="n">
-        <v>6396889</v>
+        <v>6396894</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10306,45 +10300,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884864</v>
+        <v>128884304</v>
       </c>
       <c r="B92" t="n">
-        <v>91046</v>
+        <v>86981</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705252</v>
+        <v>705475</v>
       </c>
       <c r="R92" t="n">
-        <v>6396894</v>
+        <v>6396577</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10374,78 +10368,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884896</v>
+        <v>128884907</v>
       </c>
       <c r="B93" t="n">
-        <v>92869</v>
+        <v>90280</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5964</v>
+        <v>970</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705227</v>
+        <v>705399</v>
       </c>
       <c r="R93" t="n">
-        <v>6396932</v>
+        <v>6396889</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10508,7 +10508,7 @@
         <v>128884900</v>
       </c>
       <c r="B94" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>128884876</v>
       </c>
       <c r="B95" t="n">
-        <v>90335</v>
+        <v>90337</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>128884306</v>
       </c>
       <c r="B96" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>128884915</v>
       </c>
       <c r="B97" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10915,10 +10915,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884899</v>
+        <v>128884897</v>
       </c>
       <c r="B98" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10953,10 +10953,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705436</v>
+        <v>705297</v>
       </c>
       <c r="R98" t="n">
-        <v>6396834</v>
+        <v>6396949</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11016,10 +11016,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884897</v>
+        <v>128884899</v>
       </c>
       <c r="B99" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705297</v>
+        <v>705436</v>
       </c>
       <c r="R99" t="n">
-        <v>6396949</v>
+        <v>6396834</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11120,7 +11120,7 @@
         <v>128884303</v>
       </c>
       <c r="B100" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>128884913</v>
       </c>
       <c r="B101" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>128884910</v>
       </c>
       <c r="B102" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11420,48 +11420,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128884874</v>
+        <v>128884908</v>
       </c>
       <c r="B103" t="n">
-        <v>90335</v>
+        <v>86748</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>705425</v>
+        <v>705320</v>
       </c>
       <c r="R103" t="n">
-        <v>6396850</v>
+        <v>6396829</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11524,7 +11521,7 @@
         <v>128884911</v>
       </c>
       <c r="B104" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11619,45 +11616,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128884908</v>
+        <v>128884874</v>
       </c>
       <c r="B105" t="n">
-        <v>86746</v>
+        <v>90337</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>705320</v>
+        <v>705425</v>
       </c>
       <c r="R105" t="n">
-        <v>6396829</v>
+        <v>6396850</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
         <v>128884877</v>
       </c>
       <c r="B106" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>128906402</v>
       </c>
       <c r="B107" t="n">
-        <v>86993</v>
+        <v>86995</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>128884909</v>
       </c>
       <c r="B108" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912404</v>
+        <v>128912419</v>
       </c>
       <c r="B109" t="n">
-        <v>86791</v>
+        <v>86748</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705405</v>
+        <v>705420</v>
       </c>
       <c r="R109" t="n">
-        <v>6396928</v>
+        <v>6396917</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,10 +12132,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912419</v>
+        <v>128912424</v>
       </c>
       <c r="B110" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705420</v>
+        <v>705432</v>
       </c>
       <c r="R110" t="n">
-        <v>6396917</v>
+        <v>6396615</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,10 +12229,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912424</v>
+        <v>128912420</v>
       </c>
       <c r="B111" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705432</v>
+        <v>705443</v>
       </c>
       <c r="R111" t="n">
-        <v>6396615</v>
+        <v>6396921</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912420</v>
+        <v>128912417</v>
       </c>
       <c r="B112" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705443</v>
+        <v>705276</v>
       </c>
       <c r="R112" t="n">
-        <v>6396921</v>
+        <v>6396964</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,32 +12423,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912417</v>
+        <v>128912404</v>
       </c>
       <c r="B113" t="n">
-        <v>86746</v>
+        <v>86793</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705276</v>
+        <v>705405</v>
       </c>
       <c r="R113" t="n">
-        <v>6396964</v>
+        <v>6396928</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
         <v>128912385</v>
       </c>
       <c r="B114" t="n">
-        <v>90335</v>
+        <v>90337</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>128912405</v>
       </c>
       <c r="B115" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>128912408</v>
       </c>
       <c r="B116" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>128912380</v>
       </c>
       <c r="B117" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12913,32 +12913,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128912388</v>
+        <v>128912422</v>
       </c>
       <c r="B118" t="n">
-        <v>90335</v>
+        <v>86748</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12948,10 +12948,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>705434</v>
+        <v>705469</v>
       </c>
       <c r="R118" t="n">
-        <v>6396836</v>
+        <v>6396714</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12984,11 +12984,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>4 st</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13015,32 +13010,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128912422</v>
+        <v>128912388</v>
       </c>
       <c r="B119" t="n">
-        <v>86746</v>
+        <v>90337</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>249278</v>
+        <v>2072</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13050,10 +13045,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>705469</v>
+        <v>705434</v>
       </c>
       <c r="R119" t="n">
-        <v>6396714</v>
+        <v>6396836</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13086,6 +13081,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13115,7 +13115,7 @@
         <v>128912402</v>
       </c>
       <c r="B120" t="n">
-        <v>86791</v>
+        <v>86793</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>128912379</v>
       </c>
       <c r="B121" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>128912384</v>
       </c>
       <c r="B122" t="n">
-        <v>90324</v>
+        <v>90326</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>128912421</v>
       </c>
       <c r="B123" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>128912411</v>
       </c>
       <c r="B124" t="n">
-        <v>87014</v>
+        <v>87016</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>128912425</v>
       </c>
       <c r="B125" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>128912416</v>
       </c>
       <c r="B126" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>128912394</v>
       </c>
       <c r="B127" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>128912398</v>
       </c>
       <c r="B128" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>128912410</v>
       </c>
       <c r="B129" t="n">
-        <v>87014</v>
+        <v>87016</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14092,10 +14092,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912406</v>
+        <v>128912423</v>
       </c>
       <c r="B130" t="n">
-        <v>86893</v>
+        <v>86748</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14103,21 +14103,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705470</v>
+        <v>705462</v>
       </c>
       <c r="R130" t="n">
-        <v>6396774</v>
+        <v>6396694</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14189,10 +14189,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128912423</v>
+        <v>128912406</v>
       </c>
       <c r="B131" t="n">
-        <v>86746</v>
+        <v>86895</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14200,21 +14200,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14224,10 +14224,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>705462</v>
+        <v>705470</v>
       </c>
       <c r="R131" t="n">
-        <v>6396694</v>
+        <v>6396774</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14289,7 +14289,7 @@
         <v>128912390</v>
       </c>
       <c r="B132" t="n">
-        <v>90335</v>
+        <v>90337</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>128912407</v>
       </c>
       <c r="B133" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>128912412</v>
       </c>
       <c r="B134" t="n">
-        <v>90998</v>
+        <v>91000</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>128912382</v>
       </c>
       <c r="B135" t="n">
-        <v>92847</v>
+        <v>92849</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>128912395</v>
       </c>
       <c r="B136" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>128912396</v>
       </c>
       <c r="B137" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14866,32 +14866,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128912418</v>
+        <v>128912401</v>
       </c>
       <c r="B138" t="n">
-        <v>86746</v>
+        <v>86793</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>705286</v>
+        <v>705317</v>
       </c>
       <c r="R138" t="n">
-        <v>6396970</v>
+        <v>6396871</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14963,32 +14963,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128912401</v>
+        <v>128912418</v>
       </c>
       <c r="B139" t="n">
-        <v>86791</v>
+        <v>86748</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14998,10 +14998,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>705317</v>
+        <v>705286</v>
       </c>
       <c r="R139" t="n">
-        <v>6396871</v>
+        <v>6396970</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15063,7 +15063,7 @@
         <v>128912409</v>
       </c>
       <c r="B140" t="n">
-        <v>86968</v>
+        <v>86970</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>128912415</v>
       </c>
       <c r="B141" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>128912403</v>
       </c>
       <c r="B142" t="n">
-        <v>86791</v>
+        <v>86793</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>128912399</v>
       </c>
       <c r="B143" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>129214805</v>
       </c>
       <c r="B144" t="n">
-        <v>90324</v>
+        <v>90326</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6704,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884887</v>
+        <v>128884872</v>
       </c>
       <c r="B56" t="n">
-        <v>86970</v>
+        <v>92847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6715,21 +6715,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1988</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705305</v>
+        <v>705338</v>
       </c>
       <c r="R56" t="n">
-        <v>6396830</v>
+        <v>6396936</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,10 +6801,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884863</v>
+        <v>128884906</v>
       </c>
       <c r="B57" t="n">
-        <v>92242</v>
+        <v>92177</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6812,21 +6812,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6031</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705446</v>
+        <v>705291</v>
       </c>
       <c r="R57" t="n">
-        <v>6396726</v>
+        <v>6396952</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6898,45 +6898,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884301</v>
+        <v>128884884</v>
       </c>
       <c r="B58" t="n">
-        <v>91074</v>
+        <v>91048</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>5741</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705546</v>
+        <v>705475</v>
       </c>
       <c r="R58" t="n">
-        <v>6396613</v>
+        <v>6396574</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6966,84 +6966,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884884</v>
+        <v>128884301</v>
       </c>
       <c r="B59" t="n">
-        <v>91048</v>
+        <v>91074</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5741</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705475</v>
+        <v>705546</v>
       </c>
       <c r="R59" t="n">
-        <v>6396574</v>
+        <v>6396613</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7073,40 +7064,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884872</v>
+        <v>128884887</v>
       </c>
       <c r="B60" t="n">
-        <v>92847</v>
+        <v>86970</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7114,21 +7114,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>1988</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705338</v>
+        <v>705305</v>
       </c>
       <c r="R60" t="n">
-        <v>6396936</v>
+        <v>6396830</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7297,10 +7297,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884906</v>
+        <v>128884863</v>
       </c>
       <c r="B62" t="n">
-        <v>92177</v>
+        <v>92242</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6031</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>705291</v>
+        <v>705446</v>
       </c>
       <c r="R62" t="n">
-        <v>6396952</v>
+        <v>6396726</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7902,32 +7902,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128884914</v>
+        <v>128884861</v>
       </c>
       <c r="B68" t="n">
-        <v>86748</v>
+        <v>87039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>705401</v>
+        <v>705483</v>
       </c>
       <c r="R68" t="n">
-        <v>6396625</v>
+        <v>6396620</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7981,7 +7981,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8000,32 +7999,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128884861</v>
+        <v>128884914</v>
       </c>
       <c r="B69" t="n">
-        <v>87039</v>
+        <v>86748</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8035,10 +8034,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>705483</v>
+        <v>705401</v>
       </c>
       <c r="R69" t="n">
-        <v>6396620</v>
+        <v>6396625</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8079,6 +8078,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884869</v>
+        <v>128884867</v>
       </c>
       <c r="B75" t="n">
-        <v>86841</v>
+        <v>91048</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>5741</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>705297</v>
+        <v>705431</v>
       </c>
       <c r="R75" t="n">
-        <v>6396817</v>
+        <v>6396688</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8684,32 +8684,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884867</v>
+        <v>128884869</v>
       </c>
       <c r="B76" t="n">
-        <v>91048</v>
+        <v>86841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5741</v>
+        <v>424</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>705431</v>
+        <v>705297</v>
       </c>
       <c r="R76" t="n">
-        <v>6396688</v>
+        <v>6396817</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8878,48 +8878,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884873</v>
+        <v>128884296</v>
       </c>
       <c r="B78" t="n">
-        <v>90337</v>
+        <v>91048</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>705314</v>
+        <v>705419</v>
       </c>
       <c r="R78" t="n">
-        <v>6396809</v>
+        <v>6396769</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8949,75 +8946,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884296</v>
+        <v>128884873</v>
       </c>
       <c r="B79" t="n">
-        <v>91048</v>
+        <v>90337</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>705419</v>
+        <v>705314</v>
       </c>
       <c r="R79" t="n">
-        <v>6396769</v>
+        <v>6396809</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9047,39 +9056,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128889624</v>
+        <v>128884882</v>
       </c>
       <c r="B84" t="n">
-        <v>90337</v>
+        <v>86793</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2072</v>
+        <v>1985</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705513</v>
+        <v>705380</v>
       </c>
       <c r="R84" t="n">
-        <v>6396594</v>
+        <v>6396917</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,19 +9566,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9593,57 +9583,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884882</v>
+        <v>128889624</v>
       </c>
       <c r="B85" t="n">
-        <v>86793</v>
+        <v>90337</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1985</v>
+        <v>2072</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705380</v>
+        <v>705513</v>
       </c>
       <c r="R85" t="n">
-        <v>6396917</v>
+        <v>6396594</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9673,9 +9663,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,12 +9690,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10101,48 +10101,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884896</v>
+        <v>128884907</v>
       </c>
       <c r="B90" t="n">
-        <v>92871</v>
+        <v>90280</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5964</v>
+        <v>970</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>705227</v>
+        <v>705399</v>
       </c>
       <c r="R90" t="n">
-        <v>6396932</v>
+        <v>6396889</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10202,45 +10199,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128884864</v>
+        <v>128884304</v>
       </c>
       <c r="B91" t="n">
-        <v>91048</v>
+        <v>86981</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5741</v>
+        <v>3599</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>705252</v>
+        <v>705475</v>
       </c>
       <c r="R91" t="n">
-        <v>6396894</v>
+        <v>6396577</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10270,75 +10267,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128884304</v>
+        <v>128884864</v>
       </c>
       <c r="B92" t="n">
-        <v>86981</v>
+        <v>91048</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3599</v>
+        <v>5741</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>705475</v>
+        <v>705252</v>
       </c>
       <c r="R92" t="n">
-        <v>6396577</v>
+        <v>6396894</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10368,84 +10374,78 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128884907</v>
+        <v>128884896</v>
       </c>
       <c r="B93" t="n">
-        <v>90280</v>
+        <v>92871</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>970</v>
+        <v>5964</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>705399</v>
+        <v>705227</v>
       </c>
       <c r="R93" t="n">
-        <v>6396889</v>
+        <v>6396932</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10505,32 +10505,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884900</v>
+        <v>128884876</v>
       </c>
       <c r="B94" t="n">
-        <v>92871</v>
+        <v>90337</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5964</v>
+        <v>2072</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705445</v>
+        <v>705430</v>
       </c>
       <c r="R94" t="n">
-        <v>6396819</v>
+        <v>6396834</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10606,32 +10606,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884876</v>
+        <v>128884306</v>
       </c>
       <c r="B95" t="n">
-        <v>90337</v>
+        <v>86895</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2072</v>
+        <v>3611</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10640,14 +10640,14 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705430</v>
+        <v>705439</v>
       </c>
       <c r="R95" t="n">
-        <v>6396834</v>
+        <v>6396582</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10677,9 +10677,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10695,22 +10705,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884306</v>
+        <v>128884915</v>
       </c>
       <c r="B96" t="n">
-        <v>86895</v>
+        <v>86748</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10718,37 +10728,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705439</v>
+        <v>705291</v>
       </c>
       <c r="R96" t="n">
-        <v>6396582</v>
+        <v>6396949</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10778,85 +10785,77 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884915</v>
+        <v>128884900</v>
       </c>
       <c r="B97" t="n">
-        <v>86748</v>
+        <v>92871</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705291</v>
+        <v>705445</v>
       </c>
       <c r="R97" t="n">
-        <v>6396949</v>
+        <v>6396819</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10897,6 +10896,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10915,48 +10915,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884897</v>
+        <v>128884303</v>
       </c>
       <c r="B98" t="n">
-        <v>92871</v>
+        <v>86895</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705297</v>
+        <v>705477</v>
       </c>
       <c r="R98" t="n">
-        <v>6396949</v>
+        <v>6396583</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10986,30 +10983,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11117,45 +11123,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884303</v>
+        <v>128884897</v>
       </c>
       <c r="B100" t="n">
-        <v>86895</v>
+        <v>92871</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705477</v>
+        <v>705297</v>
       </c>
       <c r="R100" t="n">
-        <v>6396583</v>
+        <v>6396949</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11185,39 +11194,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912419</v>
+        <v>128912404</v>
       </c>
       <c r="B109" t="n">
-        <v>86748</v>
+        <v>86793</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705420</v>
+        <v>705405</v>
       </c>
       <c r="R109" t="n">
-        <v>6396917</v>
+        <v>6396928</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912424</v>
+        <v>128912419</v>
       </c>
       <c r="B110" t="n">
         <v>86748</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705432</v>
+        <v>705420</v>
       </c>
       <c r="R110" t="n">
-        <v>6396615</v>
+        <v>6396917</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,7 +12229,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912420</v>
+        <v>128912424</v>
       </c>
       <c r="B111" t="n">
         <v>86748</v>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705443</v>
+        <v>705432</v>
       </c>
       <c r="R111" t="n">
-        <v>6396921</v>
+        <v>6396615</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,7 +12326,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912417</v>
+        <v>128912420</v>
       </c>
       <c r="B112" t="n">
         <v>86748</v>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705276</v>
+        <v>705443</v>
       </c>
       <c r="R112" t="n">
-        <v>6396964</v>
+        <v>6396921</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,32 +12423,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912404</v>
+        <v>128912417</v>
       </c>
       <c r="B113" t="n">
-        <v>86793</v>
+        <v>86748</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705405</v>
+        <v>705276</v>
       </c>
       <c r="R113" t="n">
-        <v>6396928</v>
+        <v>6396964</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12816,32 +12816,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128912380</v>
+        <v>128912388</v>
       </c>
       <c r="B117" t="n">
-        <v>91048</v>
+        <v>90337</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12851,10 +12851,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>705428</v>
+        <v>705434</v>
       </c>
       <c r="R117" t="n">
-        <v>6396581</v>
+        <v>6396836</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12887,6 +12887,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12913,32 +12918,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128912422</v>
+        <v>128912380</v>
       </c>
       <c r="B118" t="n">
-        <v>86748</v>
+        <v>91048</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>249278</v>
+        <v>5741</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12948,10 +12953,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>705469</v>
+        <v>705428</v>
       </c>
       <c r="R118" t="n">
-        <v>6396714</v>
+        <v>6396581</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13010,32 +13015,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128912388</v>
+        <v>128912422</v>
       </c>
       <c r="B119" t="n">
-        <v>90337</v>
+        <v>86748</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2072</v>
+        <v>249278</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13045,10 +13050,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>705434</v>
+        <v>705469</v>
       </c>
       <c r="R119" t="n">
-        <v>6396836</v>
+        <v>6396714</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13081,11 +13086,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>4 st</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13209,32 +13209,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128912379</v>
+        <v>128912421</v>
       </c>
       <c r="B121" t="n">
-        <v>91048</v>
+        <v>86748</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5741</v>
+        <v>249278</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13244,10 +13244,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>705404</v>
+        <v>705425</v>
       </c>
       <c r="R121" t="n">
-        <v>6396616</v>
+        <v>6396872</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13306,10 +13306,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128912384</v>
+        <v>128912379</v>
       </c>
       <c r="B122" t="n">
-        <v>90326</v>
+        <v>91048</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13317,37 +13317,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6268</v>
+        <v>5741</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>705294</v>
+        <v>705404</v>
       </c>
       <c r="R122" t="n">
-        <v>6396977</v>
+        <v>6396616</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13382,18 +13379,12 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Utbrett mycel med minst 10 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13412,45 +13403,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128912421</v>
+        <v>128912384</v>
       </c>
       <c r="B123" t="n">
-        <v>86748</v>
+        <v>90326</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>249278</v>
+        <v>6268</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>705425</v>
+        <v>705294</v>
       </c>
       <c r="R123" t="n">
-        <v>6396872</v>
+        <v>6396977</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13485,12 +13479,18 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Utbrett mycel med minst 10 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13995,32 +13995,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128912410</v>
+        <v>128912423</v>
       </c>
       <c r="B129" t="n">
-        <v>87016</v>
+        <v>86748</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>449</v>
+        <v>249278</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>705430</v>
+        <v>705462</v>
       </c>
       <c r="R129" t="n">
-        <v>6396796</v>
+        <v>6396694</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14092,32 +14092,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128912423</v>
+        <v>128912410</v>
       </c>
       <c r="B130" t="n">
-        <v>86748</v>
+        <v>87016</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>249278</v>
+        <v>449</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>705462</v>
+        <v>705430</v>
       </c>
       <c r="R130" t="n">
-        <v>6396694</v>
+        <v>6396796</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6291,48 +6291,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884885</v>
+        <v>128884883</v>
       </c>
       <c r="B52" t="n">
-        <v>86895</v>
+        <v>86793</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3611</v>
+        <v>1985</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705360</v>
+        <v>705450</v>
       </c>
       <c r="R52" t="n">
-        <v>6396790</v>
+        <v>6396748</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6392,7 +6389,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884883</v>
+        <v>128884302</v>
       </c>
       <c r="B53" t="n">
         <v>86793</v>
@@ -6423,14 +6420,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705450</v>
+        <v>705513</v>
       </c>
       <c r="R53" t="n">
-        <v>6396748</v>
+        <v>6396594</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6460,75 +6457,87 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884302</v>
+        <v>128884885</v>
       </c>
       <c r="B54" t="n">
-        <v>86793</v>
+        <v>86895</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1985</v>
+        <v>3611</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>705513</v>
+        <v>705360</v>
       </c>
       <c r="R54" t="n">
-        <v>6396594</v>
+        <v>6396790</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,39 +6567,30 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7902,32 +7902,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128884861</v>
+        <v>128884914</v>
       </c>
       <c r="B68" t="n">
-        <v>87039</v>
+        <v>86748</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>705483</v>
+        <v>705401</v>
       </c>
       <c r="R68" t="n">
-        <v>6396620</v>
+        <v>6396625</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7981,6 +7981,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7999,32 +8000,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128884914</v>
+        <v>128884861</v>
       </c>
       <c r="B69" t="n">
-        <v>86748</v>
+        <v>87039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8034,10 +8035,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>705401</v>
+        <v>705483</v>
       </c>
       <c r="R69" t="n">
-        <v>6396625</v>
+        <v>6396620</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8078,7 +8079,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884898</v>
+        <v>128884865</v>
       </c>
       <c r="B70" t="n">
-        <v>92871</v>
+        <v>91048</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,37 +8108,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705425</v>
+        <v>705416</v>
       </c>
       <c r="R70" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8198,10 +8195,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884871</v>
+        <v>128884898</v>
       </c>
       <c r="B71" t="n">
-        <v>87060</v>
+        <v>92871</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,27 +8206,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3624</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705290</v>
+        <v>705425</v>
       </c>
       <c r="R71" t="n">
         <v>6396809</v>
@@ -8273,6 +8277,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8291,48 +8296,41 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884886</v>
+        <v>128884871</v>
       </c>
       <c r="B72" t="n">
-        <v>86895</v>
+        <v>87060</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3611</v>
+        <v>3624</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705473</v>
+        <v>705290</v>
       </c>
       <c r="R72" t="n">
-        <v>6396572</v>
+        <v>6396809</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8373,7 +8371,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8392,45 +8389,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884865</v>
+        <v>128884886</v>
       </c>
       <c r="B73" t="n">
-        <v>91048</v>
+        <v>86895</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5741</v>
+        <v>3611</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705416</v>
+        <v>705473</v>
       </c>
       <c r="R73" t="n">
-        <v>6396601</v>
+        <v>6396572</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884867</v>
+        <v>128884869</v>
       </c>
       <c r="B75" t="n">
-        <v>91048</v>
+        <v>86841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5741</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>705431</v>
+        <v>705297</v>
       </c>
       <c r="R75" t="n">
-        <v>6396688</v>
+        <v>6396817</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8684,32 +8684,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884869</v>
+        <v>128884867</v>
       </c>
       <c r="B76" t="n">
-        <v>86841</v>
+        <v>91048</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>424</v>
+        <v>5741</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>705297</v>
+        <v>705431</v>
       </c>
       <c r="R76" t="n">
-        <v>6396817</v>
+        <v>6396688</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884882</v>
+        <v>128889624</v>
       </c>
       <c r="B84" t="n">
-        <v>86793</v>
+        <v>90337</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1985</v>
+        <v>2072</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705380</v>
+        <v>705513</v>
       </c>
       <c r="R84" t="n">
-        <v>6396917</v>
+        <v>6396594</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,9 +9566,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9583,57 +9593,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128889624</v>
+        <v>128884882</v>
       </c>
       <c r="B85" t="n">
-        <v>90337</v>
+        <v>86793</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2072</v>
+        <v>1985</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705513</v>
+        <v>705380</v>
       </c>
       <c r="R85" t="n">
-        <v>6396594</v>
+        <v>6396917</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9663,19 +9673,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,12 +9690,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9799,45 +9799,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128884300</v>
+        <v>128884878</v>
       </c>
       <c r="B87" t="n">
-        <v>86841</v>
+        <v>86994</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>705540</v>
+        <v>705291</v>
       </c>
       <c r="R87" t="n">
-        <v>6396625</v>
+        <v>6396809</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9867,46 +9867,37 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128884870</v>
+        <v>128884300</v>
       </c>
       <c r="B88" t="n">
         <v>86841</v>
@@ -9937,14 +9928,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>705479</v>
+        <v>705540</v>
       </c>
       <c r="R88" t="n">
-        <v>6396566</v>
+        <v>6396625</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9974,9 +9965,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9991,44 +9992,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128884878</v>
+        <v>128884870</v>
       </c>
       <c r="B89" t="n">
-        <v>86994</v>
+        <v>86841</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10038,10 +10039,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>705291</v>
+        <v>705479</v>
       </c>
       <c r="R89" t="n">
-        <v>6396809</v>
+        <v>6396566</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10082,7 +10083,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10505,32 +10505,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884876</v>
+        <v>128884306</v>
       </c>
       <c r="B94" t="n">
-        <v>90337</v>
+        <v>86895</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2072</v>
+        <v>3611</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10539,14 +10539,14 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>705430</v>
+        <v>705439</v>
       </c>
       <c r="R94" t="n">
-        <v>6396834</v>
+        <v>6396582</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10576,9 +10576,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10594,44 +10604,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128884306</v>
+        <v>128884876</v>
       </c>
       <c r="B95" t="n">
-        <v>86895</v>
+        <v>90337</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3611</v>
+        <v>2072</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10640,14 +10650,14 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>705439</v>
+        <v>705430</v>
       </c>
       <c r="R95" t="n">
-        <v>6396582</v>
+        <v>6396834</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10677,19 +10687,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10705,57 +10705,60 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128884915</v>
+        <v>128884900</v>
       </c>
       <c r="B96" t="n">
-        <v>86748</v>
+        <v>92871</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>705291</v>
+        <v>705445</v>
       </c>
       <c r="R96" t="n">
-        <v>6396949</v>
+        <v>6396819</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10796,6 +10799,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10814,48 +10818,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128884900</v>
+        <v>128884915</v>
       </c>
       <c r="B97" t="n">
-        <v>92871</v>
+        <v>86748</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>705445</v>
+        <v>705291</v>
       </c>
       <c r="R97" t="n">
-        <v>6396819</v>
+        <v>6396949</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10896,7 +10897,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10915,10 +10915,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128884303</v>
+        <v>128884913</v>
       </c>
       <c r="B98" t="n">
-        <v>86895</v>
+        <v>86748</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3611</v>
+        <v>249278</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>705477</v>
+        <v>705414</v>
       </c>
       <c r="R98" t="n">
-        <v>6396583</v>
+        <v>6396611</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10983,87 +10983,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128884899</v>
+        <v>128884910</v>
       </c>
       <c r="B99" t="n">
-        <v>92871</v>
+        <v>86748</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5964</v>
+        <v>249278</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>705436</v>
+        <v>705273</v>
       </c>
       <c r="R99" t="n">
-        <v>6396834</v>
+        <v>6396934</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11123,7 +11111,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128884897</v>
+        <v>128884899</v>
       </c>
       <c r="B100" t="n">
         <v>92871</v>
@@ -11161,10 +11149,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>705297</v>
+        <v>705436</v>
       </c>
       <c r="R100" t="n">
-        <v>6396949</v>
+        <v>6396834</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11224,45 +11212,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128884913</v>
+        <v>128884897</v>
       </c>
       <c r="B101" t="n">
-        <v>86748</v>
+        <v>92871</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>249278</v>
+        <v>5964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>705414</v>
+        <v>705297</v>
       </c>
       <c r="R101" t="n">
-        <v>6396611</v>
+        <v>6396949</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11322,10 +11313,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128884910</v>
+        <v>128884303</v>
       </c>
       <c r="B102" t="n">
-        <v>86748</v>
+        <v>86895</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11333,34 +11324,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>249278</v>
+        <v>3611</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>705273</v>
+        <v>705477</v>
       </c>
       <c r="R102" t="n">
-        <v>6396934</v>
+        <v>6396583</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11390,30 +11381,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -12035,32 +12035,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128912404</v>
+        <v>128912420</v>
       </c>
       <c r="B109" t="n">
-        <v>86793</v>
+        <v>86748</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1985</v>
+        <v>249278</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>705405</v>
+        <v>705443</v>
       </c>
       <c r="R109" t="n">
-        <v>6396928</v>
+        <v>6396921</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128912419</v>
+        <v>128912417</v>
       </c>
       <c r="B110" t="n">
         <v>86748</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>705420</v>
+        <v>705276</v>
       </c>
       <c r="R110" t="n">
-        <v>6396917</v>
+        <v>6396964</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12229,32 +12229,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128912424</v>
+        <v>128912404</v>
       </c>
       <c r="B111" t="n">
-        <v>86748</v>
+        <v>86793</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>249278</v>
+        <v>1985</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>705432</v>
+        <v>705405</v>
       </c>
       <c r="R111" t="n">
-        <v>6396615</v>
+        <v>6396928</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12326,7 +12326,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128912420</v>
+        <v>128912419</v>
       </c>
       <c r="B112" t="n">
         <v>86748</v>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>705443</v>
+        <v>705420</v>
       </c>
       <c r="R112" t="n">
-        <v>6396921</v>
+        <v>6396917</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12423,7 +12423,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128912417</v>
+        <v>128912424</v>
       </c>
       <c r="B113" t="n">
         <v>86748</v>
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>705276</v>
+        <v>705432</v>
       </c>
       <c r="R113" t="n">
-        <v>6396964</v>
+        <v>6396615</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15254,32 +15254,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128912403</v>
+        <v>128912399</v>
       </c>
       <c r="B142" t="n">
-        <v>86793</v>
+        <v>86994</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1985</v>
+        <v>6003295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15289,10 +15289,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>705401</v>
+        <v>705482</v>
       </c>
       <c r="R142" t="n">
-        <v>6396966</v>
+        <v>6396750</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15333,6 +15333,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15351,32 +15352,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128912399</v>
+        <v>128912403</v>
       </c>
       <c r="B143" t="n">
-        <v>86994</v>
+        <v>86793</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6003295</v>
+        <v>1985</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15386,10 +15387,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>705482</v>
+        <v>705401</v>
       </c>
       <c r="R143" t="n">
-        <v>6396750</v>
+        <v>6396966</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15430,7 +15431,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33728-2025 artfynd.xlsx
+++ b/artfynd/A 33728-2025 artfynd.xlsx
@@ -6291,45 +6291,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884883</v>
+        <v>128884885</v>
       </c>
       <c r="B52" t="n">
-        <v>86793</v>
+        <v>86896</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1985</v>
+        <v>3611</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>705450</v>
+        <v>705360</v>
       </c>
       <c r="R52" t="n">
-        <v>6396748</v>
+        <v>6396790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6389,10 +6392,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884302</v>
+        <v>128884883</v>
       </c>
       <c r="B53" t="n">
-        <v>86793</v>
+        <v>86794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6420,14 +6423,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>705513</v>
+        <v>705450</v>
       </c>
       <c r="R53" t="n">
-        <v>6396594</v>
+        <v>6396748</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6457,87 +6460,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884885</v>
+        <v>128884302</v>
       </c>
       <c r="B54" t="n">
-        <v>86895</v>
+        <v>86794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3611</v>
+        <v>1985</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>705360</v>
+        <v>705513</v>
       </c>
       <c r="R54" t="n">
-        <v>6396790</v>
+        <v>6396594</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,30 +6558,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6600,7 +6600,7 @@
         <v>128889600</v>
       </c>
       <c r="B55" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884872</v>
+        <v>128884906</v>
       </c>
       <c r="B56" t="n">
-        <v>92847</v>
+        <v>92192</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6715,21 +6715,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>6031</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>705338</v>
+        <v>705291</v>
       </c>
       <c r="R56" t="n">
-        <v>6396936</v>
+        <v>6396952</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,10 +6801,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884906</v>
+        <v>128884884</v>
       </c>
       <c r="B57" t="n">
-        <v>92177</v>
+        <v>91049</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6812,21 +6812,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6031</v>
+        <v>5741</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>705291</v>
+        <v>705475</v>
       </c>
       <c r="R57" t="n">
-        <v>6396952</v>
+        <v>6396574</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6880,6 +6880,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6898,45 +6899,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884884</v>
+        <v>128884301</v>
       </c>
       <c r="B58" t="n">
-        <v>91048</v>
+        <v>91075</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5741</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>705475</v>
+        <v>705546</v>
       </c>
       <c r="R58" t="n">
-        <v>6396574</v>
+        <v>6396613</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6966,75 +6967,84 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884301</v>
+        <v>128884887</v>
       </c>
       <c r="B59" t="n">
-        <v>91074</v>
+        <v>86971</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>1988</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>705546</v>
+        <v>705305</v>
       </c>
       <c r="R59" t="n">
-        <v>6396613</v>
+        <v>6396830</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7064,19 +7074,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7091,22 +7091,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884887</v>
+        <v>128884872</v>
       </c>
       <c r="B60" t="n">
-        <v>86970</v>
+        <v>92833</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7114,21 +7114,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1988</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>705305</v>
+        <v>705338</v>
       </c>
       <c r="R60" t="n">
-        <v>6396830</v>
+        <v>6396936</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7203,7 +7203,7 @@
         <v>128884894</v>
       </c>
       <c r="B61" t="n">
-        <v>91000</v>
+        <v>91001</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>128884863</v>
       </c>
       <c r="B62" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>128890120</v>
       </c>
       <c r="B63" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>128884875</v>
       </c>
       <c r="B64" t="n">
-        <v>90337</v>
+        <v>90338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>128884294</v>
       </c>
       <c r="B65" t="n">
-        <v>86748</v>
+        <v>86749</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128884912</v>
       </c>
       <c r="B66" t="n">
-        <v>86748</v>
+        <v>86749</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>128884879</v>
       </c>
       <c r="B67" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7902,32 +7902,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128884914</v>
+        <v>128884861</v>
       </c>
       <c r="B68" t="n">
-        <v>86748</v>
+        <v>87040</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>705401</v>
+        <v>705483</v>
       </c>
       <c r="R68" t="n">
-        <v>6396625</v>
+        <v>6396620</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7981,7 +7981,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8000,32 +7999,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128884861</v>
+        <v>128884914</v>
       </c>
       <c r="B69" t="n">
-        <v>87039</v>
+        <v>86749</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8035,10 +8034,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>705483</v>
+        <v>705401</v>
       </c>
       <c r="R69" t="n">
-        <v>6396620</v>
+        <v>6396625</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8079,6 +8078,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128884865</v>
+        <v>128884871</v>
       </c>
       <c r="B70" t="n">
-        <v>91048</v>
+        <v>87061</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,23 +8108,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5741</v>
+        <v>3624</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8132,10 +8128,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>705416</v>
+        <v>705290</v>
       </c>
       <c r="R70" t="n">
-        <v>6396601</v>
+        <v>6396809</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8176,7 +8172,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8195,32 +8190,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128884898</v>
+        <v>128884886</v>
       </c>
       <c r="B71" t="n">
-        <v>92871</v>
+        <v>86896</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8233,10 +8228,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>705425</v>
+        <v>705473</v>
       </c>
       <c r="R71" t="n">
-        <v>6396809</v>
+        <v>6396572</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8296,10 +8291,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128884871</v>
+        <v>128884865</v>
       </c>
       <c r="B72" t="n">
-        <v>87060</v>
+        <v>91049</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8307,19 +8302,23 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3624</v>
+        <v>5741</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8327,10 +8326,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>705290</v>
+        <v>705416</v>
       </c>
       <c r="R72" t="n">
-        <v>6396809</v>
+        <v>6396601</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8371,6 +8370,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8389,32 +8389,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884886</v>
+        <v>128884898</v>
       </c>
       <c r="B73" t="n">
-        <v>86895</v>
+        <v>92857</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>705473</v>
+        <v>705425</v>
       </c>
       <c r="R73" t="n">
-        <v>6396572</v>
+        <v>6396809</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8493,7 +8493,7 @@
         <v>128884868</v>
       </c>
       <c r="B74" t="n">
-        <v>91048</v>
+        <v>91049</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884869</v>
+        <v>128884867</v>
       </c>
       <c r="B75" t="n">
-        <v>86841</v>
+        <v>91049</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>5741</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>705297</v>
+        <v>705431</v>
       </c>
       <c r="R75" t="n">
-        <v>6396817</v>
+        <v>6396688</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8684,32 +8684,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884867</v>
+        <v>128884869</v>
       </c>
       <c r="B76" t="n">
-        <v>91048</v>
+        <v>86842</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5741</v>
+        <v>424</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>705431</v>
+        <v>705297</v>
       </c>
       <c r="R76" t="n">
-        <v>6396688</v>
+        <v>6396817</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8784,7 +8784,7 @@
         <v>128884890</v>
       </c>
       <c r="B77" t="n">
-        <v>105728</v>
+        <v>105754</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8878,45 +8878,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884296</v>
+        <v>128884873</v>
       </c>
       <c r="B78" t="n">
-        <v>91048</v>
+        <v>90338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5741</v>
+        <v>2072</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>705419</v>
+        <v>705314</v>
       </c>
       <c r="R78" t="n">
-        <v>6396769</v>
+        <v>6396809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8946,87 +8949,75 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884873</v>
+        <v>128884296</v>
       </c>
       <c r="B79" t="n">
-        <v>90337</v>
+        <v>91049</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2072</v>
+        <v>5741</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>705314</v>
+        <v>705419</v>
       </c>
       <c r="R79" t="n">
-        <v>6396809</v>
+        <v>6396769</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9056,30 +9047,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
         <v>128884299</v>
       </c>
       <c r="B80" t="n">
-        <v>86895</v>
+        <v>86896</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>128884881</v>
       </c>
       <c r="B81" t="n">
-        <v>86981</v>
+        <v>86982</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>128884305</v>
       </c>
       <c r="B82" t="n">
-        <v>91048</v>
+        <v>91049</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>128884866</v>
       </c>
       <c r="B83" t="n">
-        <v>91048</v>
+        <v>91049</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9498,45 +9498,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128889624</v>
+        <v>128884862</v>
       </c>
       <c r="B84" t="n">
-        <v>90337</v>
+        <v>87040</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2072</v>
+        <v>3767</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bro, Gtl</t>
+          <t>Bro Ytlings, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>705513</v>
+        <v>705398</v>
       </c>
       <c r="R84" t="n">
-        <v>6396594</v>
+        <v>6396569</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9566,19 +9566,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9593,57 +9583,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884882</v>
+        <v>128889624</v>
       </c>
       <c r="B85" t="n">
-        <v>86793</v>
+        <v>90338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1985</v>
+        <v>2072</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>705380</v>
+        <v>705513</v>
       </c>
       <c r="R85" t="n">
-        <v>6396917</v>
+        <v>6396594</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9673,9 +9663,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9690,22 +9690,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884862</v>
+        <v>128884882</v>
       </c>
       <c r="B86" t="n">
-        <v>87039</v>
+        <v>86794</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>705398</v>
+        <v>705380</v>
       </c>
       <c r="R86" t="n">
-        <v>6396569</v>
+        <v>6396917</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9799,45 +9799,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128884878</v>
+        <v>128884300</v>
       </c>
       <c r="B87" t="n">
-        <v>86994</v>
+        <v>86842</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bro Ytlings, Gtl</t>
+          <t>Bro, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>705291</v>
+        <v>705540</v>
       </c>
       <c r="R87" t="n">
-        <v>6396809</v>
+        <v>6396625</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9867,40 +9867,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n"